--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45109</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>45155</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44585</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>45540</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 27881-2026</t>
+          <t>A 12943-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46191</v>
+        <v>44642</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1990,23 +1990,23 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
@@ -2014,155 +2014,21 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="T11" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="U11" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Björktrast
-Harticka
-Lunglav
-Rödvingetrast
-Talltita
-Tretåig hackspett
-Ullticka
-Finbräken
-Kransrams
-Luddlav
-Spindelblomster
-Stuplav
-Svart trolldruva
-Tvåblad
-Ögonpyrola
-Bergfink
-Blåsippa
-Brudborste
-Ekbräken
-Kransmossa
-Kärrfibbla
-Nordisk stormhatt
-Ormbär
-Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 27881-2026 artfynd.xlsx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 27881-2026 karta.png", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 27881-2026 georefererad karta.tif", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 27881-2026 FSC-klagomål.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 27881-2026 FSC-klagomål mail.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 27881-2026 tillsynsbegäran.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 27881-2026 tillsynsbegäran mail.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 27881-2026 prioriterade fågelarter.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 12943-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44642</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>12</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>23</v>
-      </c>
-      <c r="T12" t="n">
-        <v>68</v>
-      </c>
-      <c r="U12" t="n">
-        <v>56</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Trolldruvemätare
 Knärot
@@ -2189,115 +2055,115 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 12943-2022 artfynd.xlsx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 12943-2022 karta.png", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 12943-2022 georefererad karta.tif", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 12943-2022 karta knärot.png", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 12943-2022 FSC-klagomål.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 12943-2022 FSC-klagomål mail.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 12943-2022 tillsynsbegäran.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 12943-2022 tillsynsbegäran mail.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 12943-2022 prioriterade fågelarter.docx", "A 12943-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 14960-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>46104</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>14.8</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J12" t="n">
         <v>8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K12" t="n">
         <v>7</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L12" t="n">
         <v>7</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M12" t="n">
         <v>2</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>9</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R12" t="n">
         <v>2</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S12" t="n">
         <v>22</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T12" t="n">
         <v>180</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U12" t="n">
         <v>164</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -2323,115 +2189,115 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 14960-2026 artfynd.xlsx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 14960-2026 karta.png", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 14960-2026 georefererad karta.tif", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 14960-2026 karta knärot.png", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 14960-2026 FSC-klagomål.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 14960-2026 FSC-klagomål mail.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 14960-2026 tillsynsbegäran.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 14960-2026 tillsynsbegäran mail.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 14960-2026 prioriterade fågelarter.docx", "A 14960-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 48059-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>45932</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>12.2</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J13" t="n">
         <v>6</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L13" t="n">
         <v>12</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M13" t="n">
         <v>2</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>14</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R13" t="n">
         <v>2</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S13" t="n">
         <v>22</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T13" t="n">
         <v>115</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U13" t="n">
         <v>115</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -2457,40 +2323,170 @@
 Tjäder</t>
         </is>
       </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 48059-2025 artfynd.xlsx", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 48059-2025 karta.png", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 48059-2025 georefererad karta.tif", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 48059-2025 karta knärot.png", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 48059-2025 FSC-klagomål.docx", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 48059-2025 FSC-klagomål mail.docx", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 48059-2025 tillsynsbegäran.docx", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 48059-2025 tillsynsbegäran mail.docx", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 48059-2025 prioriterade fågelarter.docx", "A 48059-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 27881-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>22</v>
+      </c>
+      <c r="T14" t="n">
+        <v>37</v>
+      </c>
+      <c r="U14" t="n">
+        <v>37</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Lunglav
+Rödvingetrast
+Talltita
+Tretåig hackspett
+Ullticka
+Finbräken
+Kransrams
+Luddlav
+Spindelblomster
+Stuplav
+Svart trolldruva
+Tvåblad
+Ögonpyrola
+Blåsippa
+Brudborste
+Ekbräken
+Kransmossa
+Kärrfibbla
+Nordisk stormhatt
+Ormbär
+Fläcknycklar</t>
+        </is>
+      </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 48059-2025 artfynd.xlsx", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 27881-2026 artfynd.xlsx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 48059-2025 karta.png", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 27881-2026 karta.png", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 48059-2025 georefererad karta.tif", "A 48059-2025")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 48059-2025 karta knärot.png", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 27881-2026 georefererad karta.tif", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 48059-2025 FSC-klagomål.docx", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 27881-2026 FSC-klagomål.docx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 48059-2025 FSC-klagomål mail.docx", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 27881-2026 FSC-klagomål mail.docx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 48059-2025 tillsynsbegäran.docx", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 27881-2026 tillsynsbegäran.docx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 48059-2025 tillsynsbegäran mail.docx", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 27881-2026 tillsynsbegäran mail.docx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 48059-2025 prioriterade fågelarter.docx", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 27881-2026 prioriterade fågelarter.docx", "A 27881-2026")</f>
         <v/>
       </c>
     </row>
@@ -2514,7 +2510,7 @@
         <v>46108</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2643,7 +2639,7 @@
         <v>45985</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2776,7 +2772,7 @@
         <v>45600</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2914,7 +2910,7 @@
         <v>46195</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3047,7 +3043,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3180,7 +3176,7 @@
         <v>45924</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3312,7 +3308,7 @@
         <v>46195</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3444,7 +3440,7 @@
         <v>46119</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3572,7 +3568,7 @@
         <v>46195</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3703,7 +3699,7 @@
         <v>45988</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3838,7 +3834,7 @@
         <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3964,7 +3960,7 @@
         <v>45975</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4094,7 +4090,7 @@
         <v>46129</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4219,7 +4215,7 @@
         <v>44945</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4347,7 +4343,7 @@
         <v>45747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4475,7 +4471,7 @@
         <v>44971</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4603,7 +4599,7 @@
         <v>44819</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4731,7 +4727,7 @@
         <v>46210</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4858,7 +4854,7 @@
         <v>45376</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4986,7 +4982,7 @@
         <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5104,7 +5100,7 @@
         <v>45932</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5230,7 +5226,7 @@
         <v>45916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5356,7 +5352,7 @@
         <v>46044</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5473,7 +5469,7 @@
         <v>45975</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5593,7 +5589,7 @@
         <v>45978</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5713,7 +5709,7 @@
         <v>45890</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5837,7 +5833,7 @@
         <v>46073</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5961,7 +5957,7 @@
         <v>46010</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6085,7 +6081,7 @@
         <v>45929</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6205,7 +6201,7 @@
         <v>46140</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6320,7 +6316,7 @@
         <v>45932</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6443,7 +6439,7 @@
         <v>46213</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6566,7 +6562,7 @@
         <v>45602</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6693,7 +6689,7 @@
         <v>45475</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6816,7 +6812,7 @@
         <v>45063</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6934,7 +6930,7 @@
         <v>45575</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7052,7 +7048,7 @@
         <v>45415</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7174,7 +7170,7 @@
         <v>45574</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7293,7 +7289,7 @@
         <v>46044</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7407,7 +7403,7 @@
         <v>44851</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7529,7 +7525,7 @@
         <v>46195</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7651,7 +7647,7 @@
         <v>45937</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7773,7 +7769,7 @@
         <v>45526</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7892,7 +7888,7 @@
         <v>46042</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8010,7 +8006,7 @@
         <v>45621</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8128,7 +8124,7 @@
         <v>45986</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8246,7 +8242,7 @@
         <v>44637</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8359,7 +8355,7 @@
         <v>45649</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8476,7 +8472,7 @@
         <v>45470</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8597,7 +8593,7 @@
         <v>45940</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8718,7 +8714,7 @@
         <v>45937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8839,7 +8835,7 @@
         <v>46133</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8957,7 +8953,7 @@
         <v>45952</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9078,7 +9074,7 @@
         <v>46076</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9198,7 +9194,7 @@
         <v>45897</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9315,7 +9311,7 @@
         <v>45170</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9436,7 +9432,7 @@
         <v>45349</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9557,7 +9553,7 @@
         <v>46119</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9677,7 +9673,7 @@
         <v>45161</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9797,7 +9793,7 @@
         <v>46119</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9913,7 +9909,7 @@
         <v>44911</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10029,7 +10025,7 @@
         <v>44945</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10149,7 +10145,7 @@
         <v>45189</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10260,7 +10256,7 @@
         <v>46073</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10379,7 +10375,7 @@
         <v>46073</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10498,7 +10494,7 @@
         <v>45028</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10618,7 +10614,7 @@
         <v>46119</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10737,7 +10733,7 @@
         <v>46010</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10856,7 +10852,7 @@
         <v>45936</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10975,7 +10971,7 @@
         <v>46043</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11090,7 +11086,7 @@
         <v>46105</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11205,7 +11201,7 @@
         <v>45890</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11320,7 +11316,7 @@
         <v>45806</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11439,7 +11435,7 @@
         <v>45953</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11558,7 +11554,7 @@
         <v>45975</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11673,7 +11669,7 @@
         <v>45751</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11789,7 +11785,7 @@
         <v>45762</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11904,7 +11900,7 @@
         <v>44929</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12018,7 +12014,7 @@
         <v>45618</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12137,7 +12133,7 @@
         <v>44840</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12247,7 +12243,7 @@
         <v>46006</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12366,7 +12362,7 @@
         <v>45233</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12481,7 +12477,7 @@
         <v>46097</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12591,7 +12587,7 @@
         <v>46195</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12701,7 +12697,7 @@
         <v>46008</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12815,7 +12811,7 @@
         <v>46065</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12929,7 +12925,7 @@
         <v>45553</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13039,7 +13035,7 @@
         <v>46059</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13157,7 +13153,7 @@
         <v>45809</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13271,7 +13267,7 @@
         <v>44623</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13380,7 +13376,7 @@
         <v>44742</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13494,7 +13490,7 @@
         <v>45349</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13608,7 +13604,7 @@
         <v>45901</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13726,7 +13722,7 @@
         <v>45278</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13835,7 +13831,7 @@
         <v>45975</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13948,7 +13944,7 @@
         <v>45897</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14062,7 +14058,7 @@
         <v>45349</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14180,7 +14176,7 @@
         <v>46000</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14297,7 +14293,7 @@
         <v>46030</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14410,7 +14406,7 @@
         <v>45985</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14523,7 +14519,7 @@
         <v>45049</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14632,7 +14628,7 @@
         <v>45237</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14749,7 +14745,7 @@
         <v>45748</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14857,7 +14853,7 @@
         <v>44904</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14965,7 +14961,7 @@
         <v>44977</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15078,7 +15074,7 @@
         <v>45978</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15190,7 +15186,7 @@
         <v>46098</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15298,7 +15294,7 @@
         <v>44908</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15406,7 +15402,7 @@
         <v>46160</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15522,7 +15518,7 @@
         <v>44750</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15630,7 +15626,7 @@
         <v>44853</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15742,7 +15738,7 @@
         <v>45721</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15855,7 +15851,7 @@
         <v>45570</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15963,7 +15959,7 @@
         <v>46279</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16076,7 +16072,7 @@
         <v>45320</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16184,7 +16180,7 @@
         <v>45462</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16292,7 +16288,7 @@
         <v>45785</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16405,7 +16401,7 @@
         <v>45187</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16521,7 +16517,7 @@
         <v>45245</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16633,7 +16629,7 @@
         <v>44904</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16744,7 +16740,7 @@
         <v>46137</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16851,7 +16847,7 @@
         <v>45919</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16963,7 +16959,7 @@
         <v>45198</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17075,7 +17071,7 @@
         <v>46155</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17182,7 +17178,7 @@
         <v>44904</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17293,7 +17289,7 @@
         <v>45644</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17404,7 +17400,7 @@
         <v>45559</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17516,7 +17512,7 @@
         <v>46177</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17623,7 +17619,7 @@
         <v>45561</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17735,7 +17731,7 @@
         <v>45223</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17847,7 +17843,7 @@
         <v>45233</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17954,7 +17950,7 @@
         <v>45615</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18061,7 +18057,7 @@
         <v>46225</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18177,7 +18173,7 @@
         <v>45737</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18292,7 +18288,7 @@
         <v>46275</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18404,7 +18400,7 @@
         <v>44904</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18511,7 +18507,7 @@
         <v>44956</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18618,7 +18614,7 @@
         <v>45412</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18725,7 +18721,7 @@
         <v>44544</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18835,7 +18831,7 @@
         <v>44957</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18941,7 +18937,7 @@
         <v>45643</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19052,7 +19048,7 @@
         <v>44476</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19162,7 +19158,7 @@
         <v>45321</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19268,7 +19264,7 @@
         <v>45952</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19374,7 +19370,7 @@
         <v>44927</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19484,7 +19480,7 @@
         <v>45533</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19590,7 +19586,7 @@
         <v>45751</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19696,7 +19692,7 @@
         <v>44617</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19807,7 +19803,7 @@
         <v>45987</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19913,7 +19909,7 @@
         <v>45558</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20024,7 +20020,7 @@
         <v>45975</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20130,7 +20126,7 @@
         <v>46198</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20236,7 +20232,7 @@
         <v>44956</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20342,7 +20338,7 @@
         <v>45441</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20457,7 +20453,7 @@
         <v>44916</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20563,7 +20559,7 @@
         <v>45553</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20673,7 +20669,7 @@
         <v>45715</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20779,7 +20775,7 @@
         <v>44643</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20885,7 +20881,7 @@
         <v>45538</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20991,7 +20987,7 @@
         <v>44694</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21101,7 +21097,7 @@
         <v>44515</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21211,7 +21207,7 @@
         <v>44742</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21325,7 +21321,7 @@
         <v>45313</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21435,7 +21431,7 @@
         <v>44594</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21540,7 +21536,7 @@
         <v>44642</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21650,7 +21646,7 @@
         <v>44742</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21760,7 +21756,7 @@
         <v>45238</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21870,7 +21866,7 @@
         <v>45637</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21984,7 +21980,7 @@
         <v>45685</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22089,7 +22085,7 @@
         <v>45096</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22194,7 +22190,7 @@
         <v>46038</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22299,7 +22295,7 @@
         <v>45679</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22409,7 +22405,7 @@
         <v>45511</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22514,7 +22510,7 @@
         <v>45617</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22623,7 +22619,7 @@
         <v>45280</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22728,7 +22724,7 @@
         <v>45509</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22838,7 +22834,7 @@
         <v>46142</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22948,7 +22944,7 @@
         <v>45646</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23062,7 +23058,7 @@
         <v>44900</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23167,7 +23163,7 @@
         <v>45118</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23272,7 +23268,7 @@
         <v>45968</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23382,7 +23378,7 @@
         <v>44785</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23491,7 +23487,7 @@
         <v>45629</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23605,7 +23601,7 @@
         <v>45678</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23710,7 +23706,7 @@
         <v>45624</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23820,7 +23816,7 @@
         <v>45999</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23930,7 +23926,7 @@
         <v>46051</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24035,7 +24031,7 @@
         <v>45223</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24145,7 +24141,7 @@
         <v>46184</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24250,7 +24246,7 @@
         <v>45719</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24360,7 +24356,7 @@
         <v>45763</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24465,7 +24461,7 @@
         <v>46190</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24570,7 +24566,7 @@
         <v>44491</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24680,7 +24676,7 @@
         <v>44928</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24789,7 +24785,7 @@
         <v>46120</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24894,7 +24890,7 @@
         <v>46125</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24999,7 +24995,7 @@
         <v>45559</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25109,7 +25105,7 @@
         <v>46217</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25219,7 +25215,7 @@
         <v>45028</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25324,7 +25320,7 @@
         <v>46276</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25429,7 +25425,7 @@
         <v>45797</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25534,7 +25530,7 @@
         <v>45558</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25644,7 +25640,7 @@
         <v>45841</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25749,7 +25745,7 @@
         <v>45867</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25859,7 +25855,7 @@
         <v>45867</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25969,7 +25965,7 @@
         <v>45957</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26083,7 +26079,7 @@
         <v>44879</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26156,7 +26152,7 @@
         <v>44510</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26229,7 +26225,7 @@
         <v>44524</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26307,7 +26303,7 @@
         <v>44838</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26385,7 +26381,7 @@
         <v>44540</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26458,7 +26454,7 @@
         <v>44613</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26531,7 +26527,7 @@
         <v>44581</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26604,7 +26600,7 @@
         <v>44852</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26677,7 +26673,7 @@
         <v>44561</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26750,7 +26746,7 @@
         <v>44566</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26823,7 +26819,7 @@
         <v>44755</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26901,7 +26897,7 @@
         <v>44852</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26974,7 +26970,7 @@
         <v>44540</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27047,7 +27043,7 @@
         <v>44537</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27120,7 +27116,7 @@
         <v>44889</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27193,7 +27189,7 @@
         <v>44609</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27266,7 +27262,7 @@
         <v>44516</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27339,7 +27335,7 @@
         <v>44875</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27417,7 +27413,7 @@
         <v>44886</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27515,7 +27511,7 @@
         <v>44750</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27588,7 +27584,7 @@
         <v>44517</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27661,7 +27657,7 @@
         <v>44601</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27734,7 +27730,7 @@
         <v>44722</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27812,7 +27808,7 @@
         <v>44722</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27890,7 +27886,7 @@
         <v>44721</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27963,7 +27959,7 @@
         <v>44845</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28036,7 +28032,7 @@
         <v>44540</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28109,7 +28105,7 @@
         <v>44655</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28182,7 +28178,7 @@
         <v>44704</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28260,7 +28256,7 @@
         <v>45273</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28333,7 +28329,7 @@
         <v>44799</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28406,7 +28402,7 @@
         <v>45634</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28479,7 +28475,7 @@
         <v>44599</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28552,7 +28548,7 @@
         <v>45189</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28625,7 +28621,7 @@
         <v>44875</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28698,7 +28694,7 @@
         <v>45505</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28776,7 +28772,7 @@
         <v>44607</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28849,7 +28845,7 @@
         <v>44911</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28922,7 +28918,7 @@
         <v>45721</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28995,7 +28991,7 @@
         <v>44706</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29068,7 +29064,7 @@
         <v>45667</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29146,7 +29142,7 @@
         <v>45569</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29219,7 +29215,7 @@
         <v>45588</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29292,7 +29288,7 @@
         <v>45457</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29365,7 +29361,7 @@
         <v>45315</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29438,7 +29434,7 @@
         <v>45600</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29516,7 +29512,7 @@
         <v>45621</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29594,7 +29590,7 @@
         <v>44634</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29667,7 +29663,7 @@
         <v>44911</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29740,7 +29736,7 @@
         <v>45691</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29818,7 +29814,7 @@
         <v>44837</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29891,7 +29887,7 @@
         <v>44909</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29969,7 +29965,7 @@
         <v>45221</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30042,7 +30038,7 @@
         <v>45336</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30115,7 +30111,7 @@
         <v>44977</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30193,7 +30189,7 @@
         <v>44711</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30266,7 +30262,7 @@
         <v>44475</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30339,7 +30335,7 @@
         <v>44742</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30412,7 +30408,7 @@
         <v>44655</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30485,7 +30481,7 @@
         <v>44529</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30558,7 +30554,7 @@
         <v>45321</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30631,7 +30627,7 @@
         <v>44970</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30709,7 +30705,7 @@
         <v>45659</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30782,7 +30778,7 @@
         <v>45188</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30855,7 +30851,7 @@
         <v>45004</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30928,7 +30924,7 @@
         <v>44743</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31001,7 +30997,7 @@
         <v>45309</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31074,7 +31070,7 @@
         <v>45107</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31147,7 +31143,7 @@
         <v>45261</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31225,7 +31221,7 @@
         <v>45089</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31298,7 +31294,7 @@
         <v>45231</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31376,7 +31372,7 @@
         <v>45223</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31449,7 +31445,7 @@
         <v>45707</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31522,7 +31518,7 @@
         <v>45691</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31595,7 +31591,7 @@
         <v>46029</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31668,7 +31664,7 @@
         <v>46136</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31746,7 +31742,7 @@
         <v>45681</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31824,7 +31820,7 @@
         <v>45681</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31902,7 +31898,7 @@
         <v>45520</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31975,7 +31971,7 @@
         <v>45190</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32048,7 +32044,7 @@
         <v>45625</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32121,7 +32117,7 @@
         <v>45688</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32194,7 +32190,7 @@
         <v>45888</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32267,7 +32263,7 @@
         <v>45800</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32340,7 +32336,7 @@
         <v>45342</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32418,7 +32414,7 @@
         <v>45895</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32491,7 +32487,7 @@
         <v>46139</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32569,7 +32565,7 @@
         <v>44466</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32642,7 +32638,7 @@
         <v>46008</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32715,7 +32711,7 @@
         <v>45895</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32788,7 +32784,7 @@
         <v>45338</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32861,7 +32857,7 @@
         <v>44949</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32934,7 +32930,7 @@
         <v>45632</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33007,7 +33003,7 @@
         <v>45901</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33080,7 +33076,7 @@
         <v>44790</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33153,7 +33149,7 @@
         <v>46139</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33231,7 +33227,7 @@
         <v>46139</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33309,7 +33305,7 @@
         <v>44511</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33382,7 +33378,7 @@
         <v>45696</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33455,7 +33451,7 @@
         <v>45902</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33528,7 +33524,7 @@
         <v>45902</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33601,7 +33597,7 @@
         <v>45837</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33679,7 +33675,7 @@
         <v>45904</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33752,7 +33748,7 @@
         <v>45300</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33825,7 +33821,7 @@
         <v>45909</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33898,7 +33894,7 @@
         <v>45911</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33971,7 +33967,7 @@
         <v>44790</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34044,7 +34040,7 @@
         <v>45344</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34117,7 +34113,7 @@
         <v>45916</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34190,7 +34186,7 @@
         <v>45265</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34268,7 +34264,7 @@
         <v>45922</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34346,7 +34342,7 @@
         <v>45922</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34424,7 +34420,7 @@
         <v>45586</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34502,7 +34498,7 @@
         <v>45922</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34580,7 +34576,7 @@
         <v>45922</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34658,7 +34654,7 @@
         <v>45922</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34736,7 +34732,7 @@
         <v>45922</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34809,7 +34805,7 @@
         <v>45924</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34887,7 +34883,7 @@
         <v>45924</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34965,7 +34961,7 @@
         <v>45096</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35038,7 +35034,7 @@
         <v>46142</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35116,7 +35112,7 @@
         <v>45412</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35189,7 +35185,7 @@
         <v>45588</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35262,7 +35258,7 @@
         <v>45576</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35335,7 +35331,7 @@
         <v>45580</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35408,7 +35404,7 @@
         <v>45583</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35481,7 +35477,7 @@
         <v>45646</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35559,7 +35555,7 @@
         <v>45646</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35637,7 +35633,7 @@
         <v>45708</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35710,7 +35706,7 @@
         <v>45553</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35783,7 +35779,7 @@
         <v>45264</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35856,7 +35852,7 @@
         <v>45937</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35934,7 +35930,7 @@
         <v>44889</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36012,7 +36008,7 @@
         <v>45012</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36085,7 +36081,7 @@
         <v>45112</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36158,7 +36154,7 @@
         <v>45944</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36236,7 +36232,7 @@
         <v>45667</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36314,7 +36310,7 @@
         <v>46153</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36387,7 +36383,7 @@
         <v>45475</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36465,7 +36461,7 @@
         <v>45707</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36538,7 +36534,7 @@
         <v>45593</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36616,7 +36612,7 @@
         <v>45593</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36694,7 +36690,7 @@
         <v>45597</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36772,7 +36768,7 @@
         <v>45954</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36845,7 +36841,7 @@
         <v>45688</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36923,7 +36919,7 @@
         <v>45957</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37001,7 +36997,7 @@
         <v>45958</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37079,7 +37075,7 @@
         <v>46150</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37152,7 +37148,7 @@
         <v>45634</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37225,7 +37221,7 @@
         <v>46150</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37298,7 +37294,7 @@
         <v>45002</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37376,7 +37372,7 @@
         <v>46150</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37449,7 +37445,7 @@
         <v>45964</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37527,7 +37523,7 @@
         <v>45691</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37600,7 +37596,7 @@
         <v>44952</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37673,7 +37669,7 @@
         <v>45177</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37751,7 +37747,7 @@
         <v>45693</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37824,7 +37820,7 @@
         <v>44907</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37902,7 +37898,7 @@
         <v>44750</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37975,7 +37971,7 @@
         <v>46154</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38053,7 +38049,7 @@
         <v>45985</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38126,7 +38122,7 @@
         <v>45985</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38199,7 +38195,7 @@
         <v>46156</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38277,7 +38273,7 @@
         <v>45986</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38350,7 +38346,7 @@
         <v>45887</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38423,7 +38419,7 @@
         <v>46120</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38496,7 +38492,7 @@
         <v>45686</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38569,7 +38565,7 @@
         <v>45987</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38642,7 +38638,7 @@
         <v>45992</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38715,7 +38711,7 @@
         <v>45992</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38788,7 +38784,7 @@
         <v>45012</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38861,7 +38857,7 @@
         <v>45992</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38934,7 +38930,7 @@
         <v>45302</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39007,7 +39003,7 @@
         <v>44911</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39080,7 +39076,7 @@
         <v>46163</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39153,7 +39149,7 @@
         <v>46163</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39226,7 +39222,7 @@
         <v>44721</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39299,7 +39295,7 @@
         <v>45616</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39377,7 +39373,7 @@
         <v>44922</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39450,7 +39446,7 @@
         <v>44680</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39523,7 +39519,7 @@
         <v>46163</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39596,7 +39592,7 @@
         <v>46066</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39669,7 +39665,7 @@
         <v>46164</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39747,7 +39743,7 @@
         <v>46164</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39825,7 +39821,7 @@
         <v>45993</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39898,7 +39894,7 @@
         <v>46000</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39971,7 +39967,7 @@
         <v>46164</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40049,7 +40045,7 @@
         <v>46164</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40122,7 +40118,7 @@
         <v>46000</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40195,7 +40191,7 @@
         <v>46164</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40273,7 +40269,7 @@
         <v>46164</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40351,7 +40347,7 @@
         <v>46164</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40429,7 +40425,7 @@
         <v>46164</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40507,7 +40503,7 @@
         <v>46003</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40580,7 +40576,7 @@
         <v>45239</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40658,7 +40654,7 @@
         <v>46164</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40736,7 +40732,7 @@
         <v>46003</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40809,7 +40805,7 @@
         <v>46003</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40882,7 +40878,7 @@
         <v>46003</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40955,7 +40951,7 @@
         <v>46003</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41028,7 +41024,7 @@
         <v>46007</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41101,7 +41097,7 @@
         <v>46164</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41174,7 +41170,7 @@
         <v>46007</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41252,7 +41248,7 @@
         <v>46010</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41325,7 +41321,7 @@
         <v>46010</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41398,7 +41394,7 @@
         <v>46013</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41471,7 +41467,7 @@
         <v>45628</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41544,7 +41540,7 @@
         <v>46013</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41617,7 +41613,7 @@
         <v>45428</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41695,7 +41691,7 @@
         <v>46014</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41768,7 +41764,7 @@
         <v>45092</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41841,7 +41837,7 @@
         <v>46019</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41914,7 +41910,7 @@
         <v>45709</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41992,7 +41988,7 @@
         <v>46024</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42065,7 +42061,7 @@
         <v>46029</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42138,7 +42134,7 @@
         <v>46206</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42211,7 +42207,7 @@
         <v>46034</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42284,7 +42280,7 @@
         <v>46037</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42357,7 +42353,7 @@
         <v>46032</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42430,7 +42426,7 @@
         <v>45707</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42503,7 +42499,7 @@
         <v>46037</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42576,7 +42572,7 @@
         <v>45748</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42649,7 +42645,7 @@
         <v>45770</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42722,7 +42718,7 @@
         <v>46038</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42795,7 +42791,7 @@
         <v>46041</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42868,7 +42864,7 @@
         <v>45547</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42941,7 +42937,7 @@
         <v>46045</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43019,7 +43015,7 @@
         <v>46045</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43092,7 +43088,7 @@
         <v>46050</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43165,7 +43161,7 @@
         <v>46175</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43243,7 +43239,7 @@
         <v>45344</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43316,7 +43312,7 @@
         <v>45588</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43394,7 +43390,7 @@
         <v>45600</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43472,7 +43468,7 @@
         <v>45260</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43545,7 +43541,7 @@
         <v>45260</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43618,7 +43614,7 @@
         <v>45376</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43691,7 +43687,7 @@
         <v>46056</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43764,7 +43760,7 @@
         <v>44880</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43837,7 +43833,7 @@
         <v>45707</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43915,7 +43911,7 @@
         <v>45462</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43993,7 +43989,7 @@
         <v>46066</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44071,7 +44067,7 @@
         <v>46066</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44149,7 +44145,7 @@
         <v>46070</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44227,7 +44223,7 @@
         <v>44609</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44300,7 +44296,7 @@
         <v>44635</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44373,7 +44369,7 @@
         <v>46073</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44446,7 +44442,7 @@
         <v>46078</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44519,7 +44515,7 @@
         <v>46078</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44592,7 +44588,7 @@
         <v>46184</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44665,7 +44661,7 @@
         <v>46076</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44743,7 +44739,7 @@
         <v>45677</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44816,7 +44812,7 @@
         <v>46183</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44889,7 +44885,7 @@
         <v>45720</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44967,7 +44963,7 @@
         <v>45743</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45040,7 +45036,7 @@
         <v>45722</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45118,7 +45114,7 @@
         <v>45978</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45191,7 +45187,7 @@
         <v>45789</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45264,7 +45260,7 @@
         <v>45736</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45337,7 +45333,7 @@
         <v>45743</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45410,7 +45406,7 @@
         <v>45720</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45488,7 +45484,7 @@
         <v>45149</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45561,7 +45557,7 @@
         <v>45435</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45634,7 +45630,7 @@
         <v>45057</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45707,7 +45703,7 @@
         <v>46188</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45780,7 +45776,7 @@
         <v>45475</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45853,7 +45849,7 @@
         <v>46190</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45926,7 +45922,7 @@
         <v>46190</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45999,7 +45995,7 @@
         <v>46091</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46072,7 +46068,7 @@
         <v>45221</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46145,7 +46141,7 @@
         <v>46190</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46218,7 +46214,7 @@
         <v>45315</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46291,7 +46287,7 @@
         <v>46098</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46364,7 +46360,7 @@
         <v>45477</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46437,7 +46433,7 @@
         <v>45763</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46510,7 +46506,7 @@
         <v>45166</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46588,7 +46584,7 @@
         <v>45236</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46666,7 +46662,7 @@
         <v>45677</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46739,7 +46735,7 @@
         <v>44922</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46812,7 +46808,7 @@
         <v>45057</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46890,7 +46886,7 @@
         <v>44986</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46968,7 +46964,7 @@
         <v>46097</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47046,7 +47042,7 @@
         <v>44735</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47119,7 +47115,7 @@
         <v>45183</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47192,7 +47188,7 @@
         <v>44757</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47265,7 +47261,7 @@
         <v>45237</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47338,7 +47334,7 @@
         <v>44883</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47411,7 +47407,7 @@
         <v>45370</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47484,7 +47480,7 @@
         <v>46114</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47557,7 +47553,7 @@
         <v>46125</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47630,7 +47626,7 @@
         <v>46126</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47708,7 +47704,7 @@
         <v>45159</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47781,7 +47777,7 @@
         <v>45572</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47859,7 +47855,7 @@
         <v>45762</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47937,7 +47933,7 @@
         <v>46133</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48015,7 +48011,7 @@
         <v>46203</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48088,7 +48084,7 @@
         <v>46132</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48161,7 +48157,7 @@
         <v>46132</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48234,7 +48230,7 @@
         <v>46135</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48307,7 +48303,7 @@
         <v>44679</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48380,7 +48376,7 @@
         <v>45223</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48453,7 +48449,7 @@
         <v>46000</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48526,7 +48522,7 @@
         <v>45223</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48599,7 +48595,7 @@
         <v>45236</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48672,7 +48668,7 @@
         <v>45477</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48745,7 +48741,7 @@
         <v>45008</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48818,7 +48814,7 @@
         <v>45660</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48891,7 +48887,7 @@
         <v>46248</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48964,7 +48960,7 @@
         <v>46206</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49037,7 +49033,7 @@
         <v>45639</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49115,7 +49111,7 @@
         <v>44721</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49193,7 +49189,7 @@
         <v>46206</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49266,7 +49262,7 @@
         <v>45096</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49339,7 +49335,7 @@
         <v>44614</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49412,7 +49408,7 @@
         <v>44986</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49490,7 +49486,7 @@
         <v>45231</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49568,7 +49564,7 @@
         <v>45707</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49641,7 +49637,7 @@
         <v>45324</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49719,7 +49715,7 @@
         <v>44533</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49792,7 +49788,7 @@
         <v>44952</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49865,7 +49861,7 @@
         <v>44937</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49938,7 +49934,7 @@
         <v>45429</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50011,7 +50007,7 @@
         <v>45702</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50084,7 +50080,7 @@
         <v>45690</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50157,7 +50153,7 @@
         <v>46216</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50235,7 +50231,7 @@
         <v>45313</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50308,7 +50304,7 @@
         <v>45460</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50381,7 +50377,7 @@
         <v>45615</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50454,7 +50450,7 @@
         <v>46073</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50527,7 +50523,7 @@
         <v>46180</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50600,7 +50596,7 @@
         <v>45939</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50678,7 +50674,7 @@
         <v>45306</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50751,7 +50747,7 @@
         <v>44889</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50824,7 +50820,7 @@
         <v>46220</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50897,7 +50893,7 @@
         <v>46203</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50970,7 +50966,7 @@
         <v>45328</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51043,7 +51039,7 @@
         <v>44564</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51116,7 +51112,7 @@
         <v>45636</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51189,7 +51185,7 @@
         <v>45198</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51267,7 +51263,7 @@
         <v>45692</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51340,7 +51336,7 @@
         <v>46269</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51418,7 +51414,7 @@
         <v>46272</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51491,7 +51487,7 @@
         <v>45779</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51564,7 +51560,7 @@
         <v>45686</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51637,7 +51633,7 @@
         <v>46275</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51710,7 +51706,7 @@
         <v>46231</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51788,7 +51784,7 @@
         <v>46231</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51866,7 +51862,7 @@
         <v>46231</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51944,7 +51940,7 @@
         <v>46231</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52022,7 +52018,7 @@
         <v>46275</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52100,7 +52096,7 @@
         <v>46135</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52173,7 +52169,7 @@
         <v>46279</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52246,7 +52242,7 @@
         <v>46279</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52319,7 +52315,7 @@
         <v>46276</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52397,7 +52393,7 @@
         <v>45686</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52470,7 +52466,7 @@
         <v>45686</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52543,7 +52539,7 @@
         <v>45789</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52616,7 +52612,7 @@
         <v>46279</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52689,7 +52685,7 @@
         <v>46280</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52767,7 +52763,7 @@
         <v>46281</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52840,7 +52836,7 @@
         <v>46281</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52913,7 +52909,7 @@
         <v>45790</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52986,7 +52982,7 @@
         <v>46238</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53059,7 +53055,7 @@
         <v>45793</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53132,7 +53128,7 @@
         <v>46239</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53205,7 +53201,7 @@
         <v>46283</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53283,7 +53279,7 @@
         <v>46241</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53356,7 +53352,7 @@
         <v>46282</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53434,7 +53430,7 @@
         <v>46241</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53507,7 +53503,7 @@
         <v>45561</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53585,7 +53581,7 @@
         <v>45611</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53658,7 +53654,7 @@
         <v>45799</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53731,7 +53727,7 @@
         <v>45803</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53809,7 +53805,7 @@
         <v>45805</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53887,7 +53883,7 @@
         <v>45587</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53960,7 +53956,7 @@
         <v>45691</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54038,7 +54034,7 @@
         <v>45807</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54111,7 +54107,7 @@
         <v>45551</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54189,7 +54185,7 @@
         <v>45813</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54262,7 +54258,7 @@
         <v>45819</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54340,7 +54336,7 @@
         <v>45818</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54418,7 +54414,7 @@
         <v>45847</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54496,7 +54492,7 @@
         <v>45847</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54574,7 +54570,7 @@
         <v>45847</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54652,7 +54648,7 @@
         <v>45800</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54725,7 +54721,7 @@
         <v>45807</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54798,7 +54794,7 @@
         <v>45866</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54876,7 +54872,7 @@
         <v>45744</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54949,7 +54945,7 @@
         <v>45820</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55022,7 +55018,7 @@
         <v>46058</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55095,7 +55091,7 @@
         <v>46058</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45109</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>45155</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44585</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>45540</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>46191</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>44642</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>46104</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>45932</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>46108</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45985</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>45600</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>46195</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>45924</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>46195</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46119</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>46195</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45988</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45975</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>46129</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44945</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>45747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>44819</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>46210</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>44971</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>45376</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>45932</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45112</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>45916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>46044</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>45978</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45890</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>46010</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>46073</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>45929</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45932</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46140</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>46213</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>44851</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45415</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45621</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>45063</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>46044</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45575</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>46195</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>45475</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>45937</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>46042</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45574</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>45602</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>45526</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>45986</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45649</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>46133</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45937</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45470</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>45940</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>45952</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>44637</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45349</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>45897</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>46076</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>46119</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>46119</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>45170</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>45161</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44911</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45189</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>46073</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>46073</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>46119</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>44945</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>46010</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>46043</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>46105</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>45890</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>45936</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>45806</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>45953</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45975</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>45028</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>45751</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44929</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45809</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>46097</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>46065</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>46006</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45762</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>45618</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>46195</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>46008</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45553</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>45233</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>46059</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44623</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>44742</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>45278</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45349</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45901</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>45975</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>45897</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45985</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>46000</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>46030</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45349</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45049</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>44908</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45570</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>45721</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45320</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>45237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45748</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45462</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45978</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>44853</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>46098</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>46160</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>44750</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>44904</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>46279</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>44977</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>45785</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>46280</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45223</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>44904</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45559</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45644</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45919</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45615</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>46137</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>45245</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45198</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>46177</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>45187</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>45233</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>46225</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>46275</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>44956</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45561</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>46155</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>46288</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>44904</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>44904</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>45737</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>45412</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>44544</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45975</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45558</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45553</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>44617</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44927</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44643</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45987</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>45643</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>45441</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45715</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45952</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>44476</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45533</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>46198</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>44916</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>45321</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>44957</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>46282</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>44956</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45751</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44694</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>44515</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>44742</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45313</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44594</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45223</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44742</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45558</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45797</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>44900</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45646</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>45629</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46051</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45096</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45719</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45509</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45763</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45678</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45238</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45624</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>46120</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45968</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45637</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>46125</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45999</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45511</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45685</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45559</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>46038</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45280</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>46142</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>45841</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>44491</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>45867</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>45867</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45617</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>46184</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>46190</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45118</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>46217</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>44642</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45679</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>45028</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>46276</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>44785</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>44928</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45957</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44879</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44510</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>44524</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44838</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>44540</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>44613</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>44581</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44852</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44561</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44566</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44755</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44852</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44540</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>44537</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44609</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44889</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44516</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44875</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>44886</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>44750</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>44517</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>44601</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>44722</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>44722</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>44721</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44845</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>44540</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44655</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>44704</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45621</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>44757</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45412</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45338</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45324</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45370</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45315</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45462</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45702</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>46014</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>46019</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45561</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>46024</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>45309</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>46029</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>45435</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45793</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45477</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45012</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45475</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>45611</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>45002</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>46034</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45625</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45799</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45888</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>46032</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45800</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45707</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>46038</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>45748</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>46037</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>46037</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>46041</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45895</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44911</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45895</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45902</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45902</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>46045</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>46045</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45901</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>46050</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45646</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>45646</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45904</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>45909</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>45477</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>44475</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>45300</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>45911</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>46056</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45803</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45916</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>44599</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32655,7 +32655,7 @@
         <v>45922</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45922</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32811,7 +32811,7 @@
         <v>45922</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>45922</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>45922</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>45922</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>46066</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>46066</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>46070</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>45924</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33430,7 +33430,7 @@
         <v>45924</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>45805</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>45587</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>46076</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>46073</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>45636</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>46078</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>46078</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34029,7 +34029,7 @@
         <v>45722</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>45736</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>45789</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45743</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>45720</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45720</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>45743</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>45588</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>45978</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>45691</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>45551</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>45634</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>45807</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45583</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>45576</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>45580</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>44680</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>46091</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35368,7 +35368,7 @@
         <v>45236</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35446,7 +35446,7 @@
         <v>45937</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>45344</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44977</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>45221</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45944</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45237</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>46098</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44655</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45260</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45707</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44634</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45547</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45057</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45954</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44735</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>46097</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>45688</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>45958</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45964</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>46125</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>46114</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         <v>45813</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37082,7 +37082,7 @@
         <v>45600</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>46126</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>45460</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>46132</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37384,7 +37384,7 @@
         <v>46133</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45818</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37540,7 +37540,7 @@
         <v>44750</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>45985</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37686,7 +37686,7 @@
         <v>45986</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>45985</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>45692</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>46135</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>45992</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45987</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45992</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45992</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>45667</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>46136</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38426,7 +38426,7 @@
         <v>44466</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>46139</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45696</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>45993</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>46000</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>46000</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>45198</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45691</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>44970</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39098,7 +39098,7 @@
         <v>46003</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>46003</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39244,7 +39244,7 @@
         <v>46139</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39322,7 +39322,7 @@
         <v>45819</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>46003</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39473,7 +39473,7 @@
         <v>46139</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>46003</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>46003</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>46008</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>45707</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45837</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>46007</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>46007</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45770</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>46010</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>44711</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>45520</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>46010</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45223</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>46029</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>46013</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>46013</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40734,7 +40734,7 @@
         <v>45707</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>45505</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>46000</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>45586</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>44922</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>44790</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>46142</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
         <v>44909</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>45057</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>46150</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>46150</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>46150</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>45691</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>46153</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>45693</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45096</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44880</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>46154</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>46156</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45261</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45686</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>45887</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42380,7 +42380,7 @@
         <v>46120</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42453,7 +42453,7 @@
         <v>46164</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>46066</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>46163</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45089</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>46163</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>46164</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42901,7 +42901,7 @@
         <v>46164</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>46164</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43052,7 +43052,7 @@
         <v>46164</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43130,7 +43130,7 @@
         <v>45336</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>46164</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>46164</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>46164</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>46164</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>46164</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43588,7 +43588,7 @@
         <v>46163</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>45847</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>45847</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45847</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>45344</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45593</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>46206</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45800</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45096</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45166</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45866</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>46175</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45807</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45092</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45457</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45306</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>46183</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45616</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>46184</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>44529</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45328</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>46188</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>46190</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>46190</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>46190</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45453,7 +45453,7 @@
         <v>45763</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>44609</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45428</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45628</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45190</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45597</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45634</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>46203</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>44564</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45681</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45681</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>45691</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45107</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>46206</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>46206</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45762</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45221</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>44635</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>45189</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45615</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         <v>45429</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>44706</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>45709</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>45572</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45231</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>46216</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>45707</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45659</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45677</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>45188</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>44743</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>44721</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45721</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45321</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>44907</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>45315</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>46203</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45265</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45939</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>46180</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>45313</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48511,7 +48511,7 @@
         <v>46073</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48584,7 +48584,7 @@
         <v>46220</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45302</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48730,7 +48730,7 @@
         <v>44799</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>45231</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48881,7 +48881,7 @@
         <v>45260</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>46272</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49027,7 +49027,7 @@
         <v>46269</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>46231</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>46231</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>46231</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         <v>46231</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45273</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>44533</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>44614</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>46275</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49714,7 +49714,7 @@
         <v>46275</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>46276</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>45588</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>46279</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>46135</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>46280</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>46279</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>44790</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>46279</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>46281</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50454,7 +50454,7 @@
         <v>46239</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>46281</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>46282</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>46238</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45475</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
         <v>46241</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45690</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>46283</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45342</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>46241</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         <v>44952</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45008</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51345,7 +51345,7 @@
         <v>46286</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51418,7 +51418,7 @@
         <v>46287</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45376</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>46288</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>46132</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         <v>44889</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51798,7 +51798,7 @@
         <v>44875</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>46286</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51944,7 +51944,7 @@
         <v>44949</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>46289</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>46248</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>45239</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52241,7 +52241,7 @@
         <v>44721</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>44511</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>45600</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52470,7 +52470,7 @@
         <v>45112</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>44937</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>44679</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52689,7 +52689,7 @@
         <v>44986</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52767,7 +52767,7 @@
         <v>44607</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>44742</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         <v>45569</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>45149</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53059,7 +53059,7 @@
         <v>45639</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>45183</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>44952</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53283,7 +53283,7 @@
         <v>44883</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53356,7 +53356,7 @@
         <v>44837</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45677</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53502,7 +53502,7 @@
         <v>45177</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53580,7 +53580,7 @@
         <v>45632</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>44889</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53726,7 +53726,7 @@
         <v>44911</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53799,7 +53799,7 @@
         <v>45593</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>45553</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53950,7 +53950,7 @@
         <v>45223</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54023,7 +54023,7 @@
         <v>45223</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54096,7 +54096,7 @@
         <v>45012</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>45004</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45236</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54315,7 +54315,7 @@
         <v>45688</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54393,7 +54393,7 @@
         <v>45588</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54471,7 +54471,7 @@
         <v>44986</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54549,7 +54549,7 @@
         <v>45708</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>44922</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54695,7 +54695,7 @@
         <v>44911</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54768,7 +54768,7 @@
         <v>45667</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>45159</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45264</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>45660</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>45779</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45686</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55211,7 +55211,7 @@
         <v>45686</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55284,7 +55284,7 @@
         <v>45686</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55357,7 +55357,7 @@
         <v>45789</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>45790</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55503,7 +55503,7 @@
         <v>45744</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55576,7 +55576,7 @@
         <v>45820</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55649,7 +55649,7 @@
         <v>46058</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55722,7 +55722,7 @@
         <v>46058</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>46276</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45109</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>45155</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44585</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>45540</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>45690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 27881-2026</t>
+          <t>A 12943-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46191</v>
+        <v>44642</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1990,23 +1990,23 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
@@ -2014,155 +2014,21 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="T11" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="U11" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Björktrast
-Harticka
-Lunglav
-Rödvingetrast
-Talltita
-Tretåig hackspett
-Ullticka
-Finbräken
-Kransrams
-Luddlav
-Spindelblomster
-Stuplav
-Svart trolldruva
-Tvåblad
-Ögonpyrola
-Bergfink
-Blåsippa
-Brudborste
-Ekbräken
-Kransmossa
-Kärrfibbla
-Nordisk stormhatt
-Ormbär
-Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 27881-2026 artfynd.xlsx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 27881-2026 karta.png", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 27881-2026 georefererad karta.tif", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 27881-2026 FSC-klagomål.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 27881-2026 FSC-klagomål mail.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 27881-2026 tillsynsbegäran.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 27881-2026 tillsynsbegäran mail.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 27881-2026 prioriterade fågelarter.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 12943-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44642</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>12</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>23</v>
-      </c>
-      <c r="T12" t="n">
-        <v>68</v>
-      </c>
-      <c r="U12" t="n">
-        <v>56</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Trolldruvemätare
 Knärot
@@ -2189,115 +2055,115 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 12943-2022 artfynd.xlsx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 12943-2022 karta.png", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 12943-2022 georefererad karta.tif", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 12943-2022 karta knärot.png", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 12943-2022 FSC-klagomål.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 12943-2022 FSC-klagomål mail.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 12943-2022 tillsynsbegäran.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 12943-2022 tillsynsbegäran mail.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 12943-2022 prioriterade fågelarter.docx", "A 12943-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 14960-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>46104</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>14.8</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J12" t="n">
         <v>8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K12" t="n">
         <v>7</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L12" t="n">
         <v>7</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M12" t="n">
         <v>2</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>9</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R12" t="n">
         <v>2</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S12" t="n">
         <v>22</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T12" t="n">
         <v>180</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U12" t="n">
         <v>164</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -2323,115 +2189,115 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 14960-2026 artfynd.xlsx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 14960-2026 karta.png", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 14960-2026 georefererad karta.tif", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 14960-2026 karta knärot.png", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 14960-2026 FSC-klagomål.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 14960-2026 FSC-klagomål mail.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 14960-2026 tillsynsbegäran.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 14960-2026 tillsynsbegäran mail.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 14960-2026 prioriterade fågelarter.docx", "A 14960-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 48059-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>45932</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>12.2</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J13" t="n">
         <v>6</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L13" t="n">
         <v>12</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M13" t="n">
         <v>2</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>14</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R13" t="n">
         <v>2</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S13" t="n">
         <v>22</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T13" t="n">
         <v>115</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U13" t="n">
         <v>115</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -2457,40 +2323,170 @@
 Tjäder</t>
         </is>
       </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 48059-2025 artfynd.xlsx", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 48059-2025 karta.png", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 48059-2025 georefererad karta.tif", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 48059-2025 karta knärot.png", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 48059-2025 FSC-klagomål.docx", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 48059-2025 FSC-klagomål mail.docx", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 48059-2025 tillsynsbegäran.docx", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 48059-2025 tillsynsbegäran mail.docx", "A 48059-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 48059-2025 prioriterade fågelarter.docx", "A 48059-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 27881-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>22</v>
+      </c>
+      <c r="T14" t="n">
+        <v>37</v>
+      </c>
+      <c r="U14" t="n">
+        <v>37</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Lunglav
+Rödvingetrast
+Talltita
+Tretåig hackspett
+Ullticka
+Finbräken
+Kransrams
+Luddlav
+Spindelblomster
+Stuplav
+Svart trolldruva
+Tvåblad
+Ögonpyrola
+Blåsippa
+Brudborste
+Ekbräken
+Kransmossa
+Kärrfibbla
+Nordisk stormhatt
+Ormbär
+Fläcknycklar</t>
+        </is>
+      </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 48059-2025 artfynd.xlsx", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 27881-2026 artfynd.xlsx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 48059-2025 karta.png", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 27881-2026 karta.png", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 48059-2025 georefererad karta.tif", "A 48059-2025")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 48059-2025 karta knärot.png", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 27881-2026 georefererad karta.tif", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 48059-2025 FSC-klagomål.docx", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 27881-2026 FSC-klagomål.docx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 48059-2025 FSC-klagomål mail.docx", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 27881-2026 FSC-klagomål mail.docx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 48059-2025 tillsynsbegäran.docx", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 27881-2026 tillsynsbegäran.docx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 48059-2025 tillsynsbegäran mail.docx", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 27881-2026 tillsynsbegäran mail.docx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 48059-2025 prioriterade fågelarter.docx", "A 48059-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 27881-2026 prioriterade fågelarter.docx", "A 27881-2026")</f>
         <v/>
       </c>
     </row>
@@ -2514,7 +2510,7 @@
         <v>46108</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2643,7 +2639,7 @@
         <v>45985</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2776,7 +2772,7 @@
         <v>45600</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2914,7 +2910,7 @@
         <v>46195</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3047,7 +3043,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3180,7 +3176,7 @@
         <v>45924</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3312,7 +3308,7 @@
         <v>46195</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3444,7 +3440,7 @@
         <v>46119</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3572,7 +3568,7 @@
         <v>46195</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3703,7 +3699,7 @@
         <v>45988</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3838,7 +3834,7 @@
         <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3964,7 +3960,7 @@
         <v>45975</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4094,7 +4090,7 @@
         <v>46129</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4219,7 +4215,7 @@
         <v>44945</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4347,7 +4343,7 @@
         <v>45747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4475,7 +4471,7 @@
         <v>44819</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4603,7 +4599,7 @@
         <v>46210</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4730,7 +4726,7 @@
         <v>44971</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4858,7 +4854,7 @@
         <v>45376</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4986,7 +4982,7 @@
         <v>45932</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5112,7 +5108,7 @@
         <v>45112</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5230,7 +5226,7 @@
         <v>45916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5356,7 +5352,7 @@
         <v>46044</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5473,7 +5469,7 @@
         <v>45978</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5593,7 +5589,7 @@
         <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5713,7 +5709,7 @@
         <v>45890</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5837,7 +5833,7 @@
         <v>46010</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5961,7 +5957,7 @@
         <v>46073</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6085,7 +6081,7 @@
         <v>45929</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6205,7 +6201,7 @@
         <v>45932</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6328,7 +6324,7 @@
         <v>46140</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6443,7 +6439,7 @@
         <v>46213</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6566,7 +6562,7 @@
         <v>44851</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6688,7 +6684,7 @@
         <v>45415</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6810,7 +6806,7 @@
         <v>45621</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6928,7 +6924,7 @@
         <v>45063</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7046,7 +7042,7 @@
         <v>46044</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7160,7 +7156,7 @@
         <v>45575</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7278,7 +7274,7 @@
         <v>46195</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7400,7 +7396,7 @@
         <v>45475</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7523,7 +7519,7 @@
         <v>45937</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7645,7 +7641,7 @@
         <v>46042</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7763,7 +7759,7 @@
         <v>45574</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7882,7 +7878,7 @@
         <v>45602</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8009,7 +8005,7 @@
         <v>45526</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8128,7 +8124,7 @@
         <v>45986</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8246,7 +8242,7 @@
         <v>45649</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8363,7 +8359,7 @@
         <v>46133</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8481,7 +8477,7 @@
         <v>45937</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8602,7 +8598,7 @@
         <v>45470</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8723,7 +8719,7 @@
         <v>45940</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8844,7 +8840,7 @@
         <v>45952</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8965,7 +8961,7 @@
         <v>44637</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9078,7 +9074,7 @@
         <v>45349</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9199,7 +9195,7 @@
         <v>45897</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9316,7 +9312,7 @@
         <v>46076</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9436,7 +9432,7 @@
         <v>46119</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9556,7 +9552,7 @@
         <v>46119</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9672,7 +9668,7 @@
         <v>45170</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9793,7 +9789,7 @@
         <v>45161</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9913,7 +9909,7 @@
         <v>44911</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10029,7 +10025,7 @@
         <v>45189</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10140,7 +10136,7 @@
         <v>46073</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10259,7 +10255,7 @@
         <v>46073</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10378,7 +10374,7 @@
         <v>46119</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10497,7 +10493,7 @@
         <v>44945</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10617,7 +10613,7 @@
         <v>46010</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10736,7 +10732,7 @@
         <v>46043</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10851,7 +10847,7 @@
         <v>46105</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10966,7 +10962,7 @@
         <v>45890</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11081,7 +11077,7 @@
         <v>45936</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11200,7 +11196,7 @@
         <v>45806</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11319,7 +11315,7 @@
         <v>45953</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11438,7 +11434,7 @@
         <v>45975</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11553,7 +11549,7 @@
         <v>45028</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11673,7 +11669,7 @@
         <v>45751</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11789,7 +11785,7 @@
         <v>44929</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11903,7 +11899,7 @@
         <v>45809</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12017,7 +12013,7 @@
         <v>46097</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12127,7 +12123,7 @@
         <v>46065</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12241,7 +12237,7 @@
         <v>46006</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12360,7 +12356,7 @@
         <v>45762</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12475,7 +12471,7 @@
         <v>45618</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12594,7 +12590,7 @@
         <v>46195</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12704,7 +12700,7 @@
         <v>46008</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12818,7 +12814,7 @@
         <v>45553</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12928,7 +12924,7 @@
         <v>45233</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13043,7 +13039,7 @@
         <v>44840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13153,7 +13149,7 @@
         <v>46059</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13271,7 +13267,7 @@
         <v>44623</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13380,7 +13376,7 @@
         <v>44742</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13494,7 +13490,7 @@
         <v>45278</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13603,7 +13599,7 @@
         <v>45349</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13717,7 +13713,7 @@
         <v>45901</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13835,7 +13831,7 @@
         <v>45975</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13948,7 +13944,7 @@
         <v>45897</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14062,7 +14058,7 @@
         <v>45985</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14175,7 +14171,7 @@
         <v>46000</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14292,7 +14288,7 @@
         <v>46030</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14405,7 +14401,7 @@
         <v>45349</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14523,7 +14519,7 @@
         <v>45049</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14632,7 +14628,7 @@
         <v>44908</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14740,7 +14736,7 @@
         <v>45570</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14848,7 +14844,7 @@
         <v>45721</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14961,7 +14957,7 @@
         <v>45320</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15069,7 +15065,7 @@
         <v>45237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15186,7 +15182,7 @@
         <v>45748</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15294,7 +15290,7 @@
         <v>45462</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15402,7 +15398,7 @@
         <v>45978</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15514,7 +15510,7 @@
         <v>44853</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15626,7 +15622,7 @@
         <v>46098</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15734,7 +15730,7 @@
         <v>46160</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15850,7 +15846,7 @@
         <v>44750</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15958,7 +15954,7 @@
         <v>44904</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16066,7 +16062,7 @@
         <v>46279</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16179,7 +16175,7 @@
         <v>44977</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16292,7 +16288,7 @@
         <v>45785</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16405,7 +16401,7 @@
         <v>46280</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16513,7 +16509,7 @@
         <v>45223</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16625,7 +16621,7 @@
         <v>44904</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16736,7 +16732,7 @@
         <v>45559</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16848,7 +16844,7 @@
         <v>45644</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16959,7 +16955,7 @@
         <v>45919</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17071,7 +17067,7 @@
         <v>45615</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17178,7 +17174,7 @@
         <v>46137</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17285,7 +17281,7 @@
         <v>45245</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17397,7 +17393,7 @@
         <v>45198</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17509,7 +17505,7 @@
         <v>46177</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17616,7 +17612,7 @@
         <v>45187</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17732,7 +17728,7 @@
         <v>45233</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17839,7 +17835,7 @@
         <v>46225</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17955,7 +17951,7 @@
         <v>46275</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18067,7 +18063,7 @@
         <v>44956</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18174,7 +18170,7 @@
         <v>45561</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18286,7 +18282,7 @@
         <v>46155</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18393,7 +18389,7 @@
         <v>46288</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18509,7 +18505,7 @@
         <v>44904</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18620,7 +18616,7 @@
         <v>44904</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18727,7 +18723,7 @@
         <v>45737</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18842,7 +18838,7 @@
         <v>45412</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18949,7 +18945,7 @@
         <v>44544</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19059,7 +19055,7 @@
         <v>45975</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19165,7 +19161,7 @@
         <v>45558</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19276,7 +19272,7 @@
         <v>45553</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19386,7 +19382,7 @@
         <v>44617</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19497,7 +19493,7 @@
         <v>44927</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19607,7 +19603,7 @@
         <v>45538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19713,7 +19709,7 @@
         <v>44643</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19819,7 +19815,7 @@
         <v>45987</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19925,7 +19921,7 @@
         <v>45643</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20036,7 +20032,7 @@
         <v>45441</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20151,7 +20147,7 @@
         <v>45715</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20257,7 +20253,7 @@
         <v>45952</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20363,7 +20359,7 @@
         <v>44476</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20473,7 +20469,7 @@
         <v>45533</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20579,7 +20575,7 @@
         <v>46198</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20685,7 +20681,7 @@
         <v>44916</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20791,7 +20787,7 @@
         <v>45321</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20897,7 +20893,7 @@
         <v>44957</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21003,7 +20999,7 @@
         <v>46282</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21109,7 +21105,7 @@
         <v>44956</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21215,7 +21211,7 @@
         <v>45751</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21321,7 +21317,7 @@
         <v>44694</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21431,7 +21427,7 @@
         <v>44515</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21541,7 +21537,7 @@
         <v>44742</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21655,7 +21651,7 @@
         <v>45313</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21765,7 +21761,7 @@
         <v>44594</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21870,7 +21866,7 @@
         <v>45223</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21980,7 +21976,7 @@
         <v>44742</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22090,7 +22086,7 @@
         <v>45558</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22200,7 +22196,7 @@
         <v>45797</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22305,7 +22301,7 @@
         <v>44900</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22410,7 +22406,7 @@
         <v>45646</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22524,7 +22520,7 @@
         <v>45629</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22638,7 +22634,7 @@
         <v>46051</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22743,7 +22739,7 @@
         <v>45096</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22848,7 +22844,7 @@
         <v>45719</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22958,7 +22954,7 @@
         <v>45509</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23068,7 +23064,7 @@
         <v>45763</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23173,7 +23169,7 @@
         <v>45678</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23278,7 +23274,7 @@
         <v>45238</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23388,7 +23384,7 @@
         <v>45624</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23498,7 +23494,7 @@
         <v>46120</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23603,7 +23599,7 @@
         <v>45968</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23713,7 +23709,7 @@
         <v>45637</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23827,7 +23823,7 @@
         <v>46125</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23932,7 +23928,7 @@
         <v>45999</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24042,7 +24038,7 @@
         <v>45511</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24147,7 +24143,7 @@
         <v>45685</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24252,7 +24248,7 @@
         <v>45559</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24362,7 +24358,7 @@
         <v>46038</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24467,7 +24463,7 @@
         <v>45280</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24572,7 +24568,7 @@
         <v>46142</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24682,7 +24678,7 @@
         <v>45841</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24787,7 +24783,7 @@
         <v>44491</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24897,7 +24893,7 @@
         <v>45867</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25007,7 +25003,7 @@
         <v>45867</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25117,7 +25113,7 @@
         <v>45617</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25226,7 +25222,7 @@
         <v>46184</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25331,7 +25327,7 @@
         <v>46190</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25436,7 +25432,7 @@
         <v>45118</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25541,7 +25537,7 @@
         <v>46217</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25651,7 +25647,7 @@
         <v>44642</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25761,7 +25757,7 @@
         <v>45679</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25871,7 +25867,7 @@
         <v>45028</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25976,7 +25972,7 @@
         <v>46276</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26081,7 +26077,7 @@
         <v>44785</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26190,7 +26186,7 @@
         <v>44928</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26299,7 +26295,7 @@
         <v>45957</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26413,7 +26409,7 @@
         <v>44879</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26486,7 +26482,7 @@
         <v>44510</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26559,7 +26555,7 @@
         <v>44524</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26637,7 +26633,7 @@
         <v>44838</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26715,7 +26711,7 @@
         <v>44540</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26788,7 +26784,7 @@
         <v>44613</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26861,7 +26857,7 @@
         <v>44581</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26934,7 +26930,7 @@
         <v>44852</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27007,7 +27003,7 @@
         <v>44561</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27080,7 +27076,7 @@
         <v>44566</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27153,7 +27149,7 @@
         <v>44755</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27231,7 +27227,7 @@
         <v>44852</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27304,7 +27300,7 @@
         <v>44540</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27377,7 +27373,7 @@
         <v>44537</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27450,7 +27446,7 @@
         <v>44609</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27523,7 +27519,7 @@
         <v>44889</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27596,7 +27592,7 @@
         <v>44516</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27669,7 +27665,7 @@
         <v>44875</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27747,7 +27743,7 @@
         <v>44886</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27845,7 +27841,7 @@
         <v>44750</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27918,7 +27914,7 @@
         <v>44517</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27991,7 +27987,7 @@
         <v>44601</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28064,7 +28060,7 @@
         <v>44722</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28142,7 +28138,7 @@
         <v>44722</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28220,7 +28216,7 @@
         <v>44721</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28293,7 +28289,7 @@
         <v>44845</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28366,7 +28362,7 @@
         <v>44540</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28439,7 +28435,7 @@
         <v>44655</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28512,7 +28508,7 @@
         <v>44704</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28590,7 +28586,7 @@
         <v>45621</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28668,7 +28664,7 @@
         <v>44757</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28741,7 +28737,7 @@
         <v>45412</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28814,7 +28810,7 @@
         <v>45338</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28887,7 +28883,7 @@
         <v>45324</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28965,7 +28961,7 @@
         <v>45370</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29038,7 +29034,7 @@
         <v>45315</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29111,7 +29107,7 @@
         <v>45462</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29189,7 +29185,7 @@
         <v>45702</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29262,7 +29258,7 @@
         <v>46014</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29335,7 +29331,7 @@
         <v>46019</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29408,7 +29404,7 @@
         <v>45561</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29486,7 +29482,7 @@
         <v>46024</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29559,7 +29555,7 @@
         <v>45309</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29632,7 +29628,7 @@
         <v>46029</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29705,7 +29701,7 @@
         <v>45435</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29778,7 +29774,7 @@
         <v>45793</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29851,7 +29847,7 @@
         <v>45477</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29924,7 +29920,7 @@
         <v>45012</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29997,7 +29993,7 @@
         <v>45475</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30075,7 +30071,7 @@
         <v>45611</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30148,7 +30144,7 @@
         <v>45002</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30226,7 +30222,7 @@
         <v>46034</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30299,7 +30295,7 @@
         <v>45625</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30372,7 +30368,7 @@
         <v>45799</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30445,7 +30441,7 @@
         <v>45888</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30518,7 +30514,7 @@
         <v>46032</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30591,7 +30587,7 @@
         <v>45800</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30664,7 +30660,7 @@
         <v>45707</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30737,7 +30733,7 @@
         <v>46038</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30810,7 +30806,7 @@
         <v>45748</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30883,7 +30879,7 @@
         <v>46037</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30956,7 +30952,7 @@
         <v>46037</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31029,7 +31025,7 @@
         <v>46041</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31102,7 +31098,7 @@
         <v>45895</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31175,7 +31171,7 @@
         <v>44911</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31248,7 +31244,7 @@
         <v>45895</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31321,7 +31317,7 @@
         <v>45902</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31394,7 +31390,7 @@
         <v>45902</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31467,7 +31463,7 @@
         <v>46045</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31545,7 +31541,7 @@
         <v>46045</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31618,7 +31614,7 @@
         <v>45901</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31691,7 +31687,7 @@
         <v>46050</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31764,7 +31760,7 @@
         <v>45646</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31842,7 +31838,7 @@
         <v>45646</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31920,7 +31916,7 @@
         <v>45904</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31993,7 +31989,7 @@
         <v>45909</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32066,7 +32062,7 @@
         <v>45477</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32139,7 +32135,7 @@
         <v>44475</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32212,7 +32208,7 @@
         <v>45300</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32285,7 +32281,7 @@
         <v>45911</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32358,7 +32354,7 @@
         <v>46056</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32431,7 +32427,7 @@
         <v>45803</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32509,7 +32505,7 @@
         <v>45916</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32582,7 +32578,7 @@
         <v>44599</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32655,7 +32651,7 @@
         <v>45922</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32733,7 +32729,7 @@
         <v>45922</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32811,7 +32807,7 @@
         <v>45922</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32889,7 +32885,7 @@
         <v>45922</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32967,7 +32963,7 @@
         <v>45922</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33045,7 +33041,7 @@
         <v>45922</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33118,7 +33114,7 @@
         <v>46066</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33196,7 +33192,7 @@
         <v>46066</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33274,7 +33270,7 @@
         <v>46070</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33352,7 +33348,7 @@
         <v>45924</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33430,7 +33426,7 @@
         <v>45924</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33508,7 +33504,7 @@
         <v>45805</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33586,7 +33582,7 @@
         <v>45587</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33659,7 +33655,7 @@
         <v>46076</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33737,7 +33733,7 @@
         <v>46073</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33810,7 +33806,7 @@
         <v>45636</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33883,7 +33879,7 @@
         <v>46078</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33956,7 +33952,7 @@
         <v>46078</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34029,7 +34025,7 @@
         <v>45722</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34107,7 +34103,7 @@
         <v>45736</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34180,7 +34176,7 @@
         <v>45789</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34253,7 +34249,7 @@
         <v>45743</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34326,7 +34322,7 @@
         <v>45720</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34404,7 +34400,7 @@
         <v>45720</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34482,7 +34478,7 @@
         <v>45743</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34555,7 +34551,7 @@
         <v>45588</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34628,7 +34624,7 @@
         <v>45978</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34701,7 +34697,7 @@
         <v>45691</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34779,7 +34775,7 @@
         <v>45551</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34857,7 +34853,7 @@
         <v>45634</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34930,7 +34926,7 @@
         <v>45807</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35003,7 +34999,7 @@
         <v>45583</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35076,7 +35072,7 @@
         <v>45576</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35149,7 +35145,7 @@
         <v>45580</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35222,7 +35218,7 @@
         <v>44680</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35295,7 +35291,7 @@
         <v>46091</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35368,7 +35364,7 @@
         <v>45236</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35446,7 +35442,7 @@
         <v>45937</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35524,7 +35520,7 @@
         <v>45344</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35597,7 +35593,7 @@
         <v>44977</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35675,7 +35671,7 @@
         <v>45221</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35748,7 +35744,7 @@
         <v>45944</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35826,7 +35822,7 @@
         <v>45237</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35899,7 +35895,7 @@
         <v>46098</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35972,7 +35968,7 @@
         <v>44655</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36045,7 +36041,7 @@
         <v>45260</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36118,7 +36114,7 @@
         <v>45707</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36191,7 +36187,7 @@
         <v>44634</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36264,7 +36260,7 @@
         <v>45547</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36337,7 +36333,7 @@
         <v>45057</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36410,7 +36406,7 @@
         <v>45954</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36483,7 +36479,7 @@
         <v>44735</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36556,7 +36552,7 @@
         <v>46097</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36634,7 +36630,7 @@
         <v>45688</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36707,7 +36703,7 @@
         <v>45958</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36785,7 +36781,7 @@
         <v>45964</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36863,7 +36859,7 @@
         <v>46125</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36936,7 +36932,7 @@
         <v>46114</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37009,7 +37005,7 @@
         <v>45813</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37082,7 +37078,7 @@
         <v>45600</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37160,7 +37156,7 @@
         <v>46126</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37238,7 +37234,7 @@
         <v>45460</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37311,7 +37307,7 @@
         <v>46132</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37384,7 +37380,7 @@
         <v>46133</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37462,7 +37458,7 @@
         <v>45818</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37540,7 +37536,7 @@
         <v>44750</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37613,7 +37609,7 @@
         <v>45985</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37686,7 +37682,7 @@
         <v>45986</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37759,7 +37755,7 @@
         <v>45985</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37832,7 +37828,7 @@
         <v>45692</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37905,7 +37901,7 @@
         <v>46135</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37978,7 +37974,7 @@
         <v>45992</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38051,7 +38047,7 @@
         <v>45987</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38124,7 +38120,7 @@
         <v>45992</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38197,7 +38193,7 @@
         <v>45992</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38270,7 +38266,7 @@
         <v>45667</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38348,7 +38344,7 @@
         <v>46136</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38426,7 +38422,7 @@
         <v>44466</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38499,7 +38495,7 @@
         <v>46139</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38577,7 +38573,7 @@
         <v>45696</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38650,7 +38646,7 @@
         <v>45993</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38723,7 +38719,7 @@
         <v>46000</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38796,7 +38792,7 @@
         <v>46000</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38869,7 +38865,7 @@
         <v>45198</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38947,7 +38943,7 @@
         <v>45691</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39020,7 +39016,7 @@
         <v>44970</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39098,7 +39094,7 @@
         <v>46003</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39171,7 +39167,7 @@
         <v>46003</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39244,7 +39240,7 @@
         <v>46139</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39322,7 +39318,7 @@
         <v>45819</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39400,7 +39396,7 @@
         <v>46003</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39473,7 +39469,7 @@
         <v>46139</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39551,7 +39547,7 @@
         <v>46003</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39624,7 +39620,7 @@
         <v>46003</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39697,7 +39693,7 @@
         <v>46008</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39770,7 +39766,7 @@
         <v>45707</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39848,7 +39844,7 @@
         <v>45837</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39926,7 +39922,7 @@
         <v>46007</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40004,7 +40000,7 @@
         <v>46007</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40077,7 +40073,7 @@
         <v>45770</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40150,7 +40146,7 @@
         <v>46010</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40223,7 +40219,7 @@
         <v>44711</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40296,7 +40292,7 @@
         <v>45520</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40369,7 +40365,7 @@
         <v>46010</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40442,7 +40438,7 @@
         <v>45223</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40515,7 +40511,7 @@
         <v>46029</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40588,7 +40584,7 @@
         <v>46013</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40661,7 +40657,7 @@
         <v>46013</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40734,7 +40730,7 @@
         <v>45707</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40807,7 +40803,7 @@
         <v>45505</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40885,7 +40881,7 @@
         <v>46000</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40958,7 +40954,7 @@
         <v>45586</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41036,7 +41032,7 @@
         <v>44922</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41109,7 +41105,7 @@
         <v>44790</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41182,7 +41178,7 @@
         <v>46142</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41260,7 +41256,7 @@
         <v>44909</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41338,7 +41334,7 @@
         <v>45057</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41416,7 +41412,7 @@
         <v>46150</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41489,7 +41485,7 @@
         <v>46150</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41562,7 +41558,7 @@
         <v>46150</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41635,7 +41631,7 @@
         <v>45691</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41708,7 +41704,7 @@
         <v>46153</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41781,7 +41777,7 @@
         <v>45693</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41854,7 +41850,7 @@
         <v>45096</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41927,7 +41923,7 @@
         <v>44880</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42000,7 +41996,7 @@
         <v>46154</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42078,7 +42074,7 @@
         <v>46156</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42156,7 +42152,7 @@
         <v>45261</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42234,7 +42230,7 @@
         <v>45686</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42307,7 +42303,7 @@
         <v>45887</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42380,7 +42376,7 @@
         <v>46120</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42453,7 +42449,7 @@
         <v>46164</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42531,7 +42527,7 @@
         <v>46066</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42604,7 +42600,7 @@
         <v>46163</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42677,7 +42673,7 @@
         <v>45089</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42750,7 +42746,7 @@
         <v>46163</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42823,7 +42819,7 @@
         <v>46164</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42901,7 +42897,7 @@
         <v>46164</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42974,7 +42970,7 @@
         <v>46164</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43052,7 +43048,7 @@
         <v>46164</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43130,7 +43126,7 @@
         <v>45336</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43203,7 +43199,7 @@
         <v>46164</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43281,7 +43277,7 @@
         <v>46164</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43359,7 +43355,7 @@
         <v>46164</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43437,7 +43433,7 @@
         <v>46164</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43515,7 +43511,7 @@
         <v>46164</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43588,7 +43584,7 @@
         <v>46163</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43661,7 +43657,7 @@
         <v>45847</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43739,7 +43735,7 @@
         <v>45847</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43817,7 +43813,7 @@
         <v>45847</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43895,7 +43891,7 @@
         <v>45344</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43968,7 +43964,7 @@
         <v>45593</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44046,7 +44042,7 @@
         <v>46206</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44119,7 +44115,7 @@
         <v>45800</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44192,7 +44188,7 @@
         <v>45096</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44265,7 +44261,7 @@
         <v>45166</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44343,7 +44339,7 @@
         <v>45866</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44421,7 +44417,7 @@
         <v>46175</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44499,7 +44495,7 @@
         <v>45807</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44572,7 +44568,7 @@
         <v>45092</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44645,7 +44641,7 @@
         <v>45457</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44718,7 +44714,7 @@
         <v>45306</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44791,7 +44787,7 @@
         <v>46183</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44864,7 +44860,7 @@
         <v>45616</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44942,7 +44938,7 @@
         <v>46184</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45015,7 +45011,7 @@
         <v>44529</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45088,7 +45084,7 @@
         <v>45328</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45161,7 +45157,7 @@
         <v>46188</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45234,7 +45230,7 @@
         <v>46190</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45307,7 +45303,7 @@
         <v>46190</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45380,7 +45376,7 @@
         <v>46190</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45453,7 +45449,7 @@
         <v>45763</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45526,7 +45522,7 @@
         <v>44609</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45599,7 +45595,7 @@
         <v>45428</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45677,7 +45673,7 @@
         <v>45628</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45750,7 +45746,7 @@
         <v>45190</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45823,7 +45819,7 @@
         <v>45597</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45901,7 +45897,7 @@
         <v>45634</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45974,7 +45970,7 @@
         <v>46203</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46047,7 +46043,7 @@
         <v>44564</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46120,7 +46116,7 @@
         <v>45681</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46198,7 +46194,7 @@
         <v>45681</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46276,7 +46272,7 @@
         <v>45691</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46354,7 +46350,7 @@
         <v>45107</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46427,7 +46423,7 @@
         <v>46206</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46500,7 +46496,7 @@
         <v>46206</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46573,7 +46569,7 @@
         <v>45762</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46651,7 +46647,7 @@
         <v>45221</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46724,7 +46720,7 @@
         <v>44635</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46797,7 +46793,7 @@
         <v>45189</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46870,7 +46866,7 @@
         <v>45615</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46943,7 +46939,7 @@
         <v>45429</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47016,7 +47012,7 @@
         <v>44706</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47089,7 +47085,7 @@
         <v>45709</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47167,7 +47163,7 @@
         <v>45572</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47245,7 +47241,7 @@
         <v>45231</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47323,7 +47319,7 @@
         <v>46216</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47401,7 +47397,7 @@
         <v>45707</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47474,7 +47470,7 @@
         <v>45659</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47547,7 +47543,7 @@
         <v>45677</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47620,7 +47616,7 @@
         <v>45188</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47693,7 +47689,7 @@
         <v>44743</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47766,7 +47762,7 @@
         <v>44721</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47839,7 +47835,7 @@
         <v>45721</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47912,7 +47908,7 @@
         <v>45321</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47985,7 +47981,7 @@
         <v>44907</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48063,7 +48059,7 @@
         <v>45315</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48136,7 +48132,7 @@
         <v>46203</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48209,7 +48205,7 @@
         <v>45265</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48287,7 +48283,7 @@
         <v>45939</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48365,7 +48361,7 @@
         <v>46180</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48438,7 +48434,7 @@
         <v>45313</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48511,7 +48507,7 @@
         <v>46073</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48584,7 +48580,7 @@
         <v>46220</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48657,7 +48653,7 @@
         <v>45302</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48730,7 +48726,7 @@
         <v>44799</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48803,7 +48799,7 @@
         <v>45231</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48881,7 +48877,7 @@
         <v>45260</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48954,7 +48950,7 @@
         <v>46272</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49027,7 +49023,7 @@
         <v>46269</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49105,7 +49101,7 @@
         <v>46231</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49183,7 +49179,7 @@
         <v>46231</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49261,7 +49257,7 @@
         <v>46231</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49339,7 +49335,7 @@
         <v>46231</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49417,7 +49413,7 @@
         <v>45273</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49490,7 +49486,7 @@
         <v>44533</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49563,7 +49559,7 @@
         <v>44614</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49636,7 +49632,7 @@
         <v>46275</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49714,7 +49710,7 @@
         <v>46275</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49787,7 +49783,7 @@
         <v>46276</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49865,7 +49861,7 @@
         <v>45588</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49938,7 +49934,7 @@
         <v>46279</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50011,7 +50007,7 @@
         <v>46135</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50084,7 +50080,7 @@
         <v>46280</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50162,7 +50158,7 @@
         <v>46279</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50235,7 +50231,7 @@
         <v>44790</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50308,7 +50304,7 @@
         <v>46279</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50381,7 +50377,7 @@
         <v>46281</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50454,7 +50450,7 @@
         <v>46239</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50527,7 +50523,7 @@
         <v>46281</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50600,7 +50596,7 @@
         <v>46282</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50678,7 +50674,7 @@
         <v>46238</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50751,7 +50747,7 @@
         <v>45475</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50824,7 +50820,7 @@
         <v>46241</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50897,7 +50893,7 @@
         <v>45690</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50970,7 +50966,7 @@
         <v>46283</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51048,7 +51044,7 @@
         <v>45342</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51126,7 +51122,7 @@
         <v>46241</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51199,7 +51195,7 @@
         <v>44952</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51272,7 +51268,7 @@
         <v>45008</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51345,7 +51341,7 @@
         <v>46286</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51418,7 +51414,7 @@
         <v>46287</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51496,7 +51492,7 @@
         <v>45376</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51569,7 +51565,7 @@
         <v>46288</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51647,7 +51643,7 @@
         <v>46132</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51720,7 +51716,7 @@
         <v>44889</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51798,7 +51794,7 @@
         <v>44875</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51871,7 +51867,7 @@
         <v>46286</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51944,7 +51940,7 @@
         <v>44949</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52017,7 +52013,7 @@
         <v>46289</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52090,7 +52086,7 @@
         <v>46248</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52163,7 +52159,7 @@
         <v>45239</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52241,7 +52237,7 @@
         <v>44721</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52319,7 +52315,7 @@
         <v>44511</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52392,7 +52388,7 @@
         <v>45600</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52470,7 +52466,7 @@
         <v>45112</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52543,7 +52539,7 @@
         <v>44937</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52616,7 +52612,7 @@
         <v>44679</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52689,7 +52685,7 @@
         <v>44986</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52767,7 +52763,7 @@
         <v>44607</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52840,7 +52836,7 @@
         <v>44742</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52913,7 +52909,7 @@
         <v>45569</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52986,7 +52982,7 @@
         <v>45149</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53059,7 +53055,7 @@
         <v>45639</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53137,7 +53133,7 @@
         <v>45183</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53210,7 +53206,7 @@
         <v>44952</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53283,7 +53279,7 @@
         <v>44883</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53356,7 +53352,7 @@
         <v>44837</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53429,7 +53425,7 @@
         <v>45677</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53502,7 +53498,7 @@
         <v>45177</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53580,7 +53576,7 @@
         <v>45632</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53653,7 +53649,7 @@
         <v>44889</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53726,7 +53722,7 @@
         <v>44911</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53799,7 +53795,7 @@
         <v>45593</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53877,7 +53873,7 @@
         <v>45553</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53950,7 +53946,7 @@
         <v>45223</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54023,7 +54019,7 @@
         <v>45223</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54096,7 +54092,7 @@
         <v>45012</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54169,7 +54165,7 @@
         <v>45004</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54242,7 +54238,7 @@
         <v>45236</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54315,7 +54311,7 @@
         <v>45688</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54393,7 +54389,7 @@
         <v>45588</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54471,7 +54467,7 @@
         <v>44986</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54549,7 +54545,7 @@
         <v>45708</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54622,7 +54618,7 @@
         <v>44922</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54695,7 +54691,7 @@
         <v>44911</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54768,7 +54764,7 @@
         <v>45667</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54846,7 +54842,7 @@
         <v>45159</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54919,7 +54915,7 @@
         <v>45264</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54992,7 +54988,7 @@
         <v>45660</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55065,7 +55061,7 @@
         <v>45779</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55138,7 +55134,7 @@
         <v>45686</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55211,7 +55207,7 @@
         <v>45686</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55284,7 +55280,7 @@
         <v>45686</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55357,7 +55353,7 @@
         <v>45789</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55430,7 +55426,7 @@
         <v>45790</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55503,7 +55499,7 @@
         <v>45744</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55576,7 +55572,7 @@
         <v>45820</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55649,7 +55645,7 @@
         <v>46058</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55722,7 +55718,7 @@
         <v>46058</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55795,7 +55791,7 @@
         <v>46276</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45109</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>45155</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44585</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>45540</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>45690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1963,75 +1963,209 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
+          <t>A 27881-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>26</v>
+      </c>
+      <c r="T11" t="n">
+        <v>42</v>
+      </c>
+      <c r="U11" t="n">
+        <v>42</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Björktrast
+Harticka
+Lunglav
+Rödvingetrast
+Talltita
+Tretåig hackspett
+Ullticka
+Finbräken
+Kransrams
+Luddlav
+Spindelblomster
+Stuplav
+Svart trolldruva
+Tvåblad
+Ögonpyrola
+Bergfink
+Blåsippa
+Brudborste
+Ekbräken
+Kransmossa
+Kärrfibbla
+Nordisk stormhatt
+Ormbär
+Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 27881-2026 artfynd.xlsx", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 27881-2026 karta.png", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 27881-2026 georefererad karta.tif", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 27881-2026 FSC-klagomål.docx", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 27881-2026 FSC-klagomål mail.docx", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 27881-2026 tillsynsbegäran.docx", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 27881-2026 tillsynsbegäran mail.docx", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 27881-2026 prioriterade fågelarter.docx", "A 27881-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>A 12943-2022</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>44642</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>10</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>7</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
         <v>9</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>9</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>2</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>12</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>3</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S12" t="n">
         <v>23</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>68</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>56</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Trolldruvemätare
 Knärot
@@ -2058,115 +2192,115 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 12943-2022 artfynd.xlsx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 12943-2022 karta.png", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 12943-2022 georefererad karta.tif", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 12943-2022 karta knärot.png", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 12943-2022 FSC-klagomål.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 12943-2022 FSC-klagomål mail.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 12943-2022 tillsynsbegäran.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 12943-2022 tillsynsbegäran mail.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 12943-2022 prioriterade fågelarter.docx", "A 12943-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 14960-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46104</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>14.8</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>8</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>7</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>7</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M13" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>9</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>2</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S13" t="n">
         <v>22</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>180</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>164</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -2192,115 +2326,115 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 14960-2026 artfynd.xlsx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 14960-2026 karta.png", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 14960-2026 georefererad karta.tif", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 14960-2026 karta knärot.png", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 14960-2026 FSC-klagomål.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 14960-2026 FSC-klagomål mail.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 14960-2026 tillsynsbegäran.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 14960-2026 tillsynsbegäran mail.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 14960-2026 prioriterade fågelarter.docx", "A 14960-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 48059-2025</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>45932</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>12.2</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>6</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>5</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>12</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M14" t="n">
         <v>2</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>14</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S14" t="n">
         <v>22</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>115</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>115</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -2326,170 +2460,40 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 48059-2025 artfynd.xlsx", "A 48059-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 48059-2025 karta.png", "A 48059-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 48059-2025 georefererad karta.tif", "A 48059-2025")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 48059-2025 karta knärot.png", "A 48059-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 48059-2025 FSC-klagomål.docx", "A 48059-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 48059-2025 FSC-klagomål mail.docx", "A 48059-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 48059-2025 tillsynsbegäran.docx", "A 48059-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 48059-2025 tillsynsbegäran mail.docx", "A 48059-2025")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 48059-2025 prioriterade fågelarter.docx", "A 48059-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 27881-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>7</v>
-      </c>
-      <c r="K14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" t="n">
-        <v>5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>22</v>
-      </c>
-      <c r="T14" t="n">
-        <v>37</v>
-      </c>
-      <c r="U14" t="n">
-        <v>37</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Lunglav
-Rödvingetrast
-Talltita
-Tretåig hackspett
-Ullticka
-Finbräken
-Kransrams
-Luddlav
-Spindelblomster
-Stuplav
-Svart trolldruva
-Tvåblad
-Ögonpyrola
-Blåsippa
-Brudborste
-Ekbräken
-Kransmossa
-Kärrfibbla
-Nordisk stormhatt
-Ormbär
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 27881-2026 artfynd.xlsx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 27881-2026 karta.png", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 27881-2026 georefererad karta.tif", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 27881-2026 FSC-klagomål.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 27881-2026 FSC-klagomål mail.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 27881-2026 tillsynsbegäran.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 27881-2026 tillsynsbegäran mail.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 27881-2026 prioriterade fågelarter.docx", "A 27881-2026")</f>
         <v/>
       </c>
     </row>
@@ -2513,7 +2517,7 @@
         <v>46108</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2642,7 +2646,7 @@
         <v>45985</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2775,7 +2779,7 @@
         <v>45600</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2913,7 +2917,7 @@
         <v>46195</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3046,7 +3050,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3179,7 +3183,7 @@
         <v>46195</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3311,7 +3315,7 @@
         <v>45924</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3443,7 +3447,7 @@
         <v>46119</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3571,7 +3575,7 @@
         <v>46195</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3702,7 +3706,7 @@
         <v>45988</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3837,7 +3841,7 @@
         <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3963,7 +3967,7 @@
         <v>45975</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4093,7 +4097,7 @@
         <v>46129</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4218,7 +4222,7 @@
         <v>45747</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4346,7 +4350,7 @@
         <v>44945</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4474,7 +4478,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4603,7 +4607,7 @@
         <v>44971</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4731,7 +4735,7 @@
         <v>46119</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4858,7 +4862,7 @@
         <v>44819</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4986,7 +4990,7 @@
         <v>46210</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5113,7 +5117,7 @@
         <v>45932</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5239,7 +5243,7 @@
         <v>45112</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5357,7 +5361,7 @@
         <v>45916</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5483,7 +5487,7 @@
         <v>46044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5600,7 +5604,7 @@
         <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5720,7 +5724,7 @@
         <v>45978</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5840,7 +5844,7 @@
         <v>46073</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5964,7 +5968,7 @@
         <v>46010</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6088,7 +6092,7 @@
         <v>45890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6212,7 +6216,7 @@
         <v>45929</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6332,7 +6336,7 @@
         <v>46119</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6455,7 +6459,7 @@
         <v>45932</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6578,7 +6582,7 @@
         <v>46140</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6693,7 +6697,7 @@
         <v>46213</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6816,7 +6820,7 @@
         <v>45602</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6943,7 +6947,7 @@
         <v>45063</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7061,7 +7065,7 @@
         <v>45475</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7184,7 +7188,7 @@
         <v>46044</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7298,7 +7302,7 @@
         <v>45621</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7416,7 +7420,7 @@
         <v>45415</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7538,7 +7542,7 @@
         <v>45575</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7656,7 +7660,7 @@
         <v>45574</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7775,7 +7779,7 @@
         <v>46195</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7897,7 +7901,7 @@
         <v>45937</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8019,7 +8023,7 @@
         <v>44851</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8141,7 +8145,7 @@
         <v>46042</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8259,7 +8263,7 @@
         <v>45526</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8378,7 +8382,7 @@
         <v>45986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8496,7 +8500,7 @@
         <v>45649</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8613,7 +8617,7 @@
         <v>46133</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8731,7 +8735,7 @@
         <v>45470</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8852,7 +8856,7 @@
         <v>45940</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8973,7 +8977,7 @@
         <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9094,7 +9098,7 @@
         <v>44637</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9207,7 +9211,7 @@
         <v>45952</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9328,7 +9332,7 @@
         <v>45320</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9440,7 +9444,7 @@
         <v>45897</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9557,7 +9561,7 @@
         <v>46076</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9677,7 +9681,7 @@
         <v>46119</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9793,7 +9797,7 @@
         <v>45170</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9914,7 +9918,7 @@
         <v>45349</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10035,7 +10039,7 @@
         <v>45161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10155,7 +10159,7 @@
         <v>44911</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10271,7 +10275,7 @@
         <v>44945</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10391,7 +10395,7 @@
         <v>45189</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10502,7 +10506,7 @@
         <v>46073</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10621,7 +10625,7 @@
         <v>46073</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10740,7 +10744,7 @@
         <v>45198</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10856,7 +10860,7 @@
         <v>46010</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10975,7 +10979,7 @@
         <v>45936</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11094,7 +11098,7 @@
         <v>46043</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11209,7 +11213,7 @@
         <v>46105</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11324,7 +11328,7 @@
         <v>45806</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11443,7 +11447,7 @@
         <v>45028</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11563,7 +11567,7 @@
         <v>45953</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11682,7 +11686,7 @@
         <v>45975</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11797,7 +11801,7 @@
         <v>45890</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11912,7 +11916,7 @@
         <v>45751</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12028,7 +12032,7 @@
         <v>45762</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12143,7 +12147,7 @@
         <v>46006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12262,7 +12266,7 @@
         <v>45809</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12376,7 +12380,7 @@
         <v>44929</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12490,7 +12494,7 @@
         <v>46097</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12600,7 +12604,7 @@
         <v>46065</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12714,7 +12718,7 @@
         <v>45618</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12833,7 +12837,7 @@
         <v>44840</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12943,7 +12947,7 @@
         <v>46195</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13053,7 +13057,7 @@
         <v>46008</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13167,7 +13171,7 @@
         <v>45553</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13277,7 +13281,7 @@
         <v>45233</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13392,7 +13396,7 @@
         <v>46059</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13510,7 +13514,7 @@
         <v>44623</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13619,7 +13623,7 @@
         <v>44742</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13733,7 +13737,7 @@
         <v>45349</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13847,7 +13851,7 @@
         <v>45901</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13965,7 +13969,7 @@
         <v>45975</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14078,7 +14082,7 @@
         <v>45897</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14192,7 +14196,7 @@
         <v>45278</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14301,7 +14305,7 @@
         <v>45349</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14419,7 +14423,7 @@
         <v>46000</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14536,7 +14540,7 @@
         <v>45985</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14649,7 +14653,7 @@
         <v>45049</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14758,7 +14762,7 @@
         <v>46294</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14876,7 +14880,7 @@
         <v>46030</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14989,7 +14993,7 @@
         <v>45237</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15106,7 +15110,7 @@
         <v>45748</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15214,7 +15218,7 @@
         <v>45721</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15327,7 +15331,7 @@
         <v>45462</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15435,7 +15439,7 @@
         <v>44904</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15543,7 +15547,7 @@
         <v>44977</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15656,7 +15660,7 @@
         <v>46098</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15764,7 +15768,7 @@
         <v>46160</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15880,7 +15884,7 @@
         <v>44908</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15988,7 +15992,7 @@
         <v>44750</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16096,7 +16100,7 @@
         <v>44853</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16208,7 +16212,7 @@
         <v>46279</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16321,7 +16325,7 @@
         <v>45978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16433,7 +16437,7 @@
         <v>45570</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16541,7 +16545,7 @@
         <v>45785</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16654,7 +16658,7 @@
         <v>46280</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16762,7 +16766,7 @@
         <v>45187</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16878,7 +16882,7 @@
         <v>45919</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16990,7 +16994,7 @@
         <v>45245</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17102,7 +17106,7 @@
         <v>46137</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17209,7 +17213,7 @@
         <v>44904</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17320,7 +17324,7 @@
         <v>44904</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17431,7 +17435,7 @@
         <v>46177</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17538,7 +17542,7 @@
         <v>45644</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17649,7 +17653,7 @@
         <v>45559</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17761,7 +17765,7 @@
         <v>46217</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17873,7 +17877,7 @@
         <v>45561</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17985,7 +17989,7 @@
         <v>46225</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18101,7 +18105,7 @@
         <v>45223</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18213,7 +18217,7 @@
         <v>46275</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18325,7 +18329,7 @@
         <v>44956</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18432,7 +18436,7 @@
         <v>46155</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18539,7 +18543,7 @@
         <v>46288</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18655,7 +18659,7 @@
         <v>45233</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18762,7 +18766,7 @@
         <v>45615</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18869,7 +18873,7 @@
         <v>45737</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18984,7 +18988,7 @@
         <v>44904</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19091,7 +19095,7 @@
         <v>45412</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19198,7 +19202,7 @@
         <v>44544</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19308,7 +19312,7 @@
         <v>44957</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19414,7 +19418,7 @@
         <v>45643</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19525,7 +19529,7 @@
         <v>45975</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19631,7 +19635,7 @@
         <v>44476</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19741,7 +19745,7 @@
         <v>44617</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19852,7 +19856,7 @@
         <v>45321</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19958,7 +19962,7 @@
         <v>45538</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20064,7 +20068,7 @@
         <v>45987</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20170,7 +20174,7 @@
         <v>44927</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20280,7 +20284,7 @@
         <v>45751</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20386,7 +20390,7 @@
         <v>45952</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20492,7 +20496,7 @@
         <v>45558</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20603,7 +20607,7 @@
         <v>46198</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20709,7 +20713,7 @@
         <v>44916</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20815,7 +20819,7 @@
         <v>46282</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20921,7 +20925,7 @@
         <v>44956</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21027,7 +21031,7 @@
         <v>45441</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21142,7 +21146,7 @@
         <v>45553</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21252,7 +21256,7 @@
         <v>45533</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21358,7 +21362,7 @@
         <v>45715</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21464,7 +21468,7 @@
         <v>44643</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21570,7 +21574,7 @@
         <v>44694</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21680,7 +21684,7 @@
         <v>44515</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21790,7 +21794,7 @@
         <v>44742</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21904,7 +21908,7 @@
         <v>45313</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22014,7 +22018,7 @@
         <v>44594</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22119,7 +22123,7 @@
         <v>44642</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22229,7 +22233,7 @@
         <v>44742</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22339,7 +22343,7 @@
         <v>45238</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22449,7 +22453,7 @@
         <v>45637</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22563,7 +22567,7 @@
         <v>45797</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22668,7 +22672,7 @@
         <v>45558</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22778,7 +22782,7 @@
         <v>46051</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22883,7 +22887,7 @@
         <v>45509</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22993,7 +22997,7 @@
         <v>45719</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23103,7 +23107,7 @@
         <v>45763</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23208,7 +23212,7 @@
         <v>45968</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23318,7 +23322,7 @@
         <v>45685</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23423,7 +23427,7 @@
         <v>46120</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23528,7 +23532,7 @@
         <v>45999</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23638,7 +23642,7 @@
         <v>45559</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23748,7 +23752,7 @@
         <v>45679</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23858,7 +23862,7 @@
         <v>45841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23963,7 +23967,7 @@
         <v>46038</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24068,7 +24072,7 @@
         <v>45344</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24173,7 +24177,7 @@
         <v>45617</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24282,7 +24286,7 @@
         <v>45511</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24387,7 +24391,7 @@
         <v>45646</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24501,7 +24505,7 @@
         <v>45867</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24611,7 +24615,7 @@
         <v>45867</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24721,7 +24725,7 @@
         <v>44900</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24826,7 +24830,7 @@
         <v>45280</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24931,7 +24935,7 @@
         <v>46142</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25041,7 +25045,7 @@
         <v>44785</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25150,7 +25154,7 @@
         <v>45629</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25264,7 +25268,7 @@
         <v>45678</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25369,7 +25373,7 @@
         <v>45624</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25479,7 +25483,7 @@
         <v>46184</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25584,7 +25588,7 @@
         <v>46188</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25689,7 +25693,7 @@
         <v>46190</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25794,7 +25798,7 @@
         <v>45223</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25904,7 +25908,7 @@
         <v>46276</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26009,7 +26013,7 @@
         <v>44491</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26119,7 +26123,7 @@
         <v>44928</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26228,7 +26232,7 @@
         <v>46295</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26333,7 +26337,7 @@
         <v>45096</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26438,7 +26442,7 @@
         <v>45118</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26543,7 +26547,7 @@
         <v>46125</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26648,7 +26652,7 @@
         <v>45028</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26753,7 +26757,7 @@
         <v>45957</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26867,7 +26871,7 @@
         <v>44879</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26940,7 +26944,7 @@
         <v>44524</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27018,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27096,7 +27100,7 @@
         <v>44510</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27169,7 +27173,7 @@
         <v>44540</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27242,7 +27246,7 @@
         <v>44613</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27315,7 +27319,7 @@
         <v>44581</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27388,7 +27392,7 @@
         <v>44852</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27461,7 +27465,7 @@
         <v>44561</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27534,7 +27538,7 @@
         <v>44566</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27607,7 +27611,7 @@
         <v>44755</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27685,7 +27689,7 @@
         <v>44852</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27758,7 +27762,7 @@
         <v>44540</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27831,7 +27835,7 @@
         <v>44537</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27904,7 +27908,7 @@
         <v>44609</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27977,7 +27981,7 @@
         <v>44889</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28050,7 +28054,7 @@
         <v>44516</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28123,7 +28127,7 @@
         <v>44875</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28201,7 +28205,7 @@
         <v>44886</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28299,7 +28303,7 @@
         <v>44750</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28372,7 +28376,7 @@
         <v>44517</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28445,7 +28449,7 @@
         <v>44601</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28518,7 +28522,7 @@
         <v>44722</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28596,7 +28600,7 @@
         <v>44722</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28674,7 +28678,7 @@
         <v>44721</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28747,7 +28751,7 @@
         <v>44845</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28820,7 +28824,7 @@
         <v>44540</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28893,7 +28897,7 @@
         <v>44655</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28966,7 +28970,7 @@
         <v>44704</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29044,7 +29048,7 @@
         <v>45273</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29117,7 +29121,7 @@
         <v>45634</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29190,7 +29194,7 @@
         <v>44799</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29263,7 +29267,7 @@
         <v>44875</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29336,7 +29340,7 @@
         <v>45505</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29414,7 +29418,7 @@
         <v>44599</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29487,7 +29491,7 @@
         <v>44607</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29560,7 +29564,7 @@
         <v>45189</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29633,7 +29637,7 @@
         <v>44911</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29706,7 +29710,7 @@
         <v>44706</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29779,7 +29783,7 @@
         <v>45721</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29852,7 +29856,7 @@
         <v>45667</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29930,7 +29934,7 @@
         <v>45588</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30003,7 +30007,7 @@
         <v>45569</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30076,7 +30080,7 @@
         <v>45457</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30149,7 +30153,7 @@
         <v>45315</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30222,7 +30226,7 @@
         <v>45621</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30300,7 +30304,7 @@
         <v>46003</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30373,7 +30377,7 @@
         <v>46003</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30446,7 +30450,7 @@
         <v>46003</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30519,7 +30523,7 @@
         <v>46003</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30592,7 +30596,7 @@
         <v>46003</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30665,7 +30669,7 @@
         <v>45600</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30743,7 +30747,7 @@
         <v>44634</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30816,7 +30820,7 @@
         <v>46007</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30889,7 +30893,7 @@
         <v>46007</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30967,7 +30971,7 @@
         <v>44911</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31040,7 +31044,7 @@
         <v>46010</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31113,7 +31117,7 @@
         <v>46010</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31186,7 +31190,7 @@
         <v>46013</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31259,7 +31263,7 @@
         <v>46013</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31332,7 +31336,7 @@
         <v>45691</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31410,7 +31414,7 @@
         <v>44837</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31483,7 +31487,7 @@
         <v>44909</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31561,7 +31565,7 @@
         <v>45221</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31634,7 +31638,7 @@
         <v>45625</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31707,7 +31711,7 @@
         <v>46019</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31780,7 +31784,7 @@
         <v>45888</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31853,7 +31857,7 @@
         <v>45800</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31926,7 +31930,7 @@
         <v>45895</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31999,7 +32003,7 @@
         <v>44977</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32077,7 +32081,7 @@
         <v>46024</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32150,7 +32154,7 @@
         <v>45895</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32223,7 +32227,7 @@
         <v>46029</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32296,7 +32300,7 @@
         <v>45336</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32369,7 +32373,7 @@
         <v>45790</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32442,7 +32446,7 @@
         <v>45901</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32515,7 +32519,7 @@
         <v>46034</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32588,7 +32592,7 @@
         <v>45902</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32661,7 +32665,7 @@
         <v>45902</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32734,7 +32738,7 @@
         <v>46037</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32807,7 +32811,7 @@
         <v>46032</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32880,7 +32884,7 @@
         <v>44711</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32953,7 +32957,7 @@
         <v>45707</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33026,7 +33030,7 @@
         <v>46037</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33099,7 +33103,7 @@
         <v>45748</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33172,7 +33176,7 @@
         <v>45904</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33245,7 +33249,7 @@
         <v>46038</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33318,7 +33322,7 @@
         <v>46041</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33391,7 +33395,7 @@
         <v>45909</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33464,7 +33468,7 @@
         <v>45911</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33537,7 +33541,7 @@
         <v>46045</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33615,7 +33619,7 @@
         <v>46045</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33688,7 +33692,7 @@
         <v>44475</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33761,7 +33765,7 @@
         <v>45561</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33839,7 +33843,7 @@
         <v>45916</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33912,7 +33916,7 @@
         <v>45611</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33985,7 +33989,7 @@
         <v>45799</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34058,7 +34062,7 @@
         <v>46050</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34131,7 +34135,7 @@
         <v>45803</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34209,7 +34213,7 @@
         <v>44529</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34282,7 +34286,7 @@
         <v>45805</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34360,7 +34364,7 @@
         <v>45587</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34433,7 +34437,7 @@
         <v>45922</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34511,7 +34515,7 @@
         <v>45922</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34589,7 +34593,7 @@
         <v>45691</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34667,7 +34671,7 @@
         <v>45922</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34745,7 +34749,7 @@
         <v>45922</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34823,7 +34827,7 @@
         <v>45922</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34901,7 +34905,7 @@
         <v>45922</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34974,7 +34978,7 @@
         <v>45924</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35052,7 +35056,7 @@
         <v>45924</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35130,7 +35134,7 @@
         <v>46056</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35203,7 +35207,7 @@
         <v>45588</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35276,7 +35280,7 @@
         <v>45576</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35349,7 +35353,7 @@
         <v>45580</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35422,7 +35426,7 @@
         <v>45583</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35495,7 +35499,7 @@
         <v>44742</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35568,7 +35572,7 @@
         <v>46066</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35646,7 +35650,7 @@
         <v>45807</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35719,7 +35723,7 @@
         <v>46066</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35797,7 +35801,7 @@
         <v>45937</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35875,7 +35879,7 @@
         <v>46070</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35953,7 +35957,7 @@
         <v>44655</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36026,7 +36030,7 @@
         <v>46073</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36099,7 +36103,7 @@
         <v>45321</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36172,7 +36176,7 @@
         <v>46078</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36245,7 +36249,7 @@
         <v>44970</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36323,7 +36327,7 @@
         <v>46078</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36396,7 +36400,7 @@
         <v>45944</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36474,7 +36478,7 @@
         <v>46076</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36552,7 +36556,7 @@
         <v>45551</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36630,7 +36634,7 @@
         <v>45707</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36703,7 +36707,7 @@
         <v>45659</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36776,7 +36780,7 @@
         <v>45188</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36849,7 +36853,7 @@
         <v>45720</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36927,7 +36931,7 @@
         <v>45743</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37000,7 +37004,7 @@
         <v>45722</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37078,7 +37082,7 @@
         <v>45978</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37151,7 +37155,7 @@
         <v>45736</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37224,7 +37228,7 @@
         <v>45743</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37297,7 +37301,7 @@
         <v>45720</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37375,7 +37379,7 @@
         <v>45813</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37448,7 +37452,7 @@
         <v>45958</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37526,7 +37530,7 @@
         <v>45004</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37599,7 +37603,7 @@
         <v>45964</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37677,7 +37681,7 @@
         <v>46091</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37750,7 +37754,7 @@
         <v>44743</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37823,7 +37827,7 @@
         <v>45309</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37896,7 +37900,7 @@
         <v>46098</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37969,7 +37973,7 @@
         <v>45107</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38042,7 +38046,7 @@
         <v>45261</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38120,7 +38124,7 @@
         <v>45819</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38198,7 +38202,7 @@
         <v>45089</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38271,7 +38275,7 @@
         <v>45818</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38349,7 +38353,7 @@
         <v>45985</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38422,7 +38426,7 @@
         <v>46097</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38500,7 +38504,7 @@
         <v>45985</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38573,7 +38577,7 @@
         <v>45231</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38651,7 +38655,7 @@
         <v>45986</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38724,7 +38728,7 @@
         <v>45987</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38797,7 +38801,7 @@
         <v>45992</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38870,7 +38874,7 @@
         <v>45992</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38943,7 +38947,7 @@
         <v>45992</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39016,7 +39020,7 @@
         <v>46114</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39089,7 +39093,7 @@
         <v>45707</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39162,7 +39166,7 @@
         <v>46125</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39235,7 +39239,7 @@
         <v>45691</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39308,7 +39312,7 @@
         <v>46126</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39386,7 +39390,7 @@
         <v>45993</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39459,7 +39463,7 @@
         <v>46000</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39532,7 +39536,7 @@
         <v>46000</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39605,7 +39609,7 @@
         <v>46133</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39683,7 +39687,7 @@
         <v>45681</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39761,7 +39765,7 @@
         <v>45681</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39839,7 +39843,7 @@
         <v>46132</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39912,7 +39916,7 @@
         <v>45190</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39985,7 +39989,7 @@
         <v>45688</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40058,7 +40062,7 @@
         <v>46135</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40131,7 +40135,7 @@
         <v>45342</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40209,7 +40213,7 @@
         <v>45338</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40282,7 +40286,7 @@
         <v>46000</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40355,7 +40359,7 @@
         <v>44949</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40428,7 +40432,7 @@
         <v>45632</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40501,7 +40505,7 @@
         <v>44790</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40574,7 +40578,7 @@
         <v>45223</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40647,7 +40651,7 @@
         <v>44511</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40720,7 +40724,7 @@
         <v>46029</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40793,7 +40797,7 @@
         <v>45847</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40871,7 +40875,7 @@
         <v>46136</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40949,7 +40953,7 @@
         <v>45847</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41027,7 +41031,7 @@
         <v>45847</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41105,7 +41109,7 @@
         <v>45300</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41178,7 +41182,7 @@
         <v>45520</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41251,7 +41255,7 @@
         <v>45265</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41329,7 +41333,7 @@
         <v>46139</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41407,7 +41411,7 @@
         <v>45586</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41485,7 +41489,7 @@
         <v>46008</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41558,7 +41562,7 @@
         <v>45096</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41631,7 +41635,7 @@
         <v>46139</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41709,7 +41713,7 @@
         <v>46139</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41787,7 +41791,7 @@
         <v>45696</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41860,7 +41864,7 @@
         <v>45800</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41933,7 +41937,7 @@
         <v>45412</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42006,7 +42010,7 @@
         <v>45837</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42084,7 +42088,7 @@
         <v>45646</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42162,7 +42166,7 @@
         <v>45646</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42240,7 +42244,7 @@
         <v>45708</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42313,7 +42317,7 @@
         <v>45553</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42386,7 +42390,7 @@
         <v>45264</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42459,7 +42463,7 @@
         <v>45807</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42532,7 +42536,7 @@
         <v>44790</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42605,7 +42609,7 @@
         <v>44889</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42683,7 +42687,7 @@
         <v>45866</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42761,7 +42765,7 @@
         <v>45012</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42834,7 +42838,7 @@
         <v>45112</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42907,7 +42911,7 @@
         <v>45667</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42985,7 +42989,7 @@
         <v>46142</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43063,7 +43067,7 @@
         <v>45475</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43141,7 +43145,7 @@
         <v>45593</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43219,7 +43223,7 @@
         <v>45593</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43297,7 +43301,7 @@
         <v>45597</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43375,7 +43379,7 @@
         <v>45688</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43453,7 +43457,7 @@
         <v>46153</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43526,7 +43530,7 @@
         <v>45634</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43599,7 +43603,7 @@
         <v>45002</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43677,7 +43681,7 @@
         <v>46150</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43750,7 +43754,7 @@
         <v>46150</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43823,7 +43827,7 @@
         <v>46150</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43896,7 +43900,7 @@
         <v>45691</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43969,7 +43973,7 @@
         <v>45693</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44042,7 +44046,7 @@
         <v>46154</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44120,7 +44124,7 @@
         <v>46156</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44198,7 +44202,7 @@
         <v>44952</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44271,7 +44275,7 @@
         <v>45887</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44344,7 +44348,7 @@
         <v>46120</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44417,7 +44421,7 @@
         <v>45686</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44490,7 +44494,7 @@
         <v>45177</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44568,7 +44572,7 @@
         <v>46163</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44641,7 +44645,7 @@
         <v>46163</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44714,7 +44718,7 @@
         <v>44907</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44792,7 +44796,7 @@
         <v>44750</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44865,7 +44869,7 @@
         <v>46163</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44938,7 +44942,7 @@
         <v>46066</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45011,7 +45015,7 @@
         <v>46164</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45089,7 +45093,7 @@
         <v>46164</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45167,7 +45171,7 @@
         <v>46164</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45245,7 +45249,7 @@
         <v>46164</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45318,7 +45322,7 @@
         <v>46164</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45396,7 +45400,7 @@
         <v>46164</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45474,7 +45478,7 @@
         <v>46164</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45552,7 +45556,7 @@
         <v>46164</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45630,7 +45634,7 @@
         <v>46164</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45708,7 +45712,7 @@
         <v>46164</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45781,7 +45785,7 @@
         <v>45012</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45854,7 +45858,7 @@
         <v>45302</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45927,7 +45931,7 @@
         <v>46175</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46005,7 +46009,7 @@
         <v>44911</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46078,7 +46082,7 @@
         <v>44721</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46151,7 +46155,7 @@
         <v>45616</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46229,7 +46233,7 @@
         <v>44680</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46302,7 +46306,7 @@
         <v>46184</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46375,7 +46379,7 @@
         <v>46183</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46448,7 +46452,7 @@
         <v>46190</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46521,7 +46525,7 @@
         <v>45239</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46599,7 +46603,7 @@
         <v>46190</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46672,7 +46676,7 @@
         <v>46190</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46745,7 +46749,7 @@
         <v>45628</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46818,7 +46822,7 @@
         <v>45763</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46891,7 +46895,7 @@
         <v>45428</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46969,7 +46973,7 @@
         <v>45092</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47042,7 +47046,7 @@
         <v>45709</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47120,7 +47124,7 @@
         <v>46206</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47193,7 +47197,7 @@
         <v>45770</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47266,7 +47270,7 @@
         <v>45547</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47339,7 +47343,7 @@
         <v>46216</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47417,7 +47421,7 @@
         <v>45344</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47490,7 +47494,7 @@
         <v>45588</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47568,7 +47572,7 @@
         <v>45600</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47646,7 +47650,7 @@
         <v>46073</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47719,7 +47723,7 @@
         <v>45260</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47792,7 +47796,7 @@
         <v>45260</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47865,7 +47869,7 @@
         <v>44880</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47938,7 +47942,7 @@
         <v>46180</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48011,7 +48015,7 @@
         <v>45939</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48089,7 +48093,7 @@
         <v>45707</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48167,7 +48171,7 @@
         <v>46220</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48240,7 +48244,7 @@
         <v>46203</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48313,7 +48317,7 @@
         <v>45462</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48391,7 +48395,7 @@
         <v>44609</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48464,7 +48468,7 @@
         <v>44635</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48537,7 +48541,7 @@
         <v>46269</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48615,7 +48619,7 @@
         <v>46272</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48688,7 +48692,7 @@
         <v>45677</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48761,7 +48765,7 @@
         <v>46275</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48834,7 +48838,7 @@
         <v>46231</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48912,7 +48916,7 @@
         <v>46231</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48990,7 +48994,7 @@
         <v>46231</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49068,7 +49072,7 @@
         <v>46231</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49146,7 +49150,7 @@
         <v>46275</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49224,7 +49228,7 @@
         <v>46135</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49297,7 +49301,7 @@
         <v>46279</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49370,7 +49374,7 @@
         <v>46279</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49443,7 +49447,7 @@
         <v>46276</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49521,7 +49525,7 @@
         <v>46279</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49594,7 +49598,7 @@
         <v>45435</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49667,7 +49671,7 @@
         <v>46280</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49745,7 +49749,7 @@
         <v>45057</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49818,7 +49822,7 @@
         <v>46281</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49891,7 +49895,7 @@
         <v>46281</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49964,7 +49968,7 @@
         <v>45475</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50037,7 +50041,7 @@
         <v>46238</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50110,7 +50114,7 @@
         <v>46239</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50183,7 +50187,7 @@
         <v>46283</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50261,7 +50265,7 @@
         <v>46241</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50334,7 +50338,7 @@
         <v>45221</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50407,7 +50411,7 @@
         <v>46282</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50485,7 +50489,7 @@
         <v>46241</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50558,7 +50562,7 @@
         <v>45315</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50631,7 +50635,7 @@
         <v>45477</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50704,7 +50708,7 @@
         <v>46286</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50777,7 +50781,7 @@
         <v>45166</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50855,7 +50859,7 @@
         <v>46287</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50933,7 +50937,7 @@
         <v>45236</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51011,7 +51015,7 @@
         <v>45677</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51084,7 +51088,7 @@
         <v>46286</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51157,7 +51161,7 @@
         <v>44922</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51230,7 +51234,7 @@
         <v>45057</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51308,7 +51312,7 @@
         <v>46132</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51381,7 +51385,7 @@
         <v>46288</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51459,7 +51463,7 @@
         <v>44986</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51537,7 +51541,7 @@
         <v>46289</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51610,7 +51614,7 @@
         <v>44735</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51683,7 +51687,7 @@
         <v>45183</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51756,7 +51760,7 @@
         <v>44757</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51829,7 +51833,7 @@
         <v>45237</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51902,7 +51906,7 @@
         <v>44883</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51975,7 +51979,7 @@
         <v>45370</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52048,7 +52052,7 @@
         <v>46248</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52121,7 +52125,7 @@
         <v>45159</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52194,7 +52198,7 @@
         <v>45572</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52272,7 +52276,7 @@
         <v>45762</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52350,7 +52354,7 @@
         <v>44679</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52423,7 +52427,7 @@
         <v>45223</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52496,7 +52500,7 @@
         <v>46294</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52569,7 +52573,7 @@
         <v>46203</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52642,7 +52646,7 @@
         <v>45223</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52715,7 +52719,7 @@
         <v>45236</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52788,7 +52792,7 @@
         <v>45789</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52861,7 +52865,7 @@
         <v>44922</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52934,7 +52938,7 @@
         <v>45477</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53007,7 +53011,7 @@
         <v>45008</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53080,7 +53084,7 @@
         <v>45660</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53153,7 +53157,7 @@
         <v>45793</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53226,7 +53230,7 @@
         <v>45639</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53304,7 +53308,7 @@
         <v>44721</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53382,7 +53386,7 @@
         <v>46206</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53455,7 +53459,7 @@
         <v>45954</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53528,7 +53532,7 @@
         <v>45096</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53601,7 +53605,7 @@
         <v>46014</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53674,7 +53678,7 @@
         <v>46206</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53747,7 +53751,7 @@
         <v>45149</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53820,7 +53824,7 @@
         <v>45376</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53893,7 +53897,7 @@
         <v>44614</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53966,7 +53970,7 @@
         <v>44986</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54044,7 +54048,7 @@
         <v>45231</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54122,7 +54126,7 @@
         <v>45707</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54195,7 +54199,7 @@
         <v>45324</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54273,7 +54277,7 @@
         <v>44533</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54346,7 +54350,7 @@
         <v>44952</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54419,7 +54423,7 @@
         <v>44937</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54492,7 +54496,7 @@
         <v>45429</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54565,7 +54569,7 @@
         <v>45702</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54638,7 +54642,7 @@
         <v>45690</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54711,7 +54715,7 @@
         <v>45313</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54784,7 +54788,7 @@
         <v>45460</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54857,7 +54861,7 @@
         <v>45615</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54930,7 +54934,7 @@
         <v>45306</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55003,7 +55007,7 @@
         <v>44889</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55076,7 +55080,7 @@
         <v>45328</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55149,7 +55153,7 @@
         <v>44564</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55222,7 +55226,7 @@
         <v>45636</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55295,7 +55299,7 @@
         <v>45198</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55373,7 +55377,7 @@
         <v>45692</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55446,7 +55450,7 @@
         <v>45779</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55519,7 +55523,7 @@
         <v>45686</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55592,7 +55596,7 @@
         <v>45686</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55665,7 +55669,7 @@
         <v>45686</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55738,7 +55742,7 @@
         <v>45789</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55811,7 +55815,7 @@
         <v>45744</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55884,7 +55888,7 @@
         <v>45820</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55957,7 +55961,7 @@
         <v>46058</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56030,7 +56034,7 @@
         <v>46058</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56103,7 +56107,7 @@
         <v>46276</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45109</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>45155</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44585</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>45540</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>45690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>46191</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44642</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>46104</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45932</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>46108</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45985</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45600</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>46195</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>46195</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45924</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>46119</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>46195</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45988</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45975</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>46129</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>45747</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44945</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44971</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>46119</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44819</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>46210</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>45932</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>45112</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>45916</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>46044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45978</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>46073</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>46010</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45929</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>46119</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45932</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>46140</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>46213</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45602</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>45063</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45475</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>46044</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>45621</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>45415</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45575</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45574</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>46195</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>45937</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44851</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>46042</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>45526</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>45986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45649</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>46133</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45470</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45940</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>44637</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45952</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>45320</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>45897</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>46076</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>46119</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>45170</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>45349</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>44911</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44945</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>45189</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>46073</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>46073</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>45198</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>46010</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>45936</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>46043</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46105</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>45806</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>45028</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>45953</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45975</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>45890</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45751</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>45762</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>46006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>45809</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>44929</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>46097</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>46065</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45618</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>44840</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>46195</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>46008</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>45553</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>45233</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>46059</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>44623</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>44742</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>45349</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45901</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45975</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45897</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>45278</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>45349</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>46000</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45985</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>45049</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>46294</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>46030</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45237</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>45748</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45721</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>45462</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>44904</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44977</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>46098</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>46160</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>44908</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44750</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>44853</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>46279</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45570</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>45785</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>46280</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45187</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45919</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45245</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>46137</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44904</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>44904</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>46177</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45644</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45559</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>46217</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45561</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>46225</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45223</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>46275</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44956</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>46155</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>46288</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45233</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>45615</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>45737</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44904</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45412</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>44544</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>44957</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>45643</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>45975</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>44476</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>44617</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>45321</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45538</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>45987</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44927</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45751</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45952</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45558</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>46198</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44916</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>46282</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>44956</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45441</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45553</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45533</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>45715</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>44643</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44694</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>44515</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44742</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45313</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>44594</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>44642</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44742</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>45238</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45637</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45797</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45558</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>46051</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45509</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45719</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>45763</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45968</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45685</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>46120</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45999</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45559</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45679</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>46038</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45344</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>45617</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45511</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45646</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45867</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45867</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>44900</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>45280</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46142</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>44785</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45629</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45678</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45624</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>46184</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>46188</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>46190</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>45223</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>46276</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>44491</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44928</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>46295</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45096</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>45118</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>46125</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45028</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>45957</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44879</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44524</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44510</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>44540</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>44613</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>44581</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44852</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>44561</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>44566</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>44755</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>44852</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>44540</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>44537</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>44609</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44889</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>44516</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44875</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>44886</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>44750</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>44517</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>44601</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44722</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>44722</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>44721</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>44845</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>44540</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>44655</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>44704</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45273</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45634</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>44799</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>44875</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>45505</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44599</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>44607</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>45189</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>44911</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>44706</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>45721</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45667</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45588</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45569</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>45457</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>45315</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45621</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>46003</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>46003</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>46003</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>46003</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46003</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>45600</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>44634</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>46007</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>46007</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44911</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>46010</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>46010</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>46013</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>46013</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45691</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44837</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44909</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>45221</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45625</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>46019</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>45888</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45800</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45895</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>44977</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>46024</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>45895</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>46029</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45336</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45790</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>45901</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>46034</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45902</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45902</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>46037</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32811,7 +32811,7 @@
         <v>46032</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32884,7 +32884,7 @@
         <v>44711</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>45707</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>46037</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>45748</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>45904</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>46038</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>46041</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45909</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>45911</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>46045</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>46045</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44475</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>45561</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45916</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>45611</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45799</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>46050</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45803</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>44529</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45805</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45587</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>45922</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45922</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45691</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>45922</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45922</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45922</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45922</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45924</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45924</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>46056</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>45588</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>45576</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35353,7 +35353,7 @@
         <v>45580</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>45583</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>44742</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>46066</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>45807</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>46066</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>45937</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>46070</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44655</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>46073</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>45321</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36176,7 +36176,7 @@
         <v>46078</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>44970</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36327,7 +36327,7 @@
         <v>46078</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36400,7 +36400,7 @@
         <v>45944</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>46076</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>45551</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>45707</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>45659</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45188</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>45720</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>45743</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>45722</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37082,7 +37082,7 @@
         <v>45978</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37155,7 +37155,7 @@
         <v>45736</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>45743</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45720</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>45813</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45958</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>45004</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>45964</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>46091</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>44743</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45309</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>46098</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>45107</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>45261</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45819</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>45089</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45818</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>45985</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38426,7 +38426,7 @@
         <v>46097</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38504,7 +38504,7 @@
         <v>45985</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45231</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>45986</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45987</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38801,7 +38801,7 @@
         <v>45992</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38874,7 +38874,7 @@
         <v>45992</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45992</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>46114</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39093,7 +39093,7 @@
         <v>45707</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>46125</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>45691</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>46126</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45993</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>46000</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>46000</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39609,7 +39609,7 @@
         <v>46133</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>45681</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45681</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>46132</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45190</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39989,7 +39989,7 @@
         <v>45688</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40062,7 +40062,7 @@
         <v>46135</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>45342</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>45338</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>46000</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>44949</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45632</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>44790</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>45223</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44511</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>46029</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>45847</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>46136</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40953,7 +40953,7 @@
         <v>45847</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>45847</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>45300</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45520</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>45265</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>46139</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45586</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>46008</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45096</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>46139</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>46139</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>45696</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>45800</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45412</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>45837</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>45646</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>45646</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42244,7 +42244,7 @@
         <v>45708</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45553</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45264</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42463,7 +42463,7 @@
         <v>45807</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>44790</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>44889</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45866</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42765,7 +42765,7 @@
         <v>45012</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45112</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45667</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>46142</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45475</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45593</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43223,7 +43223,7 @@
         <v>45593</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45597</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
         <v>45688</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46153</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45634</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>45002</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46150</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>46150</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>46150</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45691</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>45693</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>46154</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>46156</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>44952</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45887</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>46120</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45686</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45177</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>46163</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>46163</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>44907</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>44750</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>46163</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>46066</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>46164</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>46164</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>46164</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>46164</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>46164</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>46164</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>46164</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>46164</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>46164</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>46164</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>45012</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45302</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>46175</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>44911</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>44721</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>45616</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>44680</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>46184</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>46183</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>46190</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45239</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46603,7 +46603,7 @@
         <v>46190</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>46190</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45628</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45763</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45428</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45092</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45709</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>46206</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45770</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45547</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>46216</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>45344</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45588</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45600</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>46073</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>45260</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45260</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>44880</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>46180</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>45939</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>45707</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48171,7 +48171,7 @@
         <v>46220</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48244,7 +48244,7 @@
         <v>46203</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45462</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>44609</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>44635</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>46269</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>46272</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48692,7 +48692,7 @@
         <v>45677</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>46275</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>46231</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48916,7 +48916,7 @@
         <v>46231</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48994,7 +48994,7 @@
         <v>46231</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>46231</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>46275</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49228,7 +49228,7 @@
         <v>46135</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>46279</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49374,7 +49374,7 @@
         <v>46279</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>46276</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49525,7 +49525,7 @@
         <v>46279</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45435</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>46280</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>45057</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>46281</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49895,7 +49895,7 @@
         <v>46281</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>45475</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>46238</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50114,7 +50114,7 @@
         <v>46239</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>46283</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>46241</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50338,7 +50338,7 @@
         <v>45221</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>46282</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>46241</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>45315</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>45477</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>46286</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45166</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>46287</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50937,7 +50937,7 @@
         <v>45236</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>45677</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>46286</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51161,7 +51161,7 @@
         <v>44922</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45057</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51312,7 +51312,7 @@
         <v>46132</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51385,7 +51385,7 @@
         <v>46288</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51463,7 +51463,7 @@
         <v>44986</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51541,7 +51541,7 @@
         <v>46289</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51614,7 +51614,7 @@
         <v>44735</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51687,7 +51687,7 @@
         <v>45183</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>44757</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>45237</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51906,7 +51906,7 @@
         <v>44883</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51979,7 +51979,7 @@
         <v>45370</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>46248</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52125,7 +52125,7 @@
         <v>45159</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52198,7 +52198,7 @@
         <v>45572</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52276,7 +52276,7 @@
         <v>45762</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>44679</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52427,7 +52427,7 @@
         <v>45223</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52500,7 +52500,7 @@
         <v>46294</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>46203</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45223</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52719,7 +52719,7 @@
         <v>45236</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52792,7 +52792,7 @@
         <v>45789</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52865,7 +52865,7 @@
         <v>44922</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52938,7 +52938,7 @@
         <v>45477</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45008</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>45660</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53157,7 +53157,7 @@
         <v>45793</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>45639</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53308,7 +53308,7 @@
         <v>44721</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53386,7 +53386,7 @@
         <v>46206</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53459,7 +53459,7 @@
         <v>45954</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53532,7 +53532,7 @@
         <v>45096</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53605,7 +53605,7 @@
         <v>46014</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53678,7 +53678,7 @@
         <v>46206</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53751,7 +53751,7 @@
         <v>45149</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45376</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53897,7 +53897,7 @@
         <v>44614</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53970,7 +53970,7 @@
         <v>44986</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>45231</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>45707</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54199,7 +54199,7 @@
         <v>45324</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54277,7 +54277,7 @@
         <v>44533</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>44952</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         <v>44937</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54496,7 +54496,7 @@
         <v>45429</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54569,7 +54569,7 @@
         <v>45702</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54642,7 +54642,7 @@
         <v>45690</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45313</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54788,7 +54788,7 @@
         <v>45460</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         <v>45615</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54934,7 +54934,7 @@
         <v>45306</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>44889</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55080,7 +55080,7 @@
         <v>45328</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55153,7 +55153,7 @@
         <v>44564</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>45636</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>45198</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55377,7 +55377,7 @@
         <v>45692</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>45779</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55523,7 +55523,7 @@
         <v>45686</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>45686</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>45686</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>45789</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45744</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45820</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55961,7 +55961,7 @@
         <v>46058</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56034,7 +56034,7 @@
         <v>46058</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>46276</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45109</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>45155</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44585</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>45540</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>45690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 27881-2026</t>
+          <t>A 12943-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46191</v>
+        <v>44642</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1993,23 +1993,23 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
@@ -2017,155 +2017,21 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="T11" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="U11" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Björktrast
-Harticka
-Lunglav
-Rödvingetrast
-Talltita
-Tretåig hackspett
-Ullticka
-Finbräken
-Kransrams
-Luddlav
-Spindelblomster
-Stuplav
-Svart trolldruva
-Tvåblad
-Ögonpyrola
-Bergfink
-Blåsippa
-Brudborste
-Ekbräken
-Kransmossa
-Kärrfibbla
-Nordisk stormhatt
-Ormbär
-Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 27881-2026 artfynd.xlsx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 27881-2026 karta.png", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 27881-2026 georefererad karta.tif", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 27881-2026 FSC-klagomål.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 27881-2026 FSC-klagomål mail.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 27881-2026 tillsynsbegäran.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 27881-2026 tillsynsbegäran mail.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 27881-2026 prioriterade fågelarter.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 12943-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44642</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>12</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>23</v>
-      </c>
-      <c r="T12" t="n">
-        <v>68</v>
-      </c>
-      <c r="U12" t="n">
-        <v>56</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Trolldruvemätare
 Knärot
@@ -2192,115 +2058,115 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 12943-2022 artfynd.xlsx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 12943-2022 karta.png", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 12943-2022 georefererad karta.tif", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 12943-2022 karta knärot.png", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 12943-2022 FSC-klagomål.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 12943-2022 FSC-klagomål mail.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 12943-2022 tillsynsbegäran.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 12943-2022 tillsynsbegäran mail.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 12943-2022 prioriterade fågelarter.docx", "A 12943-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 14960-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>46104</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>14.8</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J12" t="n">
         <v>8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K12" t="n">
         <v>7</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L12" t="n">
         <v>7</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M12" t="n">
         <v>2</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>9</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R12" t="n">
         <v>2</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S12" t="n">
         <v>22</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T12" t="n">
         <v>180</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U12" t="n">
         <v>164</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -2326,40 +2192,170 @@
 Revlummer</t>
         </is>
       </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 14960-2026 artfynd.xlsx", "A 14960-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 14960-2026 karta.png", "A 14960-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 14960-2026 georefererad karta.tif", "A 14960-2026")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 14960-2026 karta knärot.png", "A 14960-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 14960-2026 FSC-klagomål.docx", "A 14960-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 14960-2026 FSC-klagomål mail.docx", "A 14960-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 14960-2026 tillsynsbegäran.docx", "A 14960-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 14960-2026 tillsynsbegäran mail.docx", "A 14960-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 14960-2026 prioriterade fågelarter.docx", "A 14960-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 27881-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>22</v>
+      </c>
+      <c r="T13" t="n">
+        <v>37</v>
+      </c>
+      <c r="U13" t="n">
+        <v>37</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Lunglav
+Rödvingetrast
+Talltita
+Tretåig hackspett
+Ullticka
+Finbräken
+Kransrams
+Luddlav
+Spindelblomster
+Stuplav
+Svart trolldruva
+Tvåblad
+Ögonpyrola
+Blåsippa
+Brudborste
+Ekbräken
+Kransmossa
+Kärrfibbla
+Nordisk stormhatt
+Ormbär
+Fläcknycklar</t>
+        </is>
+      </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 14960-2026 artfynd.xlsx", "A 14960-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 27881-2026 artfynd.xlsx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 14960-2026 karta.png", "A 14960-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 27881-2026 karta.png", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 14960-2026 georefererad karta.tif", "A 14960-2026")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 14960-2026 karta knärot.png", "A 14960-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 27881-2026 georefererad karta.tif", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 14960-2026 FSC-klagomål.docx", "A 14960-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 27881-2026 FSC-klagomål.docx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 14960-2026 FSC-klagomål mail.docx", "A 14960-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 27881-2026 FSC-klagomål mail.docx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 14960-2026 tillsynsbegäran.docx", "A 14960-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 27881-2026 tillsynsbegäran.docx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 14960-2026 tillsynsbegäran mail.docx", "A 14960-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 27881-2026 tillsynsbegäran mail.docx", "A 27881-2026")</f>
         <v/>
       </c>
       <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 14960-2026 prioriterade fågelarter.docx", "A 14960-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 27881-2026 prioriterade fågelarter.docx", "A 27881-2026")</f>
         <v/>
       </c>
     </row>
@@ -2383,7 +2379,7 @@
         <v>45932</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2517,7 +2513,7 @@
         <v>46108</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2646,7 +2642,7 @@
         <v>45600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2784,7 +2780,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2917,7 +2913,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3050,7 +3046,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3183,7 +3179,7 @@
         <v>46195</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3315,7 +3311,7 @@
         <v>45924</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3447,7 +3443,7 @@
         <v>46119</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3575,7 +3571,7 @@
         <v>46195</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3706,7 +3702,7 @@
         <v>45161</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3832,7 +3828,7 @@
         <v>45988</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3967,7 +3963,7 @@
         <v>45975</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4097,7 +4093,7 @@
         <v>44945</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4225,7 +4221,7 @@
         <v>46129</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4350,7 +4346,7 @@
         <v>45747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4478,7 +4474,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4607,7 +4603,7 @@
         <v>44971</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4735,7 +4731,7 @@
         <v>46119</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4862,7 +4858,7 @@
         <v>44819</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4990,7 +4986,7 @@
         <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5108,7 +5104,7 @@
         <v>45932</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5234,7 +5230,7 @@
         <v>45916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5360,7 +5356,7 @@
         <v>46044</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5477,7 +5473,7 @@
         <v>45978</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5597,7 +5593,7 @@
         <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5717,7 +5713,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5841,7 +5837,7 @@
         <v>46073</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5965,7 +5961,7 @@
         <v>45890</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6089,7 +6085,7 @@
         <v>45929</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6209,7 +6205,7 @@
         <v>46119</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6332,7 +6328,7 @@
         <v>45932</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6455,7 +6451,7 @@
         <v>46140</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6570,7 +6566,7 @@
         <v>46213</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6693,7 +6689,7 @@
         <v>45574</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6812,7 +6808,7 @@
         <v>45602</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6939,7 +6935,7 @@
         <v>45415</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7061,7 +7057,7 @@
         <v>44851</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7183,7 +7179,7 @@
         <v>45063</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7301,7 +7297,7 @@
         <v>45526</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7420,7 +7416,7 @@
         <v>45475</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7543,7 +7539,7 @@
         <v>45621</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7661,7 +7657,7 @@
         <v>46044</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7775,7 +7771,7 @@
         <v>45575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7893,7 +7889,7 @@
         <v>46195</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8015,7 +8011,7 @@
         <v>45937</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8137,7 +8133,7 @@
         <v>46042</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8255,7 +8251,7 @@
         <v>45986</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8373,7 +8369,7 @@
         <v>44637</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8486,7 +8482,7 @@
         <v>46133</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8604,7 +8600,7 @@
         <v>45649</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8721,7 +8717,7 @@
         <v>45937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8842,7 +8838,7 @@
         <v>45470</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8963,7 +8959,7 @@
         <v>45940</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9084,7 +9080,7 @@
         <v>45952</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9205,7 +9201,7 @@
         <v>45170</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9326,7 +9322,7 @@
         <v>45349</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9447,7 +9443,7 @@
         <v>45161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9567,7 +9563,7 @@
         <v>45320</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9679,7 +9675,7 @@
         <v>45897</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9796,7 +9792,7 @@
         <v>46076</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9916,7 +9912,7 @@
         <v>46119</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10032,7 +10028,7 @@
         <v>44911</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10148,7 +10144,7 @@
         <v>45198</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10264,7 +10260,7 @@
         <v>45028</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10384,7 +10380,7 @@
         <v>44945</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10504,7 +10500,7 @@
         <v>45189</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10615,7 +10611,7 @@
         <v>46073</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10734,7 +10730,7 @@
         <v>46073</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10853,7 +10849,7 @@
         <v>46043</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10968,7 +10964,7 @@
         <v>46105</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11083,7 +11079,7 @@
         <v>45936</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11202,7 +11198,7 @@
         <v>45806</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11321,7 +11317,7 @@
         <v>45975</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11436,7 +11432,7 @@
         <v>45890</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11551,7 +11547,7 @@
         <v>45953</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11670,7 +11666,7 @@
         <v>45751</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11786,7 +11782,7 @@
         <v>44929</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11900,7 +11896,7 @@
         <v>45618</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12019,7 +12015,7 @@
         <v>45809</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12133,7 +12129,7 @@
         <v>45233</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12248,7 +12244,7 @@
         <v>45762</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12363,7 +12359,7 @@
         <v>46097</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12473,7 +12469,7 @@
         <v>44840</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12583,7 +12579,7 @@
         <v>46065</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12697,7 +12693,7 @@
         <v>46006</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12816,7 +12812,7 @@
         <v>46195</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12926,7 +12922,7 @@
         <v>46008</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13040,7 +13036,7 @@
         <v>45553</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13150,7 +13146,7 @@
         <v>46059</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13268,7 +13264,7 @@
         <v>44742</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13382,7 +13378,7 @@
         <v>44623</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13491,7 +13487,7 @@
         <v>45278</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13600,7 +13596,7 @@
         <v>45349</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13714,7 +13710,7 @@
         <v>45901</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13832,7 +13828,7 @@
         <v>45349</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13950,7 +13946,7 @@
         <v>45975</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14063,7 +14059,7 @@
         <v>45897</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14177,7 +14173,7 @@
         <v>45985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14290,7 +14286,7 @@
         <v>46000</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14407,7 +14403,7 @@
         <v>45049</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14516,7 +14512,7 @@
         <v>46294</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14634,7 +14630,7 @@
         <v>46030</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14747,7 +14743,7 @@
         <v>44908</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14855,7 +14851,7 @@
         <v>45553</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14967,7 +14963,7 @@
         <v>45570</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15075,7 +15071,7 @@
         <v>45237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15192,7 +15188,7 @@
         <v>45748</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15300,7 +15296,7 @@
         <v>45462</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15408,7 +15404,7 @@
         <v>44750</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15516,7 +15512,7 @@
         <v>44853</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15628,7 +15624,7 @@
         <v>44904</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15736,7 +15732,7 @@
         <v>44977</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15849,7 +15845,7 @@
         <v>45721</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15962,7 +15958,7 @@
         <v>46098</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16070,7 +16066,7 @@
         <v>46160</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16186,7 +16182,7 @@
         <v>46279</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16299,7 +16295,7 @@
         <v>45978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16411,7 +16407,7 @@
         <v>45785</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16524,7 +16520,7 @@
         <v>46280</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16632,7 +16628,7 @@
         <v>45223</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16744,7 +16740,7 @@
         <v>44904</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16855,7 +16851,7 @@
         <v>44904</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16966,7 +16962,7 @@
         <v>45559</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17078,7 +17074,7 @@
         <v>45644</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17189,7 +17185,7 @@
         <v>44904</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17296,7 +17292,7 @@
         <v>45737</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17411,7 +17407,7 @@
         <v>45919</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17523,7 +17519,7 @@
         <v>45187</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17639,7 +17635,7 @@
         <v>45233</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17746,7 +17742,7 @@
         <v>45615</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17853,7 +17849,7 @@
         <v>45245</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17965,7 +17961,7 @@
         <v>45561</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18077,7 +18073,7 @@
         <v>46137</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18184,7 +18180,7 @@
         <v>46177</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18291,7 +18287,7 @@
         <v>46217</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18403,7 +18399,7 @@
         <v>46225</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18519,7 +18515,7 @@
         <v>46275</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18631,7 +18627,7 @@
         <v>44956</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18738,7 +18734,7 @@
         <v>46155</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18845,7 +18841,7 @@
         <v>46288</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18961,7 +18957,7 @@
         <v>45412</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19068,7 +19064,7 @@
         <v>44544</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19178,7 +19174,7 @@
         <v>45751</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19284,7 +19280,7 @@
         <v>45558</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19395,7 +19391,7 @@
         <v>44617</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19506,7 +19502,7 @@
         <v>44927</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19616,7 +19612,7 @@
         <v>45538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19722,7 +19718,7 @@
         <v>44643</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19828,7 +19824,7 @@
         <v>45321</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19934,7 +19930,7 @@
         <v>45643</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20045,7 +20041,7 @@
         <v>45441</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20160,7 +20156,7 @@
         <v>45715</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20266,7 +20262,7 @@
         <v>45987</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20372,7 +20368,7 @@
         <v>44957</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20478,7 +20474,7 @@
         <v>44956</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20584,7 +20580,7 @@
         <v>45975</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20690,7 +20686,7 @@
         <v>45952</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20796,7 +20792,7 @@
         <v>46198</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20902,7 +20898,7 @@
         <v>44916</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21008,7 +21004,7 @@
         <v>46282</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21114,7 +21110,7 @@
         <v>45533</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21220,7 +21216,7 @@
         <v>45313</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21330,7 +21326,7 @@
         <v>44742</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21444,7 +21440,7 @@
         <v>44694</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21554,7 +21550,7 @@
         <v>44515</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21664,7 +21660,7 @@
         <v>44594</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21769,7 +21765,7 @@
         <v>45223</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21879,7 +21875,7 @@
         <v>44742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21989,7 +21985,7 @@
         <v>44928</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22098,7 +22094,7 @@
         <v>44491</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22208,7 +22204,7 @@
         <v>45553</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22317,7 +22313,7 @@
         <v>45344</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22422,7 +22418,7 @@
         <v>44900</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22527,7 +22523,7 @@
         <v>45646</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22641,7 +22637,7 @@
         <v>45629</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22755,7 +22751,7 @@
         <v>45617</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22864,7 +22860,7 @@
         <v>45558</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22974,7 +22970,7 @@
         <v>45509</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23084,7 +23080,7 @@
         <v>45797</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23189,7 +23185,7 @@
         <v>45678</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23294,7 +23290,7 @@
         <v>45238</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23404,7 +23400,7 @@
         <v>45624</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23514,7 +23510,7 @@
         <v>45637</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23628,7 +23624,7 @@
         <v>44642</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23738,7 +23734,7 @@
         <v>45968</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23848,7 +23844,7 @@
         <v>45841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23953,7 +23949,7 @@
         <v>45679</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24063,7 +24059,7 @@
         <v>45867</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24173,7 +24169,7 @@
         <v>45867</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24283,7 +24279,7 @@
         <v>45685</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24388,7 +24384,7 @@
         <v>45028</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24493,7 +24489,7 @@
         <v>46120</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24598,7 +24594,7 @@
         <v>45999</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24708,7 +24704,7 @@
         <v>44785</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24817,7 +24813,7 @@
         <v>45511</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24922,7 +24918,7 @@
         <v>45559</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25032,7 +25028,7 @@
         <v>46038</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25137,7 +25133,7 @@
         <v>46051</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25242,7 +25238,7 @@
         <v>45280</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25347,7 +25343,7 @@
         <v>46142</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25457,7 +25453,7 @@
         <v>45719</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25567,7 +25563,7 @@
         <v>45763</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25672,7 +25668,7 @@
         <v>46184</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25777,7 +25773,7 @@
         <v>46190</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25882,7 +25878,7 @@
         <v>46276</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25987,7 +25983,7 @@
         <v>46295</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26092,7 +26088,7 @@
         <v>45096</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26197,7 +26193,7 @@
         <v>46125</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26302,7 +26298,7 @@
         <v>45118</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26407,7 +26403,7 @@
         <v>45957</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26521,7 +26517,7 @@
         <v>44879</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26594,7 +26590,7 @@
         <v>44510</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26667,7 +26663,7 @@
         <v>44524</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26745,7 +26741,7 @@
         <v>44838</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26823,7 +26819,7 @@
         <v>44540</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26896,7 +26892,7 @@
         <v>44613</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26969,7 +26965,7 @@
         <v>44581</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27042,7 +27038,7 @@
         <v>44852</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27115,7 +27111,7 @@
         <v>44561</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27188,7 +27184,7 @@
         <v>44566</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27261,7 +27257,7 @@
         <v>44755</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27339,7 +27335,7 @@
         <v>44852</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27412,7 +27408,7 @@
         <v>44750</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27485,7 +27481,7 @@
         <v>44540</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27558,7 +27554,7 @@
         <v>44537</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27631,7 +27627,7 @@
         <v>44517</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27704,7 +27700,7 @@
         <v>44601</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27777,7 +27773,7 @@
         <v>44722</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27855,7 +27851,7 @@
         <v>44722</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27933,7 +27929,7 @@
         <v>44540</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28006,7 +28002,7 @@
         <v>44609</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28079,7 +28075,7 @@
         <v>44721</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28152,7 +28148,7 @@
         <v>44889</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28225,7 +28221,7 @@
         <v>44845</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28298,7 +28294,7 @@
         <v>44875</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28376,7 +28372,7 @@
         <v>44886</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28474,7 +28470,7 @@
         <v>44516</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28547,7 +28543,7 @@
         <v>44655</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28620,7 +28616,7 @@
         <v>44909</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28698,7 +28694,7 @@
         <v>44704</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28776,7 +28772,7 @@
         <v>45183</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28849,7 +28845,7 @@
         <v>45057</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28927,7 +28923,7 @@
         <v>45324</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29005,7 +29001,7 @@
         <v>44952</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29078,7 +29074,7 @@
         <v>45621</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29156,7 +29152,7 @@
         <v>45702</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29229,7 +29225,7 @@
         <v>45096</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29302,7 +29298,7 @@
         <v>45338</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29375,7 +29371,7 @@
         <v>44880</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29448,7 +29444,7 @@
         <v>45370</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29521,7 +29517,7 @@
         <v>44883</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29594,7 +29590,7 @@
         <v>45261</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29672,7 +29668,7 @@
         <v>44837</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29745,7 +29741,7 @@
         <v>45677</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29818,7 +29814,7 @@
         <v>45177</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29896,7 +29892,7 @@
         <v>45632</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29969,7 +29965,7 @@
         <v>44757</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30042,7 +30038,7 @@
         <v>45315</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30115,7 +30111,7 @@
         <v>44889</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30188,7 +30184,7 @@
         <v>45089</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30261,7 +30257,7 @@
         <v>45462</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30339,7 +30335,7 @@
         <v>45336</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30412,7 +30408,7 @@
         <v>45412</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30485,7 +30481,7 @@
         <v>44911</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30558,7 +30554,7 @@
         <v>45593</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30636,7 +30632,7 @@
         <v>45223</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30709,7 +30705,7 @@
         <v>45223</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30782,7 +30778,7 @@
         <v>45012</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30855,7 +30851,7 @@
         <v>45004</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30928,7 +30924,7 @@
         <v>45236</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31001,7 +30997,7 @@
         <v>45688</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31079,7 +31075,7 @@
         <v>45588</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31157,7 +31153,7 @@
         <v>44986</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31235,7 +31231,7 @@
         <v>45593</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31313,7 +31309,7 @@
         <v>45708</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31386,7 +31382,7 @@
         <v>45096</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31459,7 +31455,7 @@
         <v>45309</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31532,7 +31528,7 @@
         <v>45625</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31605,7 +31601,7 @@
         <v>45166</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31683,7 +31679,7 @@
         <v>45435</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31756,7 +31752,7 @@
         <v>45888</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31829,7 +31825,7 @@
         <v>45800</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31902,7 +31898,7 @@
         <v>45477</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31975,7 +31971,7 @@
         <v>45012</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32048,7 +32044,7 @@
         <v>45475</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32126,7 +32122,7 @@
         <v>45002</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32204,7 +32200,7 @@
         <v>45895</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32277,7 +32273,7 @@
         <v>45895</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32350,7 +32346,7 @@
         <v>44911</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32423,7 +32419,7 @@
         <v>45667</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32501,7 +32497,7 @@
         <v>45902</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32574,7 +32570,7 @@
         <v>45902</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32647,7 +32643,7 @@
         <v>45901</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32720,7 +32716,7 @@
         <v>45159</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32793,7 +32789,7 @@
         <v>45904</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32866,7 +32862,7 @@
         <v>45264</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32939,7 +32935,7 @@
         <v>44911</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33012,7 +33008,7 @@
         <v>45660</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33085,7 +33081,7 @@
         <v>45909</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33158,7 +33154,7 @@
         <v>45092</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33231,7 +33227,7 @@
         <v>45457</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33304,7 +33300,7 @@
         <v>45306</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33377,7 +33373,7 @@
         <v>45646</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33455,7 +33451,7 @@
         <v>45646</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33533,7 +33529,7 @@
         <v>45779</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33606,7 +33602,7 @@
         <v>45911</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33679,7 +33675,7 @@
         <v>45616</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33757,7 +33753,7 @@
         <v>45916</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33830,7 +33826,7 @@
         <v>45686</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33903,7 +33899,7 @@
         <v>44529</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33976,7 +33972,7 @@
         <v>45477</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34049,7 +34045,7 @@
         <v>45328</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34122,7 +34118,7 @@
         <v>45300</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34195,7 +34191,7 @@
         <v>45922</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34273,7 +34269,7 @@
         <v>45922</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34351,7 +34347,7 @@
         <v>45922</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34429,7 +34425,7 @@
         <v>45922</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34507,7 +34503,7 @@
         <v>45922</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34585,7 +34581,7 @@
         <v>45922</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34658,7 +34654,7 @@
         <v>44599</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34731,7 +34727,7 @@
         <v>45686</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34804,7 +34800,7 @@
         <v>45686</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34877,7 +34873,7 @@
         <v>45789</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34950,7 +34946,7 @@
         <v>45924</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35028,7 +35024,7 @@
         <v>45790</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35101,7 +35097,7 @@
         <v>45924</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35179,7 +35175,7 @@
         <v>45636</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35252,7 +35248,7 @@
         <v>44609</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35325,7 +35321,7 @@
         <v>45428</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35403,7 +35399,7 @@
         <v>45561</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35481,7 +35477,7 @@
         <v>45628</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35554,7 +35550,7 @@
         <v>45634</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35627,7 +35623,7 @@
         <v>45190</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35700,7 +35696,7 @@
         <v>45588</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35773,7 +35769,7 @@
         <v>45597</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35851,7 +35847,7 @@
         <v>45583</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35924,7 +35920,7 @@
         <v>45576</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35997,7 +35993,7 @@
         <v>44680</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36070,7 +36066,7 @@
         <v>45580</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36143,7 +36139,7 @@
         <v>45634</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36216,7 +36212,7 @@
         <v>45611</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36289,7 +36285,7 @@
         <v>45799</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36362,7 +36358,7 @@
         <v>45236</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36440,7 +36436,7 @@
         <v>44564</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36513,7 +36509,7 @@
         <v>45344</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36586,7 +36582,7 @@
         <v>45803</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36664,7 +36660,7 @@
         <v>44977</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36742,7 +36738,7 @@
         <v>45681</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36820,7 +36816,7 @@
         <v>45681</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36898,7 +36894,7 @@
         <v>45221</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36971,7 +36967,7 @@
         <v>45805</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37049,7 +37045,7 @@
         <v>45587</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37122,7 +37118,7 @@
         <v>45237</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37195,7 +37191,7 @@
         <v>45691</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37273,7 +37269,7 @@
         <v>45551</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37351,7 +37347,7 @@
         <v>44655</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37424,7 +37420,7 @@
         <v>45807</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37497,7 +37493,7 @@
         <v>45937</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37575,7 +37571,7 @@
         <v>45260</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37648,7 +37644,7 @@
         <v>45691</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37726,7 +37722,7 @@
         <v>45107</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37799,7 +37795,7 @@
         <v>45762</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37877,7 +37873,7 @@
         <v>44634</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37950,7 +37946,7 @@
         <v>45221</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38023,7 +38019,7 @@
         <v>44635</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38096,7 +38092,7 @@
         <v>45944</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38174,7 +38170,7 @@
         <v>45189</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38247,7 +38243,7 @@
         <v>45615</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38320,7 +38316,7 @@
         <v>45429</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38393,7 +38389,7 @@
         <v>45547</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38466,7 +38462,7 @@
         <v>45057</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38539,7 +38535,7 @@
         <v>44735</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38612,7 +38608,7 @@
         <v>45813</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38685,7 +38681,7 @@
         <v>44706</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38758,7 +38754,7 @@
         <v>45688</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38831,7 +38827,7 @@
         <v>45818</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38909,7 +38905,7 @@
         <v>45819</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38987,7 +38983,7 @@
         <v>45709</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39065,7 +39061,7 @@
         <v>45572</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39143,7 +39139,7 @@
         <v>45707</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39216,7 +39212,7 @@
         <v>45231</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39294,7 +39290,7 @@
         <v>45600</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39372,7 +39368,7 @@
         <v>45958</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39450,7 +39446,7 @@
         <v>45460</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39523,7 +39519,7 @@
         <v>45707</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39596,7 +39592,7 @@
         <v>45659</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39669,7 +39665,7 @@
         <v>45677</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39742,7 +39738,7 @@
         <v>45964</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39820,7 +39816,7 @@
         <v>45188</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39893,7 +39889,7 @@
         <v>44743</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39966,7 +39962,7 @@
         <v>44721</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40039,7 +40035,7 @@
         <v>45721</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40112,7 +40108,7 @@
         <v>44750</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40185,7 +40181,7 @@
         <v>45321</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40258,7 +40254,7 @@
         <v>44907</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40336,7 +40332,7 @@
         <v>45692</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40409,7 +40405,7 @@
         <v>45315</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40482,7 +40478,7 @@
         <v>45847</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40560,7 +40556,7 @@
         <v>45265</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40638,7 +40634,7 @@
         <v>45847</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40716,7 +40712,7 @@
         <v>45847</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40794,7 +40790,7 @@
         <v>45667</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40872,7 +40868,7 @@
         <v>45313</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40945,7 +40941,7 @@
         <v>45800</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41018,7 +41014,7 @@
         <v>45302</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41091,7 +41087,7 @@
         <v>44799</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41164,7 +41160,7 @@
         <v>45231</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41242,7 +41238,7 @@
         <v>45866</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41320,7 +41316,7 @@
         <v>45260</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41393,7 +41389,7 @@
         <v>45691</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41466,7 +41462,7 @@
         <v>45807</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41539,7 +41535,7 @@
         <v>44970</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41617,7 +41613,7 @@
         <v>45707</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41695,7 +41691,7 @@
         <v>45770</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41768,7 +41764,7 @@
         <v>44711</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41841,7 +41837,7 @@
         <v>45273</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41914,7 +41910,7 @@
         <v>45707</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41987,7 +41983,7 @@
         <v>44533</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42060,7 +42056,7 @@
         <v>44614</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42133,7 +42129,7 @@
         <v>45505</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42211,7 +42207,7 @@
         <v>45588</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42284,7 +42280,7 @@
         <v>45985</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42357,7 +42353,7 @@
         <v>45586</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42435,7 +42431,7 @@
         <v>46098</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42508,7 +42504,7 @@
         <v>44922</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42581,7 +42577,7 @@
         <v>44790</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42654,7 +42650,7 @@
         <v>45986</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42727,7 +42723,7 @@
         <v>45985</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42800,7 +42796,7 @@
         <v>45475</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42873,7 +42869,7 @@
         <v>46097</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42951,7 +42947,7 @@
         <v>45992</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43024,7 +43020,7 @@
         <v>45987</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43097,7 +43093,7 @@
         <v>45992</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43170,7 +43166,7 @@
         <v>45992</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43243,7 +43239,7 @@
         <v>45690</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43316,7 +43312,7 @@
         <v>45342</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43394,7 +43390,7 @@
         <v>44952</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43467,7 +43463,7 @@
         <v>46125</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43540,7 +43536,7 @@
         <v>46114</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43613,7 +43609,7 @@
         <v>45993</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43686,7 +43682,7 @@
         <v>46000</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43759,7 +43755,7 @@
         <v>46000</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43832,7 +43828,7 @@
         <v>45008</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43905,7 +43901,7 @@
         <v>46126</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43983,7 +43979,7 @@
         <v>46132</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44056,7 +44052,7 @@
         <v>46133</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44134,7 +44130,7 @@
         <v>46003</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44207,7 +44203,7 @@
         <v>44889</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44285,7 +44281,7 @@
         <v>46003</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44358,7 +44354,7 @@
         <v>44875</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44431,7 +44427,7 @@
         <v>46003</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44504,7 +44500,7 @@
         <v>44949</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44577,7 +44573,7 @@
         <v>46003</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44650,7 +44646,7 @@
         <v>46003</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44723,7 +44719,7 @@
         <v>46007</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44801,7 +44797,7 @@
         <v>46007</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44874,7 +44870,7 @@
         <v>46135</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44947,7 +44943,7 @@
         <v>46010</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45020,7 +45016,7 @@
         <v>46010</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45093,7 +45089,7 @@
         <v>46136</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45171,7 +45167,7 @@
         <v>46013</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45244,7 +45240,7 @@
         <v>46139</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45322,7 +45318,7 @@
         <v>46013</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45395,7 +45391,7 @@
         <v>46019</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45468,7 +45464,7 @@
         <v>45696</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45541,7 +45537,7 @@
         <v>45239</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45619,7 +45615,7 @@
         <v>46024</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45692,7 +45688,7 @@
         <v>44721</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45770,7 +45766,7 @@
         <v>44511</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45843,7 +45839,7 @@
         <v>46029</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45916,7 +45912,7 @@
         <v>45600</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45994,7 +45990,7 @@
         <v>46139</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46072,7 +46068,7 @@
         <v>46139</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46150,7 +46146,7 @@
         <v>46034</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46223,7 +46219,7 @@
         <v>46008</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46296,7 +46292,7 @@
         <v>45112</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46369,7 +46365,7 @@
         <v>44937</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46442,7 +46438,7 @@
         <v>44679</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46515,7 +46511,7 @@
         <v>45837</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46593,7 +46589,7 @@
         <v>44986</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46671,7 +46667,7 @@
         <v>46032</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46744,7 +46740,7 @@
         <v>45520</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46817,7 +46813,7 @@
         <v>45707</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46890,7 +46886,7 @@
         <v>46038</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46963,7 +46959,7 @@
         <v>45748</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47036,7 +47032,7 @@
         <v>46037</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47109,7 +47105,7 @@
         <v>46037</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47182,7 +47178,7 @@
         <v>45223</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47255,7 +47251,7 @@
         <v>46041</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47328,7 +47324,7 @@
         <v>46029</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47401,7 +47397,7 @@
         <v>44607</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47474,7 +47470,7 @@
         <v>44742</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47547,7 +47543,7 @@
         <v>45569</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47620,7 +47616,7 @@
         <v>45639</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47698,7 +47694,7 @@
         <v>46000</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47771,7 +47767,7 @@
         <v>46045</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47849,7 +47845,7 @@
         <v>46045</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47922,7 +47918,7 @@
         <v>46050</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47995,7 +47991,7 @@
         <v>44790</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48068,7 +48064,7 @@
         <v>46056</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48141,7 +48137,7 @@
         <v>46142</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48219,7 +48215,7 @@
         <v>46066</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48297,7 +48293,7 @@
         <v>46066</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48375,7 +48371,7 @@
         <v>46150</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48448,7 +48444,7 @@
         <v>46150</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48521,7 +48517,7 @@
         <v>46070</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48599,7 +48595,7 @@
         <v>46150</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48672,7 +48668,7 @@
         <v>45691</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48745,7 +48741,7 @@
         <v>46076</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48823,7 +48819,7 @@
         <v>46073</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48896,7 +48892,7 @@
         <v>46078</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48969,7 +48965,7 @@
         <v>46153</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49042,7 +49038,7 @@
         <v>45693</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49115,7 +49111,7 @@
         <v>46078</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49188,7 +49184,7 @@
         <v>46154</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49266,7 +49262,7 @@
         <v>45722</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49344,7 +49340,7 @@
         <v>45736</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49417,7 +49413,7 @@
         <v>45743</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49490,7 +49486,7 @@
         <v>45720</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49568,7 +49564,7 @@
         <v>45720</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49646,7 +49642,7 @@
         <v>45743</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49719,7 +49715,7 @@
         <v>45978</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49792,7 +49788,7 @@
         <v>46156</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49870,7 +49866,7 @@
         <v>46091</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49943,7 +49939,7 @@
         <v>45686</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50016,7 +50012,7 @@
         <v>45887</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50089,7 +50085,7 @@
         <v>46120</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50162,7 +50158,7 @@
         <v>46164</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50240,7 +50236,7 @@
         <v>46066</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50313,7 +50309,7 @@
         <v>46163</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50386,7 +50382,7 @@
         <v>46163</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50459,7 +50455,7 @@
         <v>46164</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50537,7 +50533,7 @@
         <v>46164</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50610,7 +50606,7 @@
         <v>46164</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50688,7 +50684,7 @@
         <v>46164</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50766,7 +50762,7 @@
         <v>46164</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50844,7 +50840,7 @@
         <v>46164</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50922,7 +50918,7 @@
         <v>46164</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51000,7 +50996,7 @@
         <v>46164</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51078,7 +51074,7 @@
         <v>46164</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51151,7 +51147,7 @@
         <v>46163</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51224,7 +51220,7 @@
         <v>46175</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51302,7 +51298,7 @@
         <v>46183</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51375,7 +51371,7 @@
         <v>46184</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51448,7 +51444,7 @@
         <v>46190</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51521,7 +51517,7 @@
         <v>46190</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51594,7 +51590,7 @@
         <v>46190</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51667,7 +51663,7 @@
         <v>45763</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51740,7 +51736,7 @@
         <v>46206</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51813,7 +51809,7 @@
         <v>46216</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51891,7 +51887,7 @@
         <v>46203</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51964,7 +51960,7 @@
         <v>45939</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52042,7 +52038,7 @@
         <v>46073</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52115,7 +52111,7 @@
         <v>46220</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52188,7 +52184,7 @@
         <v>46272</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52261,7 +52257,7 @@
         <v>46269</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52339,7 +52335,7 @@
         <v>46231</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52417,7 +52413,7 @@
         <v>46231</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52495,7 +52491,7 @@
         <v>46231</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52573,7 +52569,7 @@
         <v>46231</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52651,7 +52647,7 @@
         <v>46275</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52729,7 +52725,7 @@
         <v>46275</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52802,7 +52798,7 @@
         <v>46276</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52880,7 +52876,7 @@
         <v>46279</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52953,7 +52949,7 @@
         <v>46135</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53026,7 +53022,7 @@
         <v>46280</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53104,7 +53100,7 @@
         <v>46279</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53177,7 +53173,7 @@
         <v>46279</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53250,7 +53246,7 @@
         <v>46281</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53323,7 +53319,7 @@
         <v>46239</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53396,7 +53392,7 @@
         <v>46281</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53469,7 +53465,7 @@
         <v>46282</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53547,7 +53543,7 @@
         <v>46238</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53620,7 +53616,7 @@
         <v>46241</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53693,7 +53689,7 @@
         <v>46283</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53771,7 +53767,7 @@
         <v>46241</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53844,7 +53840,7 @@
         <v>46286</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53917,7 +53913,7 @@
         <v>46287</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53995,7 +53991,7 @@
         <v>46288</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54073,7 +54069,7 @@
         <v>46132</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54146,7 +54142,7 @@
         <v>46286</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54219,7 +54215,7 @@
         <v>46289</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54292,7 +54288,7 @@
         <v>46294</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54365,7 +54361,7 @@
         <v>46248</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54438,7 +54434,7 @@
         <v>46203</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54511,7 +54507,7 @@
         <v>46206</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54584,7 +54580,7 @@
         <v>45376</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54657,7 +54653,7 @@
         <v>46180</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54730,7 +54726,7 @@
         <v>45789</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54803,7 +54799,7 @@
         <v>46300</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54876,7 +54872,7 @@
         <v>46206</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54949,7 +54945,7 @@
         <v>45954</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55022,7 +55018,7 @@
         <v>45149</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55095,7 +55091,7 @@
         <v>46014</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55168,7 +55164,7 @@
         <v>45793</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55241,7 +55237,7 @@
         <v>44922</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55314,7 +55310,7 @@
         <v>45198</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55392,7 +55388,7 @@
         <v>46301</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55465,7 +55461,7 @@
         <v>45744</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55538,7 +55534,7 @@
         <v>45820</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55611,7 +55607,7 @@
         <v>46058</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55684,7 +55680,7 @@
         <v>46058</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55757,7 +55753,7 @@
         <v>46276</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45109</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>45155</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44585</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>45540</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>45690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1963,75 +1963,209 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
+          <t>A 27881-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>26</v>
+      </c>
+      <c r="T11" t="n">
+        <v>42</v>
+      </c>
+      <c r="U11" t="n">
+        <v>42</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Björktrast
+Harticka
+Lunglav
+Rödvingetrast
+Talltita
+Tretåig hackspett
+Ullticka
+Finbräken
+Kransrams
+Luddlav
+Spindelblomster
+Stuplav
+Svart trolldruva
+Tvåblad
+Ögonpyrola
+Bergfink
+Blåsippa
+Brudborste
+Ekbräken
+Kransmossa
+Kärrfibbla
+Nordisk stormhatt
+Ormbär
+Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 27881-2026 artfynd.xlsx", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 27881-2026 karta.png", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 27881-2026 georefererad karta.tif", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 27881-2026 FSC-klagomål.docx", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 27881-2026 FSC-klagomål mail.docx", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 27881-2026 tillsynsbegäran.docx", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 27881-2026 tillsynsbegäran mail.docx", "A 27881-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 27881-2026 prioriterade fågelarter.docx", "A 27881-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>A 12943-2022</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>44642</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>10</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>7</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
         <v>9</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>9</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>2</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>12</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>3</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S12" t="n">
         <v>23</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>68</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>56</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Trolldruvemätare
 Knärot
@@ -2058,115 +2192,115 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 12943-2022 artfynd.xlsx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 12943-2022 karta.png", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 12943-2022 georefererad karta.tif", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 12943-2022 karta knärot.png", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 12943-2022 FSC-klagomål.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 12943-2022 FSC-klagomål mail.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 12943-2022 tillsynsbegäran.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 12943-2022 tillsynsbegäran mail.docx", "A 12943-2022")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 12943-2022 prioriterade fågelarter.docx", "A 12943-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 14960-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46104</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>14.8</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>8</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>7</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>7</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M13" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>9</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>2</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S13" t="n">
         <v>22</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>180</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>164</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -2192,170 +2326,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 14960-2026 artfynd.xlsx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 14960-2026 karta.png", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 14960-2026 georefererad karta.tif", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="Z12">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 14960-2026 karta knärot.png", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 14960-2026 FSC-klagomål.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 14960-2026 FSC-klagomål mail.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 14960-2026 tillsynsbegäran.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 14960-2026 tillsynsbegäran mail.docx", "A 14960-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 14960-2026 prioriterade fågelarter.docx", "A 14960-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 27881-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" t="n">
-        <v>5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>22</v>
-      </c>
-      <c r="T13" t="n">
-        <v>37</v>
-      </c>
-      <c r="U13" t="n">
-        <v>37</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Lunglav
-Rödvingetrast
-Talltita
-Tretåig hackspett
-Ullticka
-Finbräken
-Kransrams
-Luddlav
-Spindelblomster
-Stuplav
-Svart trolldruva
-Tvåblad
-Ögonpyrola
-Blåsippa
-Brudborste
-Ekbräken
-Kransmossa
-Kärrfibbla
-Nordisk stormhatt
-Ormbär
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 27881-2026 artfynd.xlsx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 27881-2026 karta.png", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor_geotiff/A 27881-2026 georefererad karta.tif", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 27881-2026 FSC-klagomål.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 27881-2026 FSC-klagomål mail.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 27881-2026 tillsynsbegäran.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 27881-2026 tillsynsbegäran mail.docx", "A 27881-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 27881-2026 prioriterade fågelarter.docx", "A 27881-2026")</f>
         <v/>
       </c>
     </row>
@@ -2379,7 +2383,7 @@
         <v>45932</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2513,7 +2517,7 @@
         <v>46108</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2642,7 +2646,7 @@
         <v>45600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2780,7 +2784,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2913,7 +2917,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3046,7 +3050,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3179,7 +3183,7 @@
         <v>46195</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3311,7 +3315,7 @@
         <v>45924</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3443,7 +3447,7 @@
         <v>46119</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3571,7 +3575,7 @@
         <v>46195</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3702,7 +3706,7 @@
         <v>45161</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3828,7 +3832,7 @@
         <v>45988</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3963,7 +3967,7 @@
         <v>45975</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4093,7 +4097,7 @@
         <v>44945</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4221,7 +4225,7 @@
         <v>46129</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4346,7 +4350,7 @@
         <v>45747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4474,7 +4478,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4603,7 +4607,7 @@
         <v>44971</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4731,7 +4735,7 @@
         <v>46119</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4858,7 +4862,7 @@
         <v>44819</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4986,7 +4990,7 @@
         <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5104,7 +5108,7 @@
         <v>45932</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5230,7 +5234,7 @@
         <v>45916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5356,7 +5360,7 @@
         <v>46044</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5473,7 +5477,7 @@
         <v>45978</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5593,7 +5597,7 @@
         <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5713,7 +5717,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5837,7 +5841,7 @@
         <v>46073</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5961,7 +5965,7 @@
         <v>45890</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6085,7 +6089,7 @@
         <v>45929</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6205,7 +6209,7 @@
         <v>46119</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6328,7 +6332,7 @@
         <v>45932</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6451,7 +6455,7 @@
         <v>46140</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6566,7 +6570,7 @@
         <v>46213</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6689,7 +6693,7 @@
         <v>45574</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6808,7 +6812,7 @@
         <v>45602</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6935,7 +6939,7 @@
         <v>45415</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7057,7 +7061,7 @@
         <v>44851</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7179,7 +7183,7 @@
         <v>45063</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7297,7 +7301,7 @@
         <v>45526</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7416,7 +7420,7 @@
         <v>45475</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7539,7 +7543,7 @@
         <v>45621</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7657,7 +7661,7 @@
         <v>46044</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7771,7 +7775,7 @@
         <v>45575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7889,7 +7893,7 @@
         <v>46195</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8011,7 +8015,7 @@
         <v>45937</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8133,7 +8137,7 @@
         <v>46042</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8251,7 +8255,7 @@
         <v>45986</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8369,7 +8373,7 @@
         <v>44637</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8482,7 +8486,7 @@
         <v>46133</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8600,7 +8604,7 @@
         <v>45649</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8717,7 +8721,7 @@
         <v>45937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8838,7 +8842,7 @@
         <v>45470</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8959,7 +8963,7 @@
         <v>45940</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9080,7 +9084,7 @@
         <v>45952</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9201,7 +9205,7 @@
         <v>45170</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9322,7 +9326,7 @@
         <v>45349</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9443,7 +9447,7 @@
         <v>45161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9563,7 +9567,7 @@
         <v>45320</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9675,7 +9679,7 @@
         <v>45897</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9792,7 +9796,7 @@
         <v>46076</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9912,7 +9916,7 @@
         <v>46119</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10028,7 +10032,7 @@
         <v>44911</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10144,7 +10148,7 @@
         <v>45198</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10260,7 +10264,7 @@
         <v>45028</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10380,7 +10384,7 @@
         <v>44945</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10500,7 +10504,7 @@
         <v>45189</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10611,7 +10615,7 @@
         <v>46073</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10730,7 +10734,7 @@
         <v>46073</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10849,7 +10853,7 @@
         <v>46043</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10964,7 +10968,7 @@
         <v>46105</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11079,7 +11083,7 @@
         <v>45936</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11198,7 +11202,7 @@
         <v>45806</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11317,7 +11321,7 @@
         <v>45975</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11432,7 +11436,7 @@
         <v>45890</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11547,7 +11551,7 @@
         <v>45953</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11666,7 +11670,7 @@
         <v>45751</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11782,7 +11786,7 @@
         <v>44929</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11896,7 +11900,7 @@
         <v>45618</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12015,7 +12019,7 @@
         <v>45809</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12129,7 +12133,7 @@
         <v>45233</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12244,7 +12248,7 @@
         <v>45762</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12359,7 +12363,7 @@
         <v>46097</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12469,7 +12473,7 @@
         <v>44840</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12579,7 +12583,7 @@
         <v>46065</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12693,7 +12697,7 @@
         <v>46006</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12812,7 +12816,7 @@
         <v>46195</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12922,7 +12926,7 @@
         <v>46008</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13036,7 +13040,7 @@
         <v>45553</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13146,7 +13150,7 @@
         <v>46059</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13264,7 +13268,7 @@
         <v>44742</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13378,7 +13382,7 @@
         <v>44623</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13487,7 +13491,7 @@
         <v>45278</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13596,7 +13600,7 @@
         <v>45349</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13710,7 +13714,7 @@
         <v>45901</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13828,7 +13832,7 @@
         <v>45349</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13946,7 +13950,7 @@
         <v>45975</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14059,7 +14063,7 @@
         <v>45897</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14173,7 +14177,7 @@
         <v>45985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14286,7 +14290,7 @@
         <v>46000</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14403,7 +14407,7 @@
         <v>45049</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14512,7 +14516,7 @@
         <v>46294</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14630,7 +14634,7 @@
         <v>46030</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14743,7 +14747,7 @@
         <v>44908</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14851,7 +14855,7 @@
         <v>45553</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14963,7 +14967,7 @@
         <v>45570</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15071,7 +15075,7 @@
         <v>45237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15188,7 +15192,7 @@
         <v>45748</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15296,7 +15300,7 @@
         <v>45462</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15404,7 +15408,7 @@
         <v>44750</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15512,7 +15516,7 @@
         <v>44853</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15624,7 +15628,7 @@
         <v>44904</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15732,7 +15736,7 @@
         <v>44977</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15845,7 +15849,7 @@
         <v>45721</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15958,7 +15962,7 @@
         <v>46098</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16066,7 +16070,7 @@
         <v>46160</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16182,7 +16186,7 @@
         <v>46279</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16295,7 +16299,7 @@
         <v>45978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16407,7 +16411,7 @@
         <v>45785</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16520,7 +16524,7 @@
         <v>46280</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16628,7 +16632,7 @@
         <v>45223</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16740,7 +16744,7 @@
         <v>44904</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16851,7 +16855,7 @@
         <v>44904</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16962,7 +16966,7 @@
         <v>45559</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17074,7 +17078,7 @@
         <v>45644</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17185,7 +17189,7 @@
         <v>44904</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17292,7 +17296,7 @@
         <v>45737</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17407,7 +17411,7 @@
         <v>45919</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17519,7 +17523,7 @@
         <v>45187</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17635,7 +17639,7 @@
         <v>45233</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17742,7 +17746,7 @@
         <v>45615</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17849,7 +17853,7 @@
         <v>45245</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17961,7 +17965,7 @@
         <v>45561</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18073,7 +18077,7 @@
         <v>46137</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18180,7 +18184,7 @@
         <v>46177</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18287,7 +18291,7 @@
         <v>46217</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18399,7 +18403,7 @@
         <v>46225</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18515,7 +18519,7 @@
         <v>46275</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18627,7 +18631,7 @@
         <v>44956</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18734,7 +18738,7 @@
         <v>46155</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18841,7 +18845,7 @@
         <v>46288</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18957,7 +18961,7 @@
         <v>45412</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19064,7 +19068,7 @@
         <v>44544</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19174,7 +19178,7 @@
         <v>45751</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19280,7 +19284,7 @@
         <v>45558</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19391,7 +19395,7 @@
         <v>44617</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19502,7 +19506,7 @@
         <v>44927</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19612,7 +19616,7 @@
         <v>45538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19718,7 +19722,7 @@
         <v>44643</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19824,7 +19828,7 @@
         <v>45321</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19930,7 +19934,7 @@
         <v>45643</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20041,7 +20045,7 @@
         <v>45441</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20156,7 +20160,7 @@
         <v>45715</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20262,7 +20266,7 @@
         <v>45987</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20368,7 +20372,7 @@
         <v>44957</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20474,7 +20478,7 @@
         <v>44956</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20580,7 +20584,7 @@
         <v>45975</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20686,7 +20690,7 @@
         <v>45952</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20792,7 +20796,7 @@
         <v>46198</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20898,7 +20902,7 @@
         <v>44916</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21004,7 +21008,7 @@
         <v>46282</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21110,7 +21114,7 @@
         <v>45533</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21216,7 +21220,7 @@
         <v>45313</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21326,7 +21330,7 @@
         <v>44742</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21440,7 +21444,7 @@
         <v>44694</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21550,7 +21554,7 @@
         <v>44515</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21660,7 +21664,7 @@
         <v>44594</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21765,7 +21769,7 @@
         <v>45223</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21875,7 +21879,7 @@
         <v>44742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21985,7 +21989,7 @@
         <v>44928</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22094,7 +22098,7 @@
         <v>44491</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22204,7 +22208,7 @@
         <v>45553</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22313,7 +22317,7 @@
         <v>45344</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22418,7 +22422,7 @@
         <v>44900</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22523,7 +22527,7 @@
         <v>45646</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22637,7 +22641,7 @@
         <v>45629</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22751,7 +22755,7 @@
         <v>45617</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22860,7 +22864,7 @@
         <v>45558</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22970,7 +22974,7 @@
         <v>45509</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23080,7 +23084,7 @@
         <v>45797</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23185,7 +23189,7 @@
         <v>45678</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23290,7 +23294,7 @@
         <v>45238</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23400,7 +23404,7 @@
         <v>45624</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23510,7 +23514,7 @@
         <v>45637</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23624,7 +23628,7 @@
         <v>44642</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23734,7 +23738,7 @@
         <v>45968</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23844,7 +23848,7 @@
         <v>45841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23949,7 +23953,7 @@
         <v>45679</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24059,7 +24063,7 @@
         <v>45867</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24169,7 +24173,7 @@
         <v>45867</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24279,7 +24283,7 @@
         <v>45685</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24384,7 +24388,7 @@
         <v>45028</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24489,7 +24493,7 @@
         <v>46120</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24594,7 +24598,7 @@
         <v>45999</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24704,7 +24708,7 @@
         <v>44785</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24813,7 +24817,7 @@
         <v>45511</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24918,7 +24922,7 @@
         <v>45559</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25028,7 +25032,7 @@
         <v>46038</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25133,7 +25137,7 @@
         <v>46051</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25238,7 +25242,7 @@
         <v>45280</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25343,7 +25347,7 @@
         <v>46142</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25453,7 +25457,7 @@
         <v>45719</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25563,7 +25567,7 @@
         <v>45763</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25668,7 +25672,7 @@
         <v>46184</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25773,7 +25777,7 @@
         <v>46190</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25878,7 +25882,7 @@
         <v>46276</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25983,7 +25987,7 @@
         <v>46295</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26088,7 +26092,7 @@
         <v>45096</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26193,7 +26197,7 @@
         <v>46125</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26298,7 +26302,7 @@
         <v>45118</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26403,7 +26407,7 @@
         <v>45957</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26517,7 +26521,7 @@
         <v>44879</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26590,7 +26594,7 @@
         <v>44510</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26663,7 +26667,7 @@
         <v>44524</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26741,7 +26745,7 @@
         <v>44838</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26819,7 +26823,7 @@
         <v>44540</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26892,7 +26896,7 @@
         <v>44613</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26965,7 +26969,7 @@
         <v>44581</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27038,7 +27042,7 @@
         <v>44852</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27111,7 +27115,7 @@
         <v>44561</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27184,7 +27188,7 @@
         <v>44566</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27257,7 +27261,7 @@
         <v>44755</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27335,7 +27339,7 @@
         <v>44852</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27408,7 +27412,7 @@
         <v>44750</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27481,7 +27485,7 @@
         <v>44540</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27554,7 +27558,7 @@
         <v>44537</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27627,7 +27631,7 @@
         <v>44517</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27700,7 +27704,7 @@
         <v>44601</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27773,7 +27777,7 @@
         <v>44722</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27851,7 +27855,7 @@
         <v>44722</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27929,7 +27933,7 @@
         <v>44540</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28002,7 +28006,7 @@
         <v>44609</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28075,7 +28079,7 @@
         <v>44721</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28148,7 +28152,7 @@
         <v>44889</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28221,7 +28225,7 @@
         <v>44845</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28294,7 +28298,7 @@
         <v>44875</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28372,7 +28376,7 @@
         <v>44886</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28470,7 +28474,7 @@
         <v>44516</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28543,7 +28547,7 @@
         <v>44655</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28616,7 +28620,7 @@
         <v>44909</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28694,7 +28698,7 @@
         <v>44704</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28772,7 +28776,7 @@
         <v>45183</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28845,7 +28849,7 @@
         <v>45057</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28923,7 +28927,7 @@
         <v>45324</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29001,7 +29005,7 @@
         <v>44952</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29074,7 +29078,7 @@
         <v>45621</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29152,7 +29156,7 @@
         <v>45702</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29225,7 +29229,7 @@
         <v>45096</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29298,7 +29302,7 @@
         <v>45338</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29371,7 +29375,7 @@
         <v>44880</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29444,7 +29448,7 @@
         <v>45370</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29517,7 +29521,7 @@
         <v>44883</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29590,7 +29594,7 @@
         <v>45261</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29668,7 +29672,7 @@
         <v>44837</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29741,7 +29745,7 @@
         <v>45677</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29814,7 +29818,7 @@
         <v>45177</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29892,7 +29896,7 @@
         <v>45632</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29965,7 +29969,7 @@
         <v>44757</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30038,7 +30042,7 @@
         <v>45315</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30111,7 +30115,7 @@
         <v>44889</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30184,7 +30188,7 @@
         <v>45089</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30257,7 +30261,7 @@
         <v>45462</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30335,7 +30339,7 @@
         <v>45336</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30408,7 +30412,7 @@
         <v>45412</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30481,7 +30485,7 @@
         <v>44911</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30554,7 +30558,7 @@
         <v>45593</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30632,7 +30636,7 @@
         <v>45223</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30705,7 +30709,7 @@
         <v>45223</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30778,7 +30782,7 @@
         <v>45012</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30851,7 +30855,7 @@
         <v>45004</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30924,7 +30928,7 @@
         <v>45236</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30997,7 +31001,7 @@
         <v>45688</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31075,7 +31079,7 @@
         <v>45588</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31153,7 +31157,7 @@
         <v>44986</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31231,7 +31235,7 @@
         <v>45593</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31309,7 +31313,7 @@
         <v>45708</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31382,7 +31386,7 @@
         <v>45096</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31455,7 +31459,7 @@
         <v>45309</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31528,7 +31532,7 @@
         <v>45625</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31601,7 +31605,7 @@
         <v>45166</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31679,7 +31683,7 @@
         <v>45435</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31752,7 +31756,7 @@
         <v>45888</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31825,7 +31829,7 @@
         <v>45800</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31898,7 +31902,7 @@
         <v>45477</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31971,7 +31975,7 @@
         <v>45012</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32044,7 +32048,7 @@
         <v>45475</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32122,7 +32126,7 @@
         <v>45002</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32200,7 +32204,7 @@
         <v>45895</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32273,7 +32277,7 @@
         <v>45895</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32346,7 +32350,7 @@
         <v>44911</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32419,7 +32423,7 @@
         <v>45667</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32497,7 +32501,7 @@
         <v>45902</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32570,7 +32574,7 @@
         <v>45902</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32643,7 +32647,7 @@
         <v>45901</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32716,7 +32720,7 @@
         <v>45159</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32789,7 +32793,7 @@
         <v>45904</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32862,7 +32866,7 @@
         <v>45264</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32935,7 +32939,7 @@
         <v>44911</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33008,7 +33012,7 @@
         <v>45660</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33081,7 +33085,7 @@
         <v>45909</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33154,7 +33158,7 @@
         <v>45092</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33227,7 +33231,7 @@
         <v>45457</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33300,7 +33304,7 @@
         <v>45306</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33373,7 +33377,7 @@
         <v>45646</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33451,7 +33455,7 @@
         <v>45646</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33529,7 +33533,7 @@
         <v>45779</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33602,7 +33606,7 @@
         <v>45911</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33675,7 +33679,7 @@
         <v>45616</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33753,7 +33757,7 @@
         <v>45916</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33826,7 +33830,7 @@
         <v>45686</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33899,7 +33903,7 @@
         <v>44529</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33972,7 +33976,7 @@
         <v>45477</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34045,7 +34049,7 @@
         <v>45328</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34118,7 +34122,7 @@
         <v>45300</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34191,7 +34195,7 @@
         <v>45922</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34269,7 +34273,7 @@
         <v>45922</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34347,7 +34351,7 @@
         <v>45922</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34425,7 +34429,7 @@
         <v>45922</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34503,7 +34507,7 @@
         <v>45922</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34581,7 +34585,7 @@
         <v>45922</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34654,7 +34658,7 @@
         <v>44599</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34727,7 +34731,7 @@
         <v>45686</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34800,7 +34804,7 @@
         <v>45686</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34873,7 +34877,7 @@
         <v>45789</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34946,7 +34950,7 @@
         <v>45924</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35024,7 +35028,7 @@
         <v>45790</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35097,7 +35101,7 @@
         <v>45924</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35175,7 +35179,7 @@
         <v>45636</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35248,7 +35252,7 @@
         <v>44609</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35321,7 +35325,7 @@
         <v>45428</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35399,7 +35403,7 @@
         <v>45561</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35477,7 +35481,7 @@
         <v>45628</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35550,7 +35554,7 @@
         <v>45634</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35623,7 +35627,7 @@
         <v>45190</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35696,7 +35700,7 @@
         <v>45588</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35769,7 +35773,7 @@
         <v>45597</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35847,7 +35851,7 @@
         <v>45583</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35920,7 +35924,7 @@
         <v>45576</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35993,7 +35997,7 @@
         <v>44680</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36066,7 +36070,7 @@
         <v>45580</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36139,7 +36143,7 @@
         <v>45634</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36212,7 +36216,7 @@
         <v>45611</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36285,7 +36289,7 @@
         <v>45799</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36358,7 +36362,7 @@
         <v>45236</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36436,7 +36440,7 @@
         <v>44564</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36509,7 +36513,7 @@
         <v>45344</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36582,7 +36586,7 @@
         <v>45803</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36660,7 +36664,7 @@
         <v>44977</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36738,7 +36742,7 @@
         <v>45681</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36816,7 +36820,7 @@
         <v>45681</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36894,7 +36898,7 @@
         <v>45221</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36967,7 +36971,7 @@
         <v>45805</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37045,7 +37049,7 @@
         <v>45587</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37118,7 +37122,7 @@
         <v>45237</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37191,7 +37195,7 @@
         <v>45691</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37269,7 +37273,7 @@
         <v>45551</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37347,7 +37351,7 @@
         <v>44655</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37420,7 +37424,7 @@
         <v>45807</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37493,7 +37497,7 @@
         <v>45937</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37571,7 +37575,7 @@
         <v>45260</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37644,7 +37648,7 @@
         <v>45691</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37722,7 +37726,7 @@
         <v>45107</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37795,7 +37799,7 @@
         <v>45762</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37873,7 +37877,7 @@
         <v>44634</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37946,7 +37950,7 @@
         <v>45221</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38019,7 +38023,7 @@
         <v>44635</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38092,7 +38096,7 @@
         <v>45944</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38170,7 +38174,7 @@
         <v>45189</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38243,7 +38247,7 @@
         <v>45615</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38316,7 +38320,7 @@
         <v>45429</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38389,7 +38393,7 @@
         <v>45547</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38462,7 +38466,7 @@
         <v>45057</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38535,7 +38539,7 @@
         <v>44735</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38608,7 +38612,7 @@
         <v>45813</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38681,7 +38685,7 @@
         <v>44706</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38754,7 +38758,7 @@
         <v>45688</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38827,7 +38831,7 @@
         <v>45818</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38905,7 +38909,7 @@
         <v>45819</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38983,7 +38987,7 @@
         <v>45709</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39061,7 +39065,7 @@
         <v>45572</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39139,7 +39143,7 @@
         <v>45707</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39212,7 +39216,7 @@
         <v>45231</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39290,7 +39294,7 @@
         <v>45600</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39368,7 +39372,7 @@
         <v>45958</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39446,7 +39450,7 @@
         <v>45460</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39519,7 +39523,7 @@
         <v>45707</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39592,7 +39596,7 @@
         <v>45659</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39665,7 +39669,7 @@
         <v>45677</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39738,7 +39742,7 @@
         <v>45964</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39816,7 +39820,7 @@
         <v>45188</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39889,7 +39893,7 @@
         <v>44743</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39962,7 +39966,7 @@
         <v>44721</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40035,7 +40039,7 @@
         <v>45721</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40108,7 +40112,7 @@
         <v>44750</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40181,7 +40185,7 @@
         <v>45321</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40254,7 +40258,7 @@
         <v>44907</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40332,7 +40336,7 @@
         <v>45692</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40405,7 +40409,7 @@
         <v>45315</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40478,7 +40482,7 @@
         <v>45847</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40556,7 +40560,7 @@
         <v>45265</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40634,7 +40638,7 @@
         <v>45847</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40712,7 +40716,7 @@
         <v>45847</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40790,7 +40794,7 @@
         <v>45667</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40868,7 +40872,7 @@
         <v>45313</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40941,7 +40945,7 @@
         <v>45800</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41014,7 +41018,7 @@
         <v>45302</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41087,7 +41091,7 @@
         <v>44799</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41160,7 +41164,7 @@
         <v>45231</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41238,7 +41242,7 @@
         <v>45866</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41316,7 +41320,7 @@
         <v>45260</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41389,7 +41393,7 @@
         <v>45691</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41462,7 +41466,7 @@
         <v>45807</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41535,7 +41539,7 @@
         <v>44970</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41613,7 +41617,7 @@
         <v>45707</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41691,7 +41695,7 @@
         <v>45770</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41764,7 +41768,7 @@
         <v>44711</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41837,7 +41841,7 @@
         <v>45273</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41910,7 +41914,7 @@
         <v>45707</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41983,7 +41987,7 @@
         <v>44533</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42056,7 +42060,7 @@
         <v>44614</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42129,7 +42133,7 @@
         <v>45505</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42207,7 +42211,7 @@
         <v>45588</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42280,7 +42284,7 @@
         <v>45985</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42353,7 +42357,7 @@
         <v>45586</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42431,7 +42435,7 @@
         <v>46098</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42504,7 +42508,7 @@
         <v>44922</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42577,7 +42581,7 @@
         <v>44790</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42650,7 +42654,7 @@
         <v>45986</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42723,7 +42727,7 @@
         <v>45985</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42796,7 +42800,7 @@
         <v>45475</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42869,7 +42873,7 @@
         <v>46097</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42947,7 +42951,7 @@
         <v>45992</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43020,7 +43024,7 @@
         <v>45987</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43093,7 +43097,7 @@
         <v>45992</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43166,7 +43170,7 @@
         <v>45992</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43239,7 +43243,7 @@
         <v>45690</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43312,7 +43316,7 @@
         <v>45342</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43390,7 +43394,7 @@
         <v>44952</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43463,7 +43467,7 @@
         <v>46125</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43536,7 +43540,7 @@
         <v>46114</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43609,7 +43613,7 @@
         <v>45993</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43682,7 +43686,7 @@
         <v>46000</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43755,7 +43759,7 @@
         <v>46000</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43828,7 +43832,7 @@
         <v>45008</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43901,7 +43905,7 @@
         <v>46126</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43979,7 +43983,7 @@
         <v>46132</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44052,7 +44056,7 @@
         <v>46133</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44130,7 +44134,7 @@
         <v>46003</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44203,7 +44207,7 @@
         <v>44889</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44281,7 +44285,7 @@
         <v>46003</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44354,7 +44358,7 @@
         <v>44875</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44427,7 +44431,7 @@
         <v>46003</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44500,7 +44504,7 @@
         <v>44949</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44573,7 +44577,7 @@
         <v>46003</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44646,7 +44650,7 @@
         <v>46003</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44719,7 +44723,7 @@
         <v>46007</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44797,7 +44801,7 @@
         <v>46007</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44870,7 +44874,7 @@
         <v>46135</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44943,7 +44947,7 @@
         <v>46010</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45016,7 +45020,7 @@
         <v>46010</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45089,7 +45093,7 @@
         <v>46136</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45167,7 +45171,7 @@
         <v>46013</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45240,7 +45244,7 @@
         <v>46139</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45318,7 +45322,7 @@
         <v>46013</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45391,7 +45395,7 @@
         <v>46019</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45464,7 +45468,7 @@
         <v>45696</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45537,7 +45541,7 @@
         <v>45239</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45615,7 +45619,7 @@
         <v>46024</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45688,7 +45692,7 @@
         <v>44721</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45766,7 +45770,7 @@
         <v>44511</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45839,7 +45843,7 @@
         <v>46029</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45912,7 +45916,7 @@
         <v>45600</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45990,7 +45994,7 @@
         <v>46139</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46068,7 +46072,7 @@
         <v>46139</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46146,7 +46150,7 @@
         <v>46034</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46219,7 +46223,7 @@
         <v>46008</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46292,7 +46296,7 @@
         <v>45112</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46365,7 +46369,7 @@
         <v>44937</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46438,7 +46442,7 @@
         <v>44679</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46511,7 +46515,7 @@
         <v>45837</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46589,7 +46593,7 @@
         <v>44986</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46667,7 +46671,7 @@
         <v>46032</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46740,7 +46744,7 @@
         <v>45520</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46813,7 +46817,7 @@
         <v>45707</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46886,7 +46890,7 @@
         <v>46038</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46959,7 +46963,7 @@
         <v>45748</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47032,7 +47036,7 @@
         <v>46037</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47105,7 +47109,7 @@
         <v>46037</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47178,7 +47182,7 @@
         <v>45223</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47251,7 +47255,7 @@
         <v>46041</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47324,7 +47328,7 @@
         <v>46029</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47397,7 +47401,7 @@
         <v>44607</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47470,7 +47474,7 @@
         <v>44742</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47543,7 +47547,7 @@
         <v>45569</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47616,7 +47620,7 @@
         <v>45639</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47694,7 +47698,7 @@
         <v>46000</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47767,7 +47771,7 @@
         <v>46045</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47845,7 +47849,7 @@
         <v>46045</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47918,7 +47922,7 @@
         <v>46050</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47991,7 +47995,7 @@
         <v>44790</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48064,7 +48068,7 @@
         <v>46056</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48137,7 +48141,7 @@
         <v>46142</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48215,7 +48219,7 @@
         <v>46066</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48293,7 +48297,7 @@
         <v>46066</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48371,7 +48375,7 @@
         <v>46150</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48444,7 +48448,7 @@
         <v>46150</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48517,7 +48521,7 @@
         <v>46070</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48595,7 +48599,7 @@
         <v>46150</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48668,7 +48672,7 @@
         <v>45691</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48741,7 +48745,7 @@
         <v>46076</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48819,7 +48823,7 @@
         <v>46073</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48892,7 +48896,7 @@
         <v>46078</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48965,7 +48969,7 @@
         <v>46153</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49038,7 +49042,7 @@
         <v>45693</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49111,7 +49115,7 @@
         <v>46078</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49184,7 +49188,7 @@
         <v>46154</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49262,7 +49266,7 @@
         <v>45722</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49340,7 +49344,7 @@
         <v>45736</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49413,7 +49417,7 @@
         <v>45743</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49486,7 +49490,7 @@
         <v>45720</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49564,7 +49568,7 @@
         <v>45720</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49642,7 +49646,7 @@
         <v>45743</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49715,7 +49719,7 @@
         <v>45978</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49788,7 +49792,7 @@
         <v>46156</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49866,7 +49870,7 @@
         <v>46091</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49939,7 +49943,7 @@
         <v>45686</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50012,7 +50016,7 @@
         <v>45887</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50085,7 +50089,7 @@
         <v>46120</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50158,7 +50162,7 @@
         <v>46164</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50236,7 +50240,7 @@
         <v>46066</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50309,7 +50313,7 @@
         <v>46163</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50382,7 +50386,7 @@
         <v>46163</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50455,7 +50459,7 @@
         <v>46164</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50533,7 +50537,7 @@
         <v>46164</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50606,7 +50610,7 @@
         <v>46164</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50684,7 +50688,7 @@
         <v>46164</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50762,7 +50766,7 @@
         <v>46164</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50840,7 +50844,7 @@
         <v>46164</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50918,7 +50922,7 @@
         <v>46164</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50996,7 +51000,7 @@
         <v>46164</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51074,7 +51078,7 @@
         <v>46164</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51147,7 +51151,7 @@
         <v>46163</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51220,7 +51224,7 @@
         <v>46175</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51298,7 +51302,7 @@
         <v>46183</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51371,7 +51375,7 @@
         <v>46184</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51444,7 +51448,7 @@
         <v>46190</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51517,7 +51521,7 @@
         <v>46190</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51590,7 +51594,7 @@
         <v>46190</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51663,7 +51667,7 @@
         <v>45763</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51736,7 +51740,7 @@
         <v>46206</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51809,7 +51813,7 @@
         <v>46216</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51887,7 +51891,7 @@
         <v>46203</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51960,7 +51964,7 @@
         <v>45939</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52038,7 +52042,7 @@
         <v>46073</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52111,7 +52115,7 @@
         <v>46220</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52184,7 +52188,7 @@
         <v>46272</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52257,7 +52261,7 @@
         <v>46269</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52335,7 +52339,7 @@
         <v>46231</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52413,7 +52417,7 @@
         <v>46231</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52491,7 +52495,7 @@
         <v>46231</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52569,7 +52573,7 @@
         <v>46231</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52647,7 +52651,7 @@
         <v>46275</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52725,7 +52729,7 @@
         <v>46275</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52798,7 +52802,7 @@
         <v>46276</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52876,7 +52880,7 @@
         <v>46279</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52949,7 +52953,7 @@
         <v>46135</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53022,7 +53026,7 @@
         <v>46280</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53100,7 +53104,7 @@
         <v>46279</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53173,7 +53177,7 @@
         <v>46279</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53246,7 +53250,7 @@
         <v>46281</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53319,7 +53323,7 @@
         <v>46239</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53392,7 +53396,7 @@
         <v>46281</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53465,7 +53469,7 @@
         <v>46282</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53543,7 +53547,7 @@
         <v>46238</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53616,7 +53620,7 @@
         <v>46241</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53689,7 +53693,7 @@
         <v>46283</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53767,7 +53771,7 @@
         <v>46241</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53840,7 +53844,7 @@
         <v>46286</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53913,7 +53917,7 @@
         <v>46287</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53991,7 +53995,7 @@
         <v>46288</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54069,7 +54073,7 @@
         <v>46132</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54142,7 +54146,7 @@
         <v>46286</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54215,7 +54219,7 @@
         <v>46289</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54288,7 +54292,7 @@
         <v>46294</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54361,7 +54365,7 @@
         <v>46248</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54434,7 +54438,7 @@
         <v>46203</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54507,7 +54511,7 @@
         <v>46206</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54580,7 +54584,7 @@
         <v>45376</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54653,7 +54657,7 @@
         <v>46180</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54726,7 +54730,7 @@
         <v>45789</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54799,7 +54803,7 @@
         <v>46300</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54872,7 +54876,7 @@
         <v>46206</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54945,7 +54949,7 @@
         <v>45954</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55018,7 +55022,7 @@
         <v>45149</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55091,7 +55095,7 @@
         <v>46014</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55164,7 +55168,7 @@
         <v>45793</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55237,7 +55241,7 @@
         <v>44922</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55310,7 +55314,7 @@
         <v>45198</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55388,7 +55392,7 @@
         <v>46301</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55461,7 +55465,7 @@
         <v>45744</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55534,7 +55538,7 @@
         <v>45820</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55607,7 +55611,7 @@
         <v>46058</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55680,7 +55684,7 @@
         <v>46058</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55753,7 +55757,7 @@
         <v>46276</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45109</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>45155</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44585</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>45540</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>45690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>46191</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44642</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>46104</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45932</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>46108</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>46195</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45924</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>46119</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>46195</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45988</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45975</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>46280</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>46129</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44945</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>45747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>45376</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44971</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>46119</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>44819</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45112</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>45932</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45916</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>46044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>45978</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>46073</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>46010</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>45890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>45929</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>46119</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>45932</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>46140</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>46213</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>45602</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>45475</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>45063</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45575</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>45415</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>45574</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>46195</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>44851</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>45937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>46042</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>45526</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>45621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>46044</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>45986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>45649</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44637</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>45470</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45940</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>46133</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45952</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>46076</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45897</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>46119</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45170</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45349</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>45161</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>44911</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>45320</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45189</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44945</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>46073</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>46073</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45198</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45028</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45936</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>46043</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>46105</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45806</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45953</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45890</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>45975</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>45751</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45762</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>44929</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45618</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>44840</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>46006</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>46097</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>46195</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>46065</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>46008</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45233</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45553</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>46059</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45809</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>44623</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44742</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45349</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45901</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>45975</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>45897</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45278</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45349</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>46000</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>45985</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>45049</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>46294</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>46030</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>45237</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>45748</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>46098</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>46160</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>44904</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>44977</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44908</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>44750</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44853</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>45721</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>46279</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45553</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45570</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45462</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45785</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>45187</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45245</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>46137</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>44904</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>45919</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44904</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45644</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>46177</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45559</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45561</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45223</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>46217</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>46225</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>46275</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>44956</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>46155</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>46288</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18547,7 +18547,7 @@
         <v>45233</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>45615</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>45737</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>44904</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45412</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>44544</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44957</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45643</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45321</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45952</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>44617</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>44927</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45751</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45987</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45975</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>45558</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>46198</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44916</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>44956</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45441</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>46282</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45715</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44643</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45533</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45538</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>44694</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44515</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>44742</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45313</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>44594</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>44642</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45238</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45637</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45685</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>46038</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45511</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>45280</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>46142</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>45679</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>45344</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45617</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>45509</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45646</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45553</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>44900</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>45968</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44785</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>45629</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45999</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>45678</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45624</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>46051</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>46184</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45719</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45763</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>46190</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>45223</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>46120</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>45559</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44491</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44928</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>46276</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45028</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>46295</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>45096</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45118</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>46125</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45797</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45558</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45841</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45867</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45867</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45957</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>44879</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>44510</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>44524</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>44838</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>44540</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>44613</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44581</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44852</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>44561</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44566</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>44755</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44852</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>44540</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44537</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>44609</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44889</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44516</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44875</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>44886</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>44750</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>44517</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>44601</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>44722</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44722</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44721</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>44845</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44540</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>44655</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>44704</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45273</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45634</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>44799</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44599</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44875</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45189</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>45505</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>44607</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44911</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>44706</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>45721</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>45667</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45588</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>45569</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>45315</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>45621</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45457</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44634</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45600</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45691</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44911</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>45221</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>44837</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44909</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45336</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>44977</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>44711</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>44529</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>44655</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>45321</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>44970</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         <v>45659</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45188</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45004</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>44743</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45309</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45107</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45261</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>45089</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44742</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45223</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46029</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45231</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>46136</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45520</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45707</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45691</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45625</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>46139</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>46008</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>45888</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45800</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45895</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45895</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45681</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>45681</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>46139</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>46139</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45190</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>45696</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45688</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>45837</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>45901</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>44790</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33477,7 +33477,7 @@
         <v>45342</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>45902</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>45902</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45904</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45909</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45338</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45911</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>46142</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>44949</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>45632</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45916</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44790</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>44511</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>45922</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>45922</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>45922</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>45300</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>45922</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45922</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45922</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>45924</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>45924</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45588</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45576</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>45580</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>46153</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>45583</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45265</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>46150</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45937</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>45586</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>46150</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>46150</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>45096</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45412</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>45944</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>45646</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>45646</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>45708</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>45691</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>45707</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45693</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>45264</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>46154</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45958</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>44889</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>46156</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>45887</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>46120</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>45686</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45012</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45964</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45112</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>45667</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45475</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>45593</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45593</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>46163</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>46163</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45597</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45688</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>46163</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>46066</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38206,7 +38206,7 @@
         <v>46164</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38284,7 +38284,7 @@
         <v>45634</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>46164</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45002</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>46164</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>46164</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>45985</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>46164</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>46164</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>46164</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>46164</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>45985</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>46164</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>45986</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>46164</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45987</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44952</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>45992</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39565,7 +39565,7 @@
         <v>45992</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39638,7 +39638,7 @@
         <v>45992</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         <v>45177</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>44907</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>44750</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>45993</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>46000</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         <v>46000</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>46003</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>46003</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>46003</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40378,7 +40378,7 @@
         <v>46003</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>46003</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>46007</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>46007</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>45012</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>46010</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40821,7 +40821,7 @@
         <v>46010</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>46013</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>45302</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>46013</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>46019</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>44911</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>46024</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>44721</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41405,7 +41405,7 @@
         <v>45616</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
         <v>46029</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44680</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>46034</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>46175</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>46037</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41853,7 +41853,7 @@
         <v>46032</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>45707</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>46037</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>45748</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>46038</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>46041</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45239</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>46045</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>46045</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>46050</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>45628</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>46056</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42739,7 +42739,7 @@
         <v>45428</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>46184</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>45092</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45709</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>46183</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>46066</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>46066</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>46070</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>46073</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>46078</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43494,7 +43494,7 @@
         <v>46078</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>46076</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>45720</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>45743</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45722</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45978</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45736</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>45743</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45720</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>46190</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>46190</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45770</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45547</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44463,7 +44463,7 @@
         <v>46190</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>46091</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44609,7 +44609,7 @@
         <v>46098</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>45344</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45588</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>45600</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>45763</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>45260</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45260</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>44880</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>46097</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45281,7 +45281,7 @@
         <v>45707</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45359,7 +45359,7 @@
         <v>46114</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45432,7 +45432,7 @@
         <v>45462</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>46125</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>44609</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>46126</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45734,7 +45734,7 @@
         <v>44635</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>46133</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>45677</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45958,7 +45958,7 @@
         <v>46132</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>46135</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45435</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         <v>45057</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45475</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>46000</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>46206</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45221</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>45315</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45477</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46688,7 +46688,7 @@
         <v>45166</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45236</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>46216</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>45677</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>44922</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45057</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>46073</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>44986</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45939</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>46220</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>44735</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45183</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>46203</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>44757</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>45237</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>46272</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>44883</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>45370</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>45159</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>46275</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>45572</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>46231</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45762</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>46231</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>46231</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48568,7 +48568,7 @@
         <v>46231</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>46275</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>46135</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48797,7 +48797,7 @@
         <v>46279</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>46279</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48943,7 +48943,7 @@
         <v>46276</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>44679</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>46279</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>46280</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49245,7 +49245,7 @@
         <v>45223</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49318,7 +49318,7 @@
         <v>46281</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>46281</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>45223</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>46238</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45236</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>46239</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>46283</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>46241</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45477</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45008</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50053,7 +50053,7 @@
         <v>46282</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>46241</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>45660</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>45639</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>44721</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50433,7 +50433,7 @@
         <v>45096</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>44614</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>46286</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50652,7 +50652,7 @@
         <v>44986</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50730,7 +50730,7 @@
         <v>45231</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>46287</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50886,7 +50886,7 @@
         <v>45707</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>45324</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51037,7 +51037,7 @@
         <v>46286</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>46132</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>46288</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51261,7 +51261,7 @@
         <v>44533</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>46289</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>44952</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51480,7 +51480,7 @@
         <v>44937</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45429</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>45702</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51699,7 +51699,7 @@
         <v>46248</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45690</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51845,7 +51845,7 @@
         <v>45313</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45460</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45615</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>45306</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>44889</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>46294</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>46203</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52356,7 +52356,7 @@
         <v>45789</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52429,7 +52429,7 @@
         <v>44922</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52502,7 +52502,7 @@
         <v>45328</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>45793</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52648,7 +52648,7 @@
         <v>46206</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45954</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>46014</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52867,7 +52867,7 @@
         <v>46206</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52940,7 +52940,7 @@
         <v>45149</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53013,7 +53013,7 @@
         <v>45376</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>44564</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45636</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53232,7 +53232,7 @@
         <v>45198</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>45692</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53383,7 +53383,7 @@
         <v>45779</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53456,7 +53456,7 @@
         <v>46300</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>46180</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53602,7 +53602,7 @@
         <v>45686</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45686</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         <v>45686</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>45789</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>46301</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>45790</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54040,7 +54040,7 @@
         <v>45561</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>45611</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54191,7 +54191,7 @@
         <v>45799</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54264,7 +54264,7 @@
         <v>45803</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54342,7 +54342,7 @@
         <v>46307</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54415,7 +54415,7 @@
         <v>46309</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45805</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>46309</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>45587</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>45691</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54795,7 +54795,7 @@
         <v>45807</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54868,7 +54868,7 @@
         <v>45551</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>45813</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55019,7 +55019,7 @@
         <v>45819</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>45818</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55175,7 +55175,7 @@
         <v>46269</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55253,7 +55253,7 @@
         <v>45847</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>45847</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55409,7 +55409,7 @@
         <v>45847</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45800</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55560,7 +55560,7 @@
         <v>45807</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55633,7 +55633,7 @@
         <v>45866</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45744</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55784,7 +55784,7 @@
         <v>45820</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55857,7 +55857,7 @@
         <v>46058</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55930,7 +55930,7 @@
         <v>46058</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56003,7 +56003,7 @@
         <v>46276</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45109</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>45155</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44585</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>45540</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>45690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>46191</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44642</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>46104</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45932</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>46108</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>46195</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45924</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>46119</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>46195</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45988</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45975</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>46280</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>46129</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44945</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>45747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>45376</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44971</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>46119</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>44819</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45112</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>45932</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45916</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>46044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>45978</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>46073</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>46010</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>45890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>45929</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>46119</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>45932</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>46140</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>46213</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>45602</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>45475</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>45063</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45575</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>45415</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>45574</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>46195</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>44851</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>45937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>46042</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>45526</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>45621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>46044</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>45986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>45649</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44637</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>45470</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45940</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>46133</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45952</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>46076</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45897</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>46119</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45170</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45349</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>45161</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>44911</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>45320</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45189</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44945</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>46073</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>46073</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45198</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45028</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45936</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>46043</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>46105</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45806</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45953</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45890</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>45975</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>45751</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45762</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>44929</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45618</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>44840</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>46006</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>46097</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>46195</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>46065</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>46008</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45233</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45553</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>46059</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45809</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>44623</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44742</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45349</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45901</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>45975</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>45897</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45278</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45349</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>46000</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>45985</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>45049</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>46294</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>46030</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>45237</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>45748</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>46098</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>46160</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>44904</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>44977</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44908</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>44750</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44853</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>45721</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>46279</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45553</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45570</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45462</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45785</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>45187</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45245</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>46137</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>44904</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>45919</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44904</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45644</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>46177</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45559</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45561</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45223</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>46217</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>46225</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>46275</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>44956</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>46155</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>46288</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18547,7 +18547,7 @@
         <v>45233</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>45615</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>45737</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>44904</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45412</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>44544</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44957</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45643</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45321</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45952</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>44617</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>44927</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45751</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45987</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45975</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>45558</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>46198</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44916</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>44956</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45441</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>46282</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45715</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44643</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45533</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45538</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>44694</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44515</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>44742</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45313</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>44594</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>44642</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45238</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45637</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45685</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>46038</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45511</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>45280</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>46142</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>45679</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>45344</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45617</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>45509</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45646</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45553</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>44900</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>45968</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44785</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>45629</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45999</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>45678</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45624</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>46051</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>46184</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45719</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45763</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>46190</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>45223</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>46120</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>45559</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44491</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44928</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>46276</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45028</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>46295</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>45096</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45118</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         <v>46125</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45797</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45558</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45841</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45867</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45867</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45957</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>44879</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>44510</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>44524</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>44838</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>44540</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>44613</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44581</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44852</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>44561</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44566</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>44755</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44852</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>44540</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44537</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>44609</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44889</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44516</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44875</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>44886</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>44750</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>44517</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>44601</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>44722</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44722</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44721</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>44845</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44540</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>44655</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>44704</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45273</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45634</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>44799</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44599</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>44875</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45189</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>45505</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>44607</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44911</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>44706</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>45721</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>45667</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45588</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>45569</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>45315</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>45621</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45457</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44634</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45600</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45691</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44911</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>45221</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>44837</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44909</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45336</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>44977</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>44711</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>44529</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>44655</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>45321</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>44970</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         <v>45659</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45188</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45004</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>44743</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45309</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45107</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45261</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>45089</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>44742</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45223</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46029</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45231</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>46136</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45520</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45707</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45691</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45625</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>46139</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>46008</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>45888</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45800</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45895</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45895</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45681</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>45681</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>46139</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>46139</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45190</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>45696</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45688</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>45837</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>45901</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>44790</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33477,7 +33477,7 @@
         <v>45342</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>45902</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>45902</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45904</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45909</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45338</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45911</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>46142</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>44949</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>45632</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45916</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44790</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>44511</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>45922</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>45922</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>45922</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>45300</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>45922</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45922</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45922</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>45924</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>45924</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45588</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45576</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>45580</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>46153</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>45583</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45265</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>46150</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45937</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>45586</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>46150</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>46150</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>45096</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45412</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>45944</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>45646</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>45646</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>45708</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>45691</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>45707</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45693</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>45264</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>46154</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45958</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>44889</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>46156</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>45887</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>46120</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>45686</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45012</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45964</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45112</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>45667</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45475</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>45593</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45593</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>46163</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>46163</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45597</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45688</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>46163</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>46066</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38206,7 +38206,7 @@
         <v>46164</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38284,7 +38284,7 @@
         <v>45634</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>46164</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45002</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>46164</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>46164</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>45985</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>46164</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>46164</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>46164</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>46164</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>45985</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>46164</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>45986</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>46164</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45987</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44952</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>45992</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39565,7 +39565,7 @@
         <v>45992</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39638,7 +39638,7 @@
         <v>45992</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         <v>45177</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>44907</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>44750</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>45993</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>46000</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         <v>46000</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>46003</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>46003</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>46003</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40378,7 +40378,7 @@
         <v>46003</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>46003</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>46007</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>46007</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>45012</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>46010</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40821,7 +40821,7 @@
         <v>46010</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>46013</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>45302</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>46013</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>46019</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>44911</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>46024</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>44721</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41405,7 +41405,7 @@
         <v>45616</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
         <v>46029</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44680</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>46034</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>46175</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>46037</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41853,7 +41853,7 @@
         <v>46032</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>45707</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>46037</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>45748</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>46038</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>46041</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45239</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>46045</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>46045</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>46050</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>45628</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>46056</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42739,7 +42739,7 @@
         <v>45428</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>46184</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>45092</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45709</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>46183</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>46066</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>46066</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>46070</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>46073</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>46078</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43494,7 +43494,7 @@
         <v>46078</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>46076</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>45720</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>45743</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45722</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45978</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45736</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>45743</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45720</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>46190</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>46190</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45770</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45547</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44463,7 +44463,7 @@
         <v>46190</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>46091</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44609,7 +44609,7 @@
         <v>46098</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>45344</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45588</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>45600</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>45763</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>45260</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45260</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>44880</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>46097</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45281,7 +45281,7 @@
         <v>45707</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45359,7 +45359,7 @@
         <v>46114</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45432,7 +45432,7 @@
         <v>45462</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>46125</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>44609</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>46126</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45734,7 +45734,7 @@
         <v>44635</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>46133</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>45677</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45958,7 +45958,7 @@
         <v>46132</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>46135</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45435</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         <v>45057</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45475</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>46000</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>46206</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45221</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>45315</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45477</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46688,7 +46688,7 @@
         <v>45166</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45236</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>46216</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>45677</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>44922</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45057</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>46073</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>44986</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45939</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>46220</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>44735</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45183</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>46203</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>44757</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>45237</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>46272</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>44883</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>45370</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>45159</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>46275</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>45572</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>46231</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45762</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>46231</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>46231</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48568,7 +48568,7 @@
         <v>46231</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>46275</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>46135</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48797,7 +48797,7 @@
         <v>46279</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>46279</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48943,7 +48943,7 @@
         <v>46276</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>44679</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>46279</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>46280</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49245,7 +49245,7 @@
         <v>45223</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49318,7 +49318,7 @@
         <v>46281</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>46281</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>45223</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>46238</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45236</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>46239</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>46283</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>46241</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45477</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45008</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50053,7 +50053,7 @@
         <v>46282</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>46241</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>45660</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>45639</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>44721</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50433,7 +50433,7 @@
         <v>45096</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>44614</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>46286</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50652,7 +50652,7 @@
         <v>44986</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50730,7 +50730,7 @@
         <v>45231</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>46287</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50886,7 +50886,7 @@
         <v>45707</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>45324</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51037,7 +51037,7 @@
         <v>46286</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>46132</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>46288</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51261,7 +51261,7 @@
         <v>44533</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>46289</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>44952</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51480,7 +51480,7 @@
         <v>44937</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45429</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>45702</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51699,7 +51699,7 @@
         <v>46248</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45690</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51845,7 +51845,7 @@
         <v>45313</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45460</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45615</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>45306</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>44889</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>46294</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>46203</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52356,7 +52356,7 @@
         <v>45789</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52429,7 +52429,7 @@
         <v>44922</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52502,7 +52502,7 @@
         <v>45328</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>45793</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52648,7 +52648,7 @@
         <v>46206</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45954</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>46014</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52867,7 +52867,7 @@
         <v>46206</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52940,7 +52940,7 @@
         <v>45149</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53013,7 +53013,7 @@
         <v>45376</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>44564</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45636</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53232,7 +53232,7 @@
         <v>45198</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>45692</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53383,7 +53383,7 @@
         <v>45779</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53456,7 +53456,7 @@
         <v>46300</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>46180</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53602,7 +53602,7 @@
         <v>45686</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45686</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         <v>45686</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>45789</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>46301</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>45790</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54040,7 +54040,7 @@
         <v>45561</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>45611</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54191,7 +54191,7 @@
         <v>45799</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54264,7 +54264,7 @@
         <v>45803</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54342,7 +54342,7 @@
         <v>46307</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54415,7 +54415,7 @@
         <v>46309</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45805</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>46309</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>45587</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>45691</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54795,7 +54795,7 @@
         <v>45807</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54868,7 +54868,7 @@
         <v>45551</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>45813</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55019,7 +55019,7 @@
         <v>45819</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>45818</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55175,7 +55175,7 @@
         <v>46269</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55253,7 +55253,7 @@
         <v>45847</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>45847</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55409,7 +55409,7 @@
         <v>45847</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45800</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55560,7 +55560,7 @@
         <v>45807</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55633,7 +55633,7 @@
         <v>45866</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45744</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55784,7 +55784,7 @@
         <v>45820</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55857,7 +55857,7 @@
         <v>46058</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55930,7 +55930,7 @@
         <v>46058</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56003,7 +56003,7 @@
         <v>46276</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45109</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>45155</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44585</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>45540</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>45690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>46191</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>44642</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46104</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45932</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>46108</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>45600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>46195</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>45924</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>46140</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>46195</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>46119</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45975</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>45988</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>45161</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>46280</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>46129</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44945</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>45376</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44971</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>46119</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44819</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>45916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45932</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45112</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>46044</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>46073</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>45978</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>45975</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>45890</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>45929</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>46119</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45932</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>46213</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>45063</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>45602</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>46195</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>45937</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45415</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44851</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>45526</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45621</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         <v>46042</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>46044</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45575</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45475</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45937</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45470</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45940</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>45649</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45952</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>46133</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>44637</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>46119</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45897</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45320</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>44911</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>45349</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>46076</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>45170</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45161</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>46043</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>46105</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45936</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45806</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>45028</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>45953</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>45975</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>45890</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>45189</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>46073</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>46073</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>45198</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>44945</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>45751</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>46195</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>46008</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45553</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>46006</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45809</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>46059</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>44929</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>46097</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>46065</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>45762</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45618</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>45233</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>44840</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44623</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>44742</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45349</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>45901</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>45278</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45985</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>46000</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45975</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>45897</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45049</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>46294</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>46030</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45349</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>44977</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>46279</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45462</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45721</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45978</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>44908</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45553</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45570</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45237</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45748</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>46098</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>46160</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>44853</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44750</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44904</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>45785</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44904</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>45223</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>45919</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>46177</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>44904</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>46217</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>46225</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44904</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45737</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>46155</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>46288</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45559</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45644</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>46137</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>46315</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>46275</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>45615</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>45245</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>45187</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45233</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45561</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45412</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44544</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>44956</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>44617</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>46198</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>44916</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45987</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45751</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45975</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>46282</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45538</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45533</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>45558</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45952</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44927</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>44643</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>45643</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45441</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45715</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45321</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>44957</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>44694</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>44515</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44742</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45313</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>44594</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>44785</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45223</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>44742</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>45509</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>46184</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>44928</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>46190</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45968</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45553</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45999</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45558</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45797</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>46051</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>46295</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>45719</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45096</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45763</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>45841</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>46125</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45118</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45867</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>45867</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>46120</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>44900</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45646</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45629</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45511</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45559</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>46038</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45280</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>46276</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>46142</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>45678</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>45238</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>45624</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45637</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>45685</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>45344</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>45617</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>44642</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45679</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45028</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45957</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>44879</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44510</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>44524</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44838</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44540</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>44613</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>44581</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>44852</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>44561</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>44566</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44755</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44852</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44540</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>44537</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44609</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>44889</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44516</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>44875</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>44886</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>44750</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>44517</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>44601</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>44722</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44722</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44721</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44845</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>44540</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28477,7 +28477,7 @@
         <v>44655</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>44704</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>44949</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45625</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45621</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45888</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45338</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>45800</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>45895</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45895</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>44757</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45412</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>45902</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45902</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45901</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45239</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45904</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>44721</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>45909</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44511</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45686</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45887</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45911</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>46120</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>46164</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45600</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>46066</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45916</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>46163</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>46163</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>46164</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>46164</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>46164</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>46164</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>45112</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
         <v>46164</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>46164</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>44937</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>44679</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>46164</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>46164</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>46164</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>46163</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45922</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45922</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>44986</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45922</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>45922</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>45922</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45922</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45324</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45924</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45924</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>44607</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>44742</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>45569</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45639</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>45588</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45583</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45576</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45580</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>46175</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>45702</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45937</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>45183</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>45370</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45944</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44952</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45315</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45462</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44883</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45707</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>46183</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>44837</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
         <v>45677</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>46184</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>45177</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45958</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>45632</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>45964</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44889</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>46190</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>46190</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>46190</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>44911</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45593</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45763</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45223</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45223</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45012</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45004</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45236</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45688</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>45588</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>44986</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>45708</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35655,7 +35655,7 @@
         <v>45985</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>45986</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>45985</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>44911</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>46206</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45667</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>45992</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45987</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>45159</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>45992</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>45992</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>46216</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>45264</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45993</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45660</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>46000</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>46000</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>46203</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45939</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>46073</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>46220</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>45779</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>46003</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>46003</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>46003</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45686</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>46003</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>46231</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>46003</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37792,7 +37792,7 @@
         <v>46231</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>46231</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>46231</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38026,7 +38026,7 @@
         <v>46007</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>46007</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>46279</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>46010</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>46010</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>46135</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>46013</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>46013</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>46280</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>46279</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>46279</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>46281</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>45686</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>46239</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45686</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>46281</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>46282</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>46019</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45789</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>46238</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>45790</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>46024</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>46029</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>46241</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>46283</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>46034</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>46241</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>46032</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45707</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>46038</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45748</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>46037</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>46037</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45561</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>46286</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40606,7 +40606,7 @@
         <v>46041</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>46287</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>46288</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>46132</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>45611</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>46286</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>45799</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>46045</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>46045</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>46050</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>46289</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45803</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45309</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>45805</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45587</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45691</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45551</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45807</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>46056</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>46294</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>45813</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>46066</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>46066</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>45818</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42408,7 +42408,7 @@
         <v>45435</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>46070</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>46248</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>45819</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42710,7 +42710,7 @@
         <v>46076</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42788,7 +42788,7 @@
         <v>46073</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>46078</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>46078</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>45722</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>45736</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45743</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45720</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>45720</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45743</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45978</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>46203</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>45477</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45012</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>46091</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>46206</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45376</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>46180</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>45789</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>46300</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>46206</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>45954</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>45149</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>46014</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>45475</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45793</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44922</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>46098</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45198</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>45002</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45847</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45847</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>45847</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>46097</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>46301</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45800</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>45866</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45807</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
         <v>46125</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>46114</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>46126</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>46132</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>44911</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>46133</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45646</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>45646</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45477</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>46309</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>46135</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45300</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>46307</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>46136</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46596,7 +46596,7 @@
         <v>46309</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>46139</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>45696</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>46314</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>44599</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>46314</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>46314</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>46139</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>46269</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>46139</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>46008</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47419,7 +47419,7 @@
         <v>45837</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47497,7 +47497,7 @@
         <v>46314</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45520</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45223</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>45636</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>46029</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47862,7 +47862,7 @@
         <v>46000</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47935,7 +47935,7 @@
         <v>46315</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>46272</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48081,7 +48081,7 @@
         <v>46315</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48154,7 +48154,7 @@
         <v>45634</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48227,7 +48227,7 @@
         <v>44790</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>44680</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>46317</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>46276</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>46142</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>45236</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>46275</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>45344</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48831,7 +48831,7 @@
         <v>46275</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>44977</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45221</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>46150</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49128,7 +49128,7 @@
         <v>45237</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49201,7 +49201,7 @@
         <v>46150</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49274,7 +49274,7 @@
         <v>46150</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>44655</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>45691</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>45260</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>46153</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>45693</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>44634</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>46154</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45547</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45057</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>44735</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>46156</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45688</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>45600</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         <v>45460</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>44750</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>45692</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45667</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>45691</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>44970</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45707</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>45770</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50910,7 +50910,7 @@
         <v>44711</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>45707</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45505</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51134,7 +51134,7 @@
         <v>45586</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>44922</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>44909</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>45057</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45096</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>44880</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>45261</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51665,7 +51665,7 @@
         <v>45089</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>45336</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51811,7 +51811,7 @@
         <v>45593</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45096</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45166</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45092</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>45457</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>45306</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45616</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>44529</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>45328</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>44609</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52556,7 +52556,7 @@
         <v>45428</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>45628</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45190</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52780,7 +52780,7 @@
         <v>45597</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45634</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>44564</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45681</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53082,7 +53082,7 @@
         <v>45681</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53160,7 +53160,7 @@
         <v>45691</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45107</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45762</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>45221</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>44635</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>45189</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53608,7 +53608,7 @@
         <v>45615</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53681,7 +53681,7 @@
         <v>45429</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>44706</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45709</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45572</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53983,7 +53983,7 @@
         <v>45231</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>45707</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54134,7 +54134,7 @@
         <v>45659</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54207,7 +54207,7 @@
         <v>45677</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45188</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>44743</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>44721</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         <v>45721</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>45321</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>44907</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
         <v>45315</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>45265</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54874,7 +54874,7 @@
         <v>45313</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
         <v>45302</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>44799</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>45231</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>45260</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55244,7 +55244,7 @@
         <v>45273</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55317,7 +55317,7 @@
         <v>44533</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55390,7 +55390,7 @@
         <v>44614</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45588</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>44790</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55609,7 +55609,7 @@
         <v>45475</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45690</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55755,7 +55755,7 @@
         <v>45342</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55833,7 +55833,7 @@
         <v>44952</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45008</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55979,7 +55979,7 @@
         <v>44889</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>44875</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56130,7 +56130,7 @@
         <v>45744</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56203,7 +56203,7 @@
         <v>45820</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56276,7 +56276,7 @@
         <v>46058</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56349,7 +56349,7 @@
         <v>46058</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56422,7 +56422,7 @@
         <v>46276</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45109</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>45155</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44585</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>45540</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>45690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>46191</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>44642</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46104</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45932</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>46108</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>45600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>46195</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>45924</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>46140</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>46195</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>46119</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45975</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>45988</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>45161</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>46280</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>46129</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44945</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>45376</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44971</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>46119</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44819</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>45916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45932</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45112</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>46044</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>46073</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>45978</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>45975</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>45890</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>45929</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>46119</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45932</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>46213</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>45063</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>45602</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>46195</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>45937</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45415</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44851</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>45526</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45621</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         <v>46042</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>46044</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45575</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45475</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45986</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45937</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45470</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>45940</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>45649</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45952</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>46133</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>44637</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>46119</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45897</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45320</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>44911</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>45349</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>46076</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>45170</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45161</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>46043</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>46105</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45936</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45806</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>45028</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>45953</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>45975</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>45890</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>45189</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>46073</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>46073</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>45198</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>44945</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>45751</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>46195</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>46008</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45553</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>46006</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45809</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>46059</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>44929</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>46097</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>46065</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>45762</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45618</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>45233</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>44840</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44623</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>44742</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45349</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>45901</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>45278</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45985</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>46000</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45975</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>45897</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45049</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>46294</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>46030</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45349</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>44977</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>46279</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45462</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45721</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45978</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>44908</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45553</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45570</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45237</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45748</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>46098</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>46160</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>44853</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44750</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44904</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>45785</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44904</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>45223</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>45919</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>46177</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>44904</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>46217</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>46225</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44904</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45737</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>46155</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>46288</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45559</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45644</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>46137</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>46315</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>46275</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>45615</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>45245</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>45187</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45233</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45561</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45412</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44544</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>44956</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>44617</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>46198</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>44916</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45987</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45751</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45975</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>46282</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45538</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45533</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>45558</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45952</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44927</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>44643</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>45643</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45441</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45715</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45321</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>44957</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>44694</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>44515</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44742</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45313</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>44594</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>44785</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45223</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>44742</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>45509</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>46184</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>44928</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>46190</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45968</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45553</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45999</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45558</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45797</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>46051</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>46295</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>45719</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45096</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45763</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>45841</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>46125</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45118</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45867</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>45867</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>46120</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>44900</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45646</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45629</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45511</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45559</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>46038</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45280</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>46276</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>46142</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>45678</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>45238</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>45624</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45637</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>45685</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>45344</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>45617</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>44642</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45679</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45028</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45957</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>44879</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44510</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>44524</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44838</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44540</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>44613</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>44581</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>44852</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>44561</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>44566</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44755</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44852</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44540</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>44537</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44609</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>44889</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44516</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>44875</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>44886</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>44750</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>44517</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>44601</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>44722</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44722</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44721</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44845</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>44540</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28477,7 +28477,7 @@
         <v>44655</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>44704</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>44949</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45625</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45621</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45888</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45338</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>45800</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>45895</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45895</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>44757</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45412</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>45902</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45902</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45901</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45239</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45904</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>44721</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>45909</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44511</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45686</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45887</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45911</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>46120</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>46164</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45600</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>46066</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45916</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>46163</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>46163</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>46164</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>46164</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>46164</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>46164</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>45112</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
         <v>46164</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>46164</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>44937</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>44679</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>46164</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>46164</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>46164</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>46163</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45922</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45922</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>44986</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45922</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>45922</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>45922</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45922</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45324</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45924</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45924</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>44607</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>44742</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>45569</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45639</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>45588</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45583</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45576</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45580</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>46175</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>45702</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45937</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>45183</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>45370</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45944</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44952</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45315</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45462</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44883</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45707</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>46183</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>44837</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
         <v>45677</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>46184</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>45177</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45958</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>45632</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>45964</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44889</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>46190</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>46190</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>46190</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>44911</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45593</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45763</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45223</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45223</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45012</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45004</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45236</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45688</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>45588</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>44986</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>45708</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35655,7 +35655,7 @@
         <v>45985</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>45986</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>45985</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>44911</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>46206</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45667</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>45992</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45987</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>45159</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>45992</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>45992</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>46216</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>45264</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45993</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45660</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>46000</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>46000</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>46203</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45939</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>46073</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>46220</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>45779</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>46003</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>46003</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>46003</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45686</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>46003</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>46231</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>46003</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37792,7 +37792,7 @@
         <v>46231</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>46231</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>46231</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38026,7 +38026,7 @@
         <v>46007</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>46007</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>46279</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>46010</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>46010</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>46135</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>46013</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>46013</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>46280</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>46279</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>46279</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>46281</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>45686</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>46239</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45686</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>46281</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>46282</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>46019</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45789</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>46238</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>45790</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>46024</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>46029</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>46241</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>46283</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>46034</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>46241</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>46032</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45707</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>46038</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45748</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>46037</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>46037</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45561</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>46286</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40606,7 +40606,7 @@
         <v>46041</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>46287</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>46288</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>46132</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>45611</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>46286</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>45799</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>46045</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>46045</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>46050</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>46289</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45803</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45309</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>45805</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45587</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45691</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45551</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45807</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>46056</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>46294</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>45813</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>46066</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>46066</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>45818</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42408,7 +42408,7 @@
         <v>45435</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>46070</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>46248</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>45819</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42710,7 +42710,7 @@
         <v>46076</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42788,7 +42788,7 @@
         <v>46073</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>46078</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>46078</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>45722</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>45736</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45743</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45720</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>45720</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45743</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45978</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>46203</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>45477</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45012</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>46091</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>46206</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45376</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>46180</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>45789</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>46300</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>46206</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>45954</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>45149</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>46014</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>45475</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45793</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>44922</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>46098</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45198</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>45002</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>45847</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45847</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>45847</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>46097</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>46301</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>45800</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>45866</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45807</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
         <v>46125</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>46114</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>46126</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>46132</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>44911</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>46133</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45646</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>45646</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45477</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>46309</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>46135</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45300</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>46307</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>46136</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46596,7 +46596,7 @@
         <v>46309</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>46139</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>45696</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>46314</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>44599</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>46314</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>46314</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>46139</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>46269</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>46139</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>46008</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47419,7 +47419,7 @@
         <v>45837</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47497,7 +47497,7 @@
         <v>46314</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45520</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45223</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>45636</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>46029</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47862,7 +47862,7 @@
         <v>46000</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47935,7 +47935,7 @@
         <v>46315</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>46272</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48081,7 +48081,7 @@
         <v>46315</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48154,7 +48154,7 @@
         <v>45634</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48227,7 +48227,7 @@
         <v>44790</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>44680</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>46317</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>46276</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>46142</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>45236</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>46275</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>45344</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48831,7 +48831,7 @@
         <v>46275</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>44977</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45221</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>46150</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49128,7 +49128,7 @@
         <v>45237</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49201,7 +49201,7 @@
         <v>46150</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49274,7 +49274,7 @@
         <v>46150</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>44655</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>45691</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>45260</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>46153</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>45693</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>44634</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>46154</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45547</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45057</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>44735</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>46156</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45688</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>45600</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         <v>45460</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>44750</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>45692</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45667</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>45691</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>44970</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45707</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>45770</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50910,7 +50910,7 @@
         <v>44711</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>45707</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45505</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51134,7 +51134,7 @@
         <v>45586</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>44922</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>44909</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>45057</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45096</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>44880</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>45261</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51665,7 +51665,7 @@
         <v>45089</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>45336</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51811,7 +51811,7 @@
         <v>45593</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45096</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45166</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45092</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>45457</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>45306</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45616</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>44529</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>45328</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>44609</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52556,7 +52556,7 @@
         <v>45428</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>45628</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45190</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52780,7 +52780,7 @@
         <v>45597</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45634</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>44564</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45681</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53082,7 +53082,7 @@
         <v>45681</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53160,7 +53160,7 @@
         <v>45691</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45107</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45762</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>45221</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>44635</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>45189</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53608,7 +53608,7 @@
         <v>45615</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53681,7 +53681,7 @@
         <v>45429</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>44706</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45709</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45572</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53983,7 +53983,7 @@
         <v>45231</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>45707</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54134,7 +54134,7 @@
         <v>45659</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54207,7 +54207,7 @@
         <v>45677</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45188</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>44743</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>44721</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         <v>45721</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>45321</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>44907</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
         <v>45315</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>45265</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54874,7 +54874,7 @@
         <v>45313</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
         <v>45302</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>44799</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>45231</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>45260</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55244,7 +55244,7 @@
         <v>45273</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55317,7 +55317,7 @@
         <v>44533</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55390,7 +55390,7 @@
         <v>44614</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45588</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>44790</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55609,7 +55609,7 @@
         <v>45475</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45690</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55755,7 +55755,7 @@
         <v>45342</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55833,7 +55833,7 @@
         <v>44952</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55906,7 +55906,7 @@
         <v>45008</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55979,7 +55979,7 @@
         <v>44889</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>44875</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56130,7 +56130,7 @@
         <v>45744</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56203,7 +56203,7 @@
         <v>45820</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56276,7 +56276,7 @@
         <v>46058</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56349,7 +56349,7 @@
         <v>46058</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56422,7 +56422,7 @@
         <v>46276</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
